--- a/SpectraGuard_Test_Report.xlsx
+++ b/SpectraGuard_Test_Report.xlsx
@@ -591,7 +591,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -5341,7 +5341,7 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
@@ -6291,7 +6291,7 @@
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J117" s="2" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J121" s="2" t="inlineStr">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J125" s="2" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J127" s="2" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J129" s="2" t="inlineStr">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J131" s="2" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J133" s="2" t="inlineStr">
@@ -7191,7 +7191,7 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J135" s="2" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J137" s="2" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
@@ -7441,7 +7441,7 @@
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J139" s="2" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J141" s="2" t="inlineStr">
@@ -7591,7 +7591,7 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
@@ -7641,7 +7641,7 @@
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J143" s="2" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J145" s="2" t="inlineStr">
@@ -7791,7 +7791,7 @@
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J147" s="2" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
@@ -7941,7 +7941,7 @@
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J149" s="2" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J151" s="2" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J152" s="2" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J153" s="2" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J154" s="2" t="inlineStr">
@@ -8241,7 +8241,7 @@
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J155" s="2" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
@@ -8341,7 +8341,7 @@
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J157" s="2" t="inlineStr">
@@ -8391,7 +8391,7 @@
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J159" s="2" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J160" s="2" t="inlineStr">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J161" s="2" t="inlineStr">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr">
@@ -8641,7 +8641,7 @@
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J163" s="2" t="inlineStr">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J164" s="2" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J165" s="2" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J166" s="2" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J167" s="2" t="inlineStr">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J168" s="2" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J169" s="2" t="inlineStr">
@@ -8991,7 +8991,7 @@
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J170" s="2" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J171" s="2" t="inlineStr">
@@ -9091,7 +9091,7 @@
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">
@@ -9141,7 +9141,7 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J173" s="2" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J174" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J175" s="2" t="inlineStr">
@@ -9291,7 +9291,7 @@
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J176" s="2" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J177" s="2" t="inlineStr">
@@ -9391,7 +9391,7 @@
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J178" s="2" t="inlineStr">
@@ -9441,7 +9441,7 @@
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J179" s="2" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J180" s="2" t="inlineStr">
@@ -9541,7 +9541,7 @@
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J181" s="2" t="inlineStr">
@@ -9591,7 +9591,7 @@
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J182" s="2" t="inlineStr">
@@ -9641,7 +9641,7 @@
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J183" s="2" t="inlineStr">
@@ -9691,7 +9691,7 @@
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J184" s="2" t="inlineStr">
@@ -9741,7 +9741,7 @@
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J185" s="2" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J186" s="2" t="inlineStr">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J187" s="2" t="inlineStr">
@@ -9891,7 +9891,7 @@
       </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J188" s="2" t="inlineStr">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J189" s="2" t="inlineStr">
@@ -9991,7 +9991,7 @@
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J190" s="2" t="inlineStr">
@@ -10041,7 +10041,7 @@
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J191" s="2" t="inlineStr">
@@ -10091,7 +10091,7 @@
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J192" s="2" t="inlineStr">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J193" s="2" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J194" s="2" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J195" s="2" t="inlineStr">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J196" s="2" t="inlineStr">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J197" s="2" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J198" s="2" t="inlineStr">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J199" s="2" t="inlineStr">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J200" s="2" t="inlineStr">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J201" s="2" t="inlineStr">
@@ -10591,7 +10591,7 @@
       </c>
       <c r="I202" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J202" s="2" t="inlineStr">
@@ -10641,7 +10641,7 @@
       </c>
       <c r="I203" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J203" s="2" t="inlineStr">
@@ -10691,7 +10691,7 @@
       </c>
       <c r="I204" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J204" s="2" t="inlineStr">
@@ -10741,7 +10741,7 @@
       </c>
       <c r="I205" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J205" s="2" t="inlineStr">
@@ -10791,7 +10791,7 @@
       </c>
       <c r="I206" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J206" s="2" t="inlineStr">
@@ -10841,7 +10841,7 @@
       </c>
       <c r="I207" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J207" s="2" t="inlineStr">
@@ -10891,7 +10891,7 @@
       </c>
       <c r="I208" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J208" s="2" t="inlineStr">
@@ -10941,7 +10941,7 @@
       </c>
       <c r="I209" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J209" s="2" t="inlineStr">
@@ -10991,7 +10991,7 @@
       </c>
       <c r="I210" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J210" s="2" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="I211" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J211" s="2" t="inlineStr">
@@ -11091,7 +11091,7 @@
       </c>
       <c r="I212" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J212" s="2" t="inlineStr">
@@ -11141,7 +11141,7 @@
       </c>
       <c r="I213" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J213" s="2" t="inlineStr">
@@ -11191,7 +11191,7 @@
       </c>
       <c r="I214" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J214" s="2" t="inlineStr">
@@ -11241,7 +11241,7 @@
       </c>
       <c r="I215" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J215" s="2" t="inlineStr">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="I216" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J216" s="2" t="inlineStr">
@@ -11341,7 +11341,7 @@
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J217" s="2" t="inlineStr">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="I218" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J218" s="2" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="I219" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J219" s="2" t="inlineStr">
@@ -11491,7 +11491,7 @@
       </c>
       <c r="I220" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J220" s="2" t="inlineStr">
@@ -11541,7 +11541,7 @@
       </c>
       <c r="I221" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J221" s="2" t="inlineStr">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="I222" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J222" s="2" t="inlineStr">
@@ -11641,7 +11641,7 @@
       </c>
       <c r="I223" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J223" s="2" t="inlineStr">
@@ -11691,7 +11691,7 @@
       </c>
       <c r="I224" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J224" s="2" t="inlineStr">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="I225" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J225" s="2" t="inlineStr">
@@ -11791,7 +11791,7 @@
       </c>
       <c r="I226" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J226" s="2" t="inlineStr">
@@ -11841,7 +11841,7 @@
       </c>
       <c r="I227" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J227" s="2" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="I228" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J228" s="2" t="inlineStr">
@@ -11941,7 +11941,7 @@
       </c>
       <c r="I229" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J229" s="2" t="inlineStr">
@@ -11991,7 +11991,7 @@
       </c>
       <c r="I230" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J230" s="2" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="I231" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J231" s="2" t="inlineStr">
@@ -12091,7 +12091,7 @@
       </c>
       <c r="I232" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J232" s="2" t="inlineStr">
@@ -12141,7 +12141,7 @@
       </c>
       <c r="I233" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J233" s="2" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="I234" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J234" s="2" t="inlineStr">
@@ -12241,7 +12241,7 @@
       </c>
       <c r="I235" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J235" s="2" t="inlineStr">
@@ -12291,7 +12291,7 @@
       </c>
       <c r="I236" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J236" s="2" t="inlineStr">
@@ -12341,7 +12341,7 @@
       </c>
       <c r="I237" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J237" s="2" t="inlineStr">
@@ -12391,7 +12391,7 @@
       </c>
       <c r="I238" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J238" s="2" t="inlineStr">
@@ -12441,7 +12441,7 @@
       </c>
       <c r="I239" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J239" s="2" t="inlineStr">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="I240" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J240" s="2" t="inlineStr">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="I241" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J241" s="2" t="inlineStr">
@@ -12591,7 +12591,7 @@
       </c>
       <c r="I242" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J242" s="2" t="inlineStr">
@@ -12641,7 +12641,7 @@
       </c>
       <c r="I243" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J243" s="2" t="inlineStr">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="I244" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J244" s="2" t="inlineStr">
@@ -12741,7 +12741,7 @@
       </c>
       <c r="I245" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J245" s="2" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="I246" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J246" s="2" t="inlineStr">
@@ -12841,7 +12841,7 @@
       </c>
       <c r="I247" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J247" s="2" t="inlineStr">
@@ -12891,7 +12891,7 @@
       </c>
       <c r="I248" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J248" s="2" t="inlineStr">
@@ -12941,7 +12941,7 @@
       </c>
       <c r="I249" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J249" s="2" t="inlineStr">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="I250" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J250" s="2" t="inlineStr">
@@ -13041,7 +13041,7 @@
       </c>
       <c r="I251" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J251" s="2" t="inlineStr">
@@ -13091,7 +13091,7 @@
       </c>
       <c r="I252" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J252" s="2" t="inlineStr">
@@ -13141,7 +13141,7 @@
       </c>
       <c r="I253" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J253" s="2" t="inlineStr">
@@ -13191,7 +13191,7 @@
       </c>
       <c r="I254" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J254" s="2" t="inlineStr">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="I255" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J255" s="2" t="inlineStr">
@@ -13291,7 +13291,7 @@
       </c>
       <c r="I256" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J256" s="2" t="inlineStr">
@@ -13341,7 +13341,7 @@
       </c>
       <c r="I257" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J257" s="2" t="inlineStr">
@@ -13391,7 +13391,7 @@
       </c>
       <c r="I258" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J258" s="2" t="inlineStr">
@@ -13441,7 +13441,7 @@
       </c>
       <c r="I259" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J259" s="2" t="inlineStr">
@@ -13491,7 +13491,7 @@
       </c>
       <c r="I260" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J260" s="2" t="inlineStr">
@@ -13541,7 +13541,7 @@
       </c>
       <c r="I261" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J261" s="2" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="I262" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J262" s="2" t="inlineStr">
@@ -13641,7 +13641,7 @@
       </c>
       <c r="I263" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J263" s="2" t="inlineStr">
@@ -13691,7 +13691,7 @@
       </c>
       <c r="I264" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J264" s="2" t="inlineStr">
@@ -13741,7 +13741,7 @@
       </c>
       <c r="I265" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J265" s="2" t="inlineStr">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="I266" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J266" s="2" t="inlineStr">
@@ -13841,7 +13841,7 @@
       </c>
       <c r="I267" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J267" s="2" t="inlineStr">
@@ -13891,7 +13891,7 @@
       </c>
       <c r="I268" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J268" s="2" t="inlineStr">
@@ -13941,7 +13941,7 @@
       </c>
       <c r="I269" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J269" s="2" t="inlineStr">
@@ -13991,7 +13991,7 @@
       </c>
       <c r="I270" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J270" s="2" t="inlineStr">
@@ -14041,7 +14041,7 @@
       </c>
       <c r="I271" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J271" s="2" t="inlineStr">
@@ -14091,7 +14091,7 @@
       </c>
       <c r="I272" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J272" s="2" t="inlineStr">
@@ -14141,7 +14141,7 @@
       </c>
       <c r="I273" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J273" s="2" t="inlineStr">
@@ -14191,7 +14191,7 @@
       </c>
       <c r="I274" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J274" s="2" t="inlineStr">
@@ -14241,7 +14241,7 @@
       </c>
       <c r="I275" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J275" s="2" t="inlineStr">
@@ -14291,7 +14291,7 @@
       </c>
       <c r="I276" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J276" s="2" t="inlineStr">
@@ -14341,7 +14341,7 @@
       </c>
       <c r="I277" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J277" s="2" t="inlineStr">
@@ -14391,7 +14391,7 @@
       </c>
       <c r="I278" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J278" s="2" t="inlineStr">
@@ -14441,7 +14441,7 @@
       </c>
       <c r="I279" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J279" s="2" t="inlineStr">
@@ -14491,7 +14491,7 @@
       </c>
       <c r="I280" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J280" s="2" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="I281" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J281" s="2" t="inlineStr">
@@ -14591,7 +14591,7 @@
       </c>
       <c r="I282" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J282" s="2" t="inlineStr">
@@ -14641,7 +14641,7 @@
       </c>
       <c r="I283" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J283" s="2" t="inlineStr">
@@ -14691,7 +14691,7 @@
       </c>
       <c r="I284" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J284" s="2" t="inlineStr">
@@ -14741,7 +14741,7 @@
       </c>
       <c r="I285" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J285" s="2" t="inlineStr">
@@ -14791,7 +14791,7 @@
       </c>
       <c r="I286" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J286" s="2" t="inlineStr">
@@ -14841,7 +14841,7 @@
       </c>
       <c r="I287" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J287" s="2" t="inlineStr">
@@ -14891,7 +14891,7 @@
       </c>
       <c r="I288" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J288" s="2" t="inlineStr">
@@ -14941,7 +14941,7 @@
       </c>
       <c r="I289" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J289" s="2" t="inlineStr">
@@ -14991,7 +14991,7 @@
       </c>
       <c r="I290" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J290" s="2" t="inlineStr">
@@ -15041,7 +15041,7 @@
       </c>
       <c r="I291" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J291" s="2" t="inlineStr">
@@ -15091,7 +15091,7 @@
       </c>
       <c r="I292" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J292" s="2" t="inlineStr">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="I293" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J293" s="2" t="inlineStr">
@@ -15191,7 +15191,7 @@
       </c>
       <c r="I294" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J294" s="2" t="inlineStr">
@@ -15241,7 +15241,7 @@
       </c>
       <c r="I295" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J295" s="2" t="inlineStr">
@@ -15291,7 +15291,7 @@
       </c>
       <c r="I296" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J296" s="2" t="inlineStr">
@@ -15341,7 +15341,7 @@
       </c>
       <c r="I297" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J297" s="2" t="inlineStr">
@@ -15391,7 +15391,7 @@
       </c>
       <c r="I298" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J298" s="2" t="inlineStr">
@@ -15441,7 +15441,7 @@
       </c>
       <c r="I299" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J299" s="2" t="inlineStr">
@@ -15491,7 +15491,7 @@
       </c>
       <c r="I300" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J300" s="2" t="inlineStr">
@@ -15541,7 +15541,7 @@
       </c>
       <c r="I301" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
       <c r="J301" s="2" t="inlineStr">
@@ -15672,7 +15672,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>9.789999999999999</v>
+        <v>21.59</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -15681,7 +15681,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
     </row>
@@ -15723,7 +15723,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>93.01000000000001</v>
+        <v>3.89</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
@@ -15732,7 +15732,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
     </row>
@@ -15774,7 +15774,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>75.27</v>
+        <v>4.45</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -15787,7 +15787,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
     </row>
@@ -15829,7 +15829,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>40.2</v>
+        <v>3.99</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
@@ -15842,7 +15842,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
     </row>
@@ -15884,7 +15884,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>196.73</v>
+        <v>8.82</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
     </row>
@@ -15935,7 +15935,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>4</v>
+        <v>4.45</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -15944,7 +15944,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
     </row>
@@ -15986,7 +15986,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -15995,7 +15995,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
     </row>
@@ -16037,7 +16037,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>4</v>
+        <v>5.13</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
     </row>
@@ -16088,7 +16088,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>5.2</v>
+        <v>4.51</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -16097,7 +16097,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
     </row>
@@ -16139,7 +16139,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>20.98</v>
+        <v>2.24</v>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
@@ -16148,7 +16148,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
     </row>
@@ -16190,7 +16190,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>15.81</v>
+        <v>2.88</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -16199,7 +16199,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:57</t>
+          <t>2026-08-10 11:44:10</t>
         </is>
       </c>
     </row>
@@ -16241,7 +16241,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>370.45</v>
+        <v>283.78</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
@@ -16250,7 +16250,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -16292,7 +16292,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>8.02</v>
+        <v>24.47</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -16343,7 +16343,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>26</v>
+        <v>19.92</v>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
@@ -16352,7 +16352,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -16394,7 +16394,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>34.58</v>
+        <v>10.41</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
@@ -16403,7 +16403,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -16445,7 +16445,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>44.37</v>
+        <v>7.78</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
@@ -16454,7 +16454,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -16496,7 +16496,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>5.96</v>
+        <v>7.34</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -16547,7 +16547,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>54.72</v>
+        <v>6.3</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -16556,7 +16556,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -16598,7 +16598,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>9.23</v>
+        <v>5.87</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -16649,7 +16649,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>24.15</v>
+        <v>7.1</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -16700,7 +16700,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>5</v>
+        <v>21.82</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -16751,7 +16751,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>22.42</v>
+        <v>6.91</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -16802,7 +16802,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>20.58</v>
+        <v>6.01</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
@@ -16811,7 +16811,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -16853,7 +16853,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>8.710000000000001</v>
+        <v>5.75</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -16904,7 +16904,7 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>32.53</v>
+        <v>7.5</v>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
@@ -16913,7 +16913,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -16955,7 +16955,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>10.11</v>
+        <v>6.34</v>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
@@ -16964,7 +16964,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -17006,7 +17006,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -17057,7 +17057,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>7</v>
+        <v>5.94</v>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
@@ -17066,7 +17066,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -17108,7 +17108,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>30.98</v>
+        <v>3.91</v>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -17159,7 +17159,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>5</v>
+        <v>5.22</v>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -17168,7 +17168,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -17210,7 +17210,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>5</v>
+        <v>6.06</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -17219,7 +17219,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -17261,7 +17261,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>6</v>
+        <v>5.84</v>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
@@ -17270,7 +17270,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -17312,7 +17312,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
@@ -17321,7 +17321,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -17363,7 +17363,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>5.11</v>
+        <v>6</v>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
@@ -17372,7 +17372,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -17414,7 +17414,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>6.55</v>
+        <v>4.33</v>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
@@ -17423,7 +17423,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -17465,7 +17465,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>3.54</v>
+        <v>4.58</v>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -17474,7 +17474,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -17516,7 +17516,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
@@ -17525,7 +17525,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -17567,7 +17567,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>4.24</v>
+        <v>3.83</v>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -17618,7 +17618,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>5.76</v>
+        <v>5.13</v>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
@@ -17627,7 +17627,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -17669,7 +17669,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>4.21</v>
+        <v>4.87</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
@@ -17678,7 +17678,7 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -17720,7 +17720,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>3.91</v>
+        <v>5.33</v>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
@@ -17733,7 +17733,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -17775,7 +17775,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>49.91</v>
+        <v>3.79</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
@@ -17788,7 +17788,7 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -17830,7 +17830,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>23.25</v>
+        <v>10.71</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
@@ -17839,7 +17839,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -17881,7 +17881,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>7.89</v>
+        <v>5.6</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -17932,7 +17932,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>5.99</v>
+        <v>4.54</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -17941,7 +17941,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -17983,7 +17983,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>7</v>
+        <v>6.82</v>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -18034,7 +18034,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>5</v>
+        <v>5.34</v>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
@@ -18043,7 +18043,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -18085,7 +18085,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>3</v>
+        <v>4.23</v>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -18136,7 +18136,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>5.29</v>
+        <v>6.78</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -18145,7 +18145,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -18187,7 +18187,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>8.98</v>
+        <v>15.7</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
@@ -18196,7 +18196,7 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -18238,7 +18238,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>4.1</v>
+        <v>6.65</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -18289,7 +18289,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>7.38</v>
+        <v>4.22</v>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -18298,7 +18298,7 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -18340,7 +18340,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>5.8</v>
+        <v>5.54</v>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
@@ -18349,7 +18349,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -18391,7 +18391,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>7.04</v>
+        <v>5.7</v>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -18442,7 +18442,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>4.54</v>
+        <v>4.89</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -18493,7 +18493,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>5.46</v>
+        <v>6.65</v>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
@@ -18502,7 +18502,7 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -18544,7 +18544,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>6</v>
+        <v>4.04</v>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -18553,7 +18553,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -18595,7 +18595,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>6</v>
+        <v>5.86</v>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
@@ -18604,7 +18604,7 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -18646,7 +18646,7 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>7.37</v>
+        <v>6.37</v>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
@@ -18655,7 +18655,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -18697,7 +18697,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>6.63</v>
+        <v>4.58</v>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
@@ -18706,7 +18706,7 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -18748,7 +18748,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>7</v>
+        <v>5.19</v>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
@@ -18757,7 +18757,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -18799,7 +18799,7 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>7</v>
+        <v>6.63</v>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
@@ -18808,7 +18808,7 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -18850,7 +18850,7 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>5.75</v>
+        <v>6.97</v>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
@@ -18859,7 +18859,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -18901,7 +18901,7 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>4.98</v>
+        <v>5.83</v>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
@@ -18910,7 +18910,7 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -18952,7 +18952,7 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>7</v>
+        <v>6.56</v>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
@@ -18961,7 +18961,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -19003,7 +19003,7 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>4</v>
+        <v>4.89</v>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
@@ -19012,7 +19012,7 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -19054,7 +19054,7 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>4</v>
+        <v>5.45</v>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
@@ -19063,7 +19063,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -19105,7 +19105,7 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>6.53</v>
+        <v>7.18</v>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -19156,7 +19156,7 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>5.47</v>
+        <v>5.28</v>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
@@ -19165,7 +19165,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -19207,7 +19207,7 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>5</v>
+        <v>7.61</v>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -19258,7 +19258,7 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>12.22</v>
+        <v>5.25</v>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
@@ -19267,7 +19267,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -19309,7 +19309,7 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>33.99</v>
+        <v>4.65</v>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
@@ -19318,7 +19318,7 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -19360,7 +19360,7 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>15.89</v>
+        <v>4.65</v>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
@@ -19369,7 +19369,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -19411,7 +19411,7 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>15.6</v>
+        <v>4.57</v>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -19420,7 +19420,7 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -19462,7 +19462,7 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>7.41</v>
+        <v>2.87</v>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
@@ -19471,7 +19471,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -19513,7 +19513,7 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>6</v>
+        <v>3.09</v>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
@@ -19522,7 +19522,7 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -19564,7 +19564,7 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>6</v>
+        <v>4.93</v>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -19615,7 +19615,7 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>3.99</v>
+        <v>4.91</v>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
@@ -19624,7 +19624,7 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -19666,7 +19666,7 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>5.74</v>
+        <v>4.81</v>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
@@ -19679,7 +19679,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -19721,7 +19721,7 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>4.32</v>
+        <v>3.81</v>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -19776,7 +19776,7 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>7.09</v>
+        <v>8.84</v>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -19827,7 +19827,7 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>4.91</v>
+        <v>5.19</v>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -19878,7 +19878,7 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>5</v>
+        <v>4.45</v>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
@@ -19887,7 +19887,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -19929,7 +19929,7 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>3</v>
+        <v>7.19</v>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
@@ -19938,7 +19938,7 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -19980,7 +19980,7 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
@@ -19989,7 +19989,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -20031,7 +20031,7 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>4</v>
+        <v>4.13</v>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
@@ -20040,7 +20040,7 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -20082,7 +20082,7 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>4</v>
+        <v>4.17</v>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
@@ -20091,7 +20091,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:58</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -20133,7 +20133,7 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>97.64</v>
+        <v>309.62</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
@@ -20142,7 +20142,7 @@
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -20184,7 +20184,7 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>8.56</v>
+        <v>20.23</v>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
@@ -20193,7 +20193,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -20235,7 +20235,7 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>9.789999999999999</v>
+        <v>14.75</v>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
@@ -20244,7 +20244,7 @@
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -20286,7 +20286,7 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>5.5</v>
+        <v>10.08</v>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
@@ -20295,7 +20295,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -20337,7 +20337,7 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>7</v>
+        <v>6.51</v>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
@@ -20346,7 +20346,7 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -20388,7 +20388,7 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>4.04</v>
+        <v>6.47</v>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
@@ -20397,7 +20397,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -20439,7 +20439,7 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>5.05</v>
+        <v>8.06</v>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
@@ -20448,7 +20448,7 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -20490,7 +20490,7 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
@@ -20499,7 +20499,7 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -20541,7 +20541,7 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>7.17</v>
+        <v>8.33</v>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
@@ -20550,7 +20550,7 @@
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -20592,7 +20592,7 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>5.83</v>
+        <v>6.44</v>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
@@ -20601,7 +20601,7 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -20643,7 +20643,7 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>4.15</v>
+        <v>6.49</v>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
@@ -20652,7 +20652,7 @@
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -20694,7 +20694,7 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>5.85</v>
+        <v>7.2</v>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
@@ -20703,7 +20703,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -20745,7 +20745,7 @@
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>4.23</v>
+        <v>6.22</v>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -20796,7 +20796,7 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>4.77</v>
+        <v>7.49</v>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -20847,7 +20847,7 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>6.4</v>
+        <v>6.22</v>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
@@ -20856,7 +20856,7 @@
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -20898,7 +20898,7 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>4</v>
+        <v>6.68</v>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
@@ -20907,7 +20907,7 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -20949,7 +20949,7 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>4.04</v>
+        <v>5.7</v>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
@@ -20958,7 +20958,7 @@
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -21000,7 +21000,7 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>4.51</v>
+        <v>5.01</v>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
@@ -21009,7 +21009,7 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -21051,7 +21051,7 @@
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>5.95</v>
+        <v>5.73</v>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
@@ -21060,7 +21060,7 @@
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -21102,7 +21102,7 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>3.85</v>
+        <v>5.14</v>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
@@ -21111,7 +21111,7 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -21153,7 +21153,7 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>5</v>
+        <v>5.33</v>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
@@ -21162,7 +21162,7 @@
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -21204,7 +21204,7 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>6.07</v>
+        <v>6.13</v>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
@@ -21213,7 +21213,7 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -21255,7 +21255,7 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>5.1</v>
+        <v>4.87</v>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -21306,7 +21306,7 @@
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>3.9</v>
+        <v>4.09</v>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -21357,7 +21357,7 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>5.03</v>
+        <v>5.76</v>
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
@@ -21366,7 +21366,7 @@
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -21408,7 +21408,7 @@
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>3.66</v>
+        <v>3.32</v>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
@@ -21417,7 +21417,7 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -21459,7 +21459,7 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>2.97</v>
+        <v>2.57</v>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
@@ -21468,7 +21468,7 @@
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:11</t>
         </is>
       </c>
     </row>
@@ -21510,7 +21510,7 @@
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>4</v>
+        <v>5.95</v>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
@@ -21519,7 +21519,7 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -21561,7 +21561,7 @@
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>4.98</v>
+        <v>5.39</v>
       </c>
       <c r="J117" s="4" t="inlineStr">
         <is>
@@ -21570,7 +21570,7 @@
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -21612,7 +21612,7 @@
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>4.7</v>
+        <v>5.66</v>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
@@ -21625,7 +21625,7 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -21667,7 +21667,7 @@
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>3.84</v>
+        <v>19.06</v>
       </c>
       <c r="J119" s="4" t="inlineStr">
         <is>
@@ -21680,7 +21680,7 @@
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -21722,7 +21722,7 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
@@ -21731,7 +21731,7 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -21773,7 +21773,7 @@
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>5</v>
+        <v>27.99</v>
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
@@ -21782,7 +21782,7 @@
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -21824,7 +21824,7 @@
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>4.08</v>
+        <v>7.12</v>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
@@ -21833,7 +21833,7 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -21875,7 +21875,7 @@
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>6</v>
+        <v>6.54</v>
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
@@ -21884,7 +21884,7 @@
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -21926,7 +21926,7 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>4.58</v>
+        <v>6.76</v>
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
@@ -21935,7 +21935,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -21977,7 +21977,7 @@
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>4.43</v>
+        <v>4.66</v>
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
@@ -21986,7 +21986,7 @@
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -22028,7 +22028,7 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>3.32</v>
+        <v>6.25</v>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
@@ -22037,7 +22037,7 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -22079,7 +22079,7 @@
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>11.41</v>
+        <v>228.21</v>
       </c>
       <c r="J127" s="4" t="inlineStr">
         <is>
@@ -22088,7 +22088,7 @@
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -22130,7 +22130,7 @@
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>6.76</v>
+        <v>19.79</v>
       </c>
       <c r="J128" s="4" t="inlineStr">
         <is>
@@ -22139,7 +22139,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -22181,7 +22181,7 @@
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>8.949999999999999</v>
+        <v>26.66</v>
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
@@ -22190,7 +22190,7 @@
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -22232,7 +22232,7 @@
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>7</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
@@ -22241,7 +22241,7 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -22283,7 +22283,7 @@
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>11.31</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -22334,7 +22334,7 @@
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>4.84</v>
+        <v>5.45</v>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
@@ -22343,7 +22343,7 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -22385,7 +22385,7 @@
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>7.85</v>
+        <v>8.84</v>
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
@@ -22394,7 +22394,7 @@
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -22436,7 +22436,7 @@
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>6</v>
+        <v>4.87</v>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
@@ -22445,7 +22445,7 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -22487,7 +22487,7 @@
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>8.119999999999999</v>
+        <v>7.12</v>
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
@@ -22496,7 +22496,7 @@
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -22538,7 +22538,7 @@
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>7.11</v>
+        <v>6.55</v>
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
@@ -22547,7 +22547,7 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -22589,7 +22589,7 @@
         </is>
       </c>
       <c r="I137" s="2" t="n">
-        <v>5.89</v>
+        <v>6.29</v>
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
@@ -22598,7 +22598,7 @@
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -22640,7 +22640,7 @@
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>9</v>
+        <v>7.55</v>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
@@ -22649,7 +22649,7 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -22691,7 +22691,7 @@
         </is>
       </c>
       <c r="I139" s="2" t="n">
-        <v>7.09</v>
+        <v>11.64</v>
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
@@ -22700,7 +22700,7 @@
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -22742,7 +22742,7 @@
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>6.91</v>
+        <v>7.25</v>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
@@ -22751,7 +22751,7 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -22793,7 +22793,7 @@
         </is>
       </c>
       <c r="I141" s="2" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -22844,7 +22844,7 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>5</v>
+        <v>6.35</v>
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
@@ -22853,7 +22853,7 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -22895,7 +22895,7 @@
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>5.17</v>
+        <v>5.25</v>
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
@@ -22904,7 +22904,7 @@
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -22946,7 +22946,7 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>4</v>
+        <v>5.68</v>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
@@ -22955,7 +22955,7 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -22997,7 +22997,7 @@
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>5</v>
+        <v>8.74</v>
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
@@ -23006,7 +23006,7 @@
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -23048,7 +23048,7 @@
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>7.08</v>
+        <v>6.08</v>
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
@@ -23057,7 +23057,7 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -23099,7 +23099,7 @@
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>5</v>
+        <v>7.07</v>
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
@@ -23108,7 +23108,7 @@
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -23150,7 +23150,7 @@
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>5</v>
+        <v>6.51</v>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
@@ -23159,7 +23159,7 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="I149" s="2" t="n">
-        <v>6</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
@@ -23210,7 +23210,7 @@
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -23252,7 +23252,7 @@
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>4</v>
+        <v>6.04</v>
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
@@ -23261,7 +23261,7 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -23303,7 +23303,7 @@
         </is>
       </c>
       <c r="I151" s="2" t="n">
-        <v>5</v>
+        <v>6.49</v>
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
@@ -23312,7 +23312,7 @@
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -23354,7 +23354,7 @@
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
@@ -23363,7 +23363,7 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -23405,7 +23405,7 @@
         </is>
       </c>
       <c r="I153" s="2" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -23465,7 +23465,7 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -23507,7 +23507,7 @@
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>4.11</v>
+        <v>6.49</v>
       </c>
       <c r="J155" s="4" t="inlineStr">
         <is>
@@ -23516,7 +23516,7 @@
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -23558,7 +23558,7 @@
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>6.49</v>
+        <v>6.11</v>
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
@@ -23571,7 +23571,7 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -23613,7 +23613,7 @@
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>5</v>
+        <v>5.97</v>
       </c>
       <c r="J157" s="4" t="inlineStr">
         <is>
@@ -23626,7 +23626,7 @@
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -23668,7 +23668,7 @@
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>9.1</v>
+        <v>36.97</v>
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
@@ -23677,7 +23677,7 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -23719,7 +23719,7 @@
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>5.9</v>
+        <v>6.85</v>
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
@@ -23728,7 +23728,7 @@
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -23770,7 +23770,7 @@
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>4</v>
+        <v>6.89</v>
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
@@ -23779,7 +23779,7 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -23821,7 +23821,7 @@
         </is>
       </c>
       <c r="I161" s="2" t="n">
-        <v>5</v>
+        <v>6.89</v>
       </c>
       <c r="J161" s="2" t="inlineStr">
         <is>
@@ -23830,7 +23830,7 @@
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -23872,7 +23872,7 @@
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>6</v>
+        <v>4.77</v>
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
@@ -23881,7 +23881,7 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -23923,7 +23923,7 @@
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>4</v>
+        <v>9.08</v>
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
@@ -23932,7 +23932,7 @@
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
@@ -23983,7 +23983,7 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -24025,7 +24025,7 @@
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>11.24</v>
+        <v>213.28</v>
       </c>
       <c r="J165" s="4" t="inlineStr">
         <is>
@@ -24034,7 +24034,7 @@
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -24076,7 +24076,7 @@
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>5.19</v>
+        <v>11.03</v>
       </c>
       <c r="J166" s="4" t="inlineStr">
         <is>
@@ -24085,7 +24085,7 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -24127,7 +24127,7 @@
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>10.24</v>
+        <v>10.56</v>
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
@@ -24136,7 +24136,7 @@
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -24178,7 +24178,7 @@
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>8.01</v>
+        <v>9.23</v>
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
@@ -24187,7 +24187,7 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -24229,7 +24229,7 @@
         </is>
       </c>
       <c r="I169" s="2" t="n">
-        <v>13</v>
+        <v>6.83</v>
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
@@ -24238,7 +24238,7 @@
       </c>
       <c r="K169" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -24280,7 +24280,7 @@
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>8</v>
+        <v>6.05</v>
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
@@ -24289,7 +24289,7 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -24331,7 +24331,7 @@
         </is>
       </c>
       <c r="I171" s="2" t="n">
-        <v>7</v>
+        <v>7.31</v>
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
@@ -24340,7 +24340,7 @@
       </c>
       <c r="K171" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -24382,7 +24382,7 @@
         </is>
       </c>
       <c r="I172" s="2" t="n">
-        <v>5.65</v>
+        <v>5.18</v>
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
@@ -24391,7 +24391,7 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -24433,7 +24433,7 @@
         </is>
       </c>
       <c r="I173" s="2" t="n">
-        <v>8.52</v>
+        <v>7.96</v>
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
@@ -24442,7 +24442,7 @@
       </c>
       <c r="K173" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -24484,7 +24484,7 @@
         </is>
       </c>
       <c r="I174" s="2" t="n">
-        <v>8</v>
+        <v>6.92</v>
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
@@ -24493,7 +24493,7 @@
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -24535,7 +24535,7 @@
         </is>
       </c>
       <c r="I175" s="2" t="n">
-        <v>8</v>
+        <v>8.02</v>
       </c>
       <c r="J175" s="2" t="inlineStr">
         <is>
@@ -24544,7 +24544,7 @@
       </c>
       <c r="K175" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -24586,7 +24586,7 @@
         </is>
       </c>
       <c r="I176" s="2" t="n">
-        <v>8</v>
+        <v>7.15</v>
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
@@ -24595,7 +24595,7 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -24637,7 +24637,7 @@
         </is>
       </c>
       <c r="I177" s="2" t="n">
-        <v>9.16</v>
+        <v>8.6</v>
       </c>
       <c r="J177" s="2" t="inlineStr">
         <is>
@@ -24646,7 +24646,7 @@
       </c>
       <c r="K177" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -24688,7 +24688,7 @@
         </is>
       </c>
       <c r="I178" s="2" t="n">
-        <v>5</v>
+        <v>7.37</v>
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
@@ -24697,7 +24697,7 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -24739,7 +24739,7 @@
         </is>
       </c>
       <c r="I179" s="2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.09</v>
       </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
@@ -24748,7 +24748,7 @@
       </c>
       <c r="K179" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -24790,7 +24790,7 @@
         </is>
       </c>
       <c r="I180" s="2" t="n">
-        <v>4.91</v>
+        <v>6.45</v>
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
@@ -24799,7 +24799,7 @@
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -24841,7 +24841,7 @@
         </is>
       </c>
       <c r="I181" s="2" t="n">
-        <v>4</v>
+        <v>5.59</v>
       </c>
       <c r="J181" s="2" t="inlineStr">
         <is>
@@ -24850,7 +24850,7 @@
       </c>
       <c r="K181" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -24892,7 +24892,7 @@
         </is>
       </c>
       <c r="I182" s="2" t="n">
-        <v>7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
@@ -24901,7 +24901,7 @@
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:12</t>
         </is>
       </c>
     </row>
@@ -24943,7 +24943,7 @@
         </is>
       </c>
       <c r="I183" s="2" t="n">
-        <v>5</v>
+        <v>8.09</v>
       </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
@@ -24952,7 +24952,7 @@
       </c>
       <c r="K183" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -24994,7 +24994,7 @@
         </is>
       </c>
       <c r="I184" s="2" t="n">
-        <v>6</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
@@ -25003,7 +25003,7 @@
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -25045,7 +25045,7 @@
         </is>
       </c>
       <c r="I185" s="2" t="n">
-        <v>6.34</v>
+        <v>11.23</v>
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
@@ -25054,7 +25054,7 @@
       </c>
       <c r="K185" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -25096,7 +25096,7 @@
         </is>
       </c>
       <c r="I186" s="2" t="n">
-        <v>5.66</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
@@ -25105,7 +25105,7 @@
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -25147,7 +25147,7 @@
         </is>
       </c>
       <c r="I187" s="2" t="n">
-        <v>5.2</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="J187" s="2" t="inlineStr">
         <is>
@@ -25156,7 +25156,7 @@
       </c>
       <c r="K187" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -25198,7 +25198,7 @@
         </is>
       </c>
       <c r="I188" s="2" t="n">
-        <v>5.99</v>
+        <v>6.31</v>
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
@@ -25207,7 +25207,7 @@
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -25249,7 +25249,7 @@
         </is>
       </c>
       <c r="I189" s="2" t="n">
-        <v>5.06</v>
+        <v>10.04</v>
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
       </c>
       <c r="K189" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -25300,7 +25300,7 @@
         </is>
       </c>
       <c r="I190" s="2" t="n">
-        <v>3</v>
+        <v>6.12</v>
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
@@ -25309,7 +25309,7 @@
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -25351,7 +25351,7 @@
         </is>
       </c>
       <c r="I191" s="2" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
@@ -25360,7 +25360,7 @@
       </c>
       <c r="K191" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -25402,7 +25402,7 @@
         </is>
       </c>
       <c r="I192" s="2" t="n">
-        <v>5.94</v>
+        <v>7.99</v>
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -25453,7 +25453,7 @@
         </is>
       </c>
       <c r="I193" s="2" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="J193" s="4" t="inlineStr">
         <is>
@@ -25462,7 +25462,7 @@
       </c>
       <c r="K193" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -25504,7 +25504,7 @@
         </is>
       </c>
       <c r="I194" s="2" t="n">
-        <v>5</v>
+        <v>10.44</v>
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
@@ -25517,7 +25517,7 @@
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -25559,7 +25559,7 @@
         </is>
       </c>
       <c r="I195" s="2" t="n">
-        <v>6.02</v>
+        <v>8.35</v>
       </c>
       <c r="J195" s="4" t="inlineStr">
         <is>
@@ -25572,7 +25572,7 @@
       </c>
       <c r="K195" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -25614,7 +25614,7 @@
         </is>
       </c>
       <c r="I196" s="2" t="n">
-        <v>9.050000000000001</v>
+        <v>13.18</v>
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
@@ -25623,7 +25623,7 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -25665,7 +25665,7 @@
         </is>
       </c>
       <c r="I197" s="2" t="n">
-        <v>4.02</v>
+        <v>9.59</v>
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
@@ -25674,7 +25674,7 @@
       </c>
       <c r="K197" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -25716,7 +25716,7 @@
         </is>
       </c>
       <c r="I198" s="2" t="n">
-        <v>5.98</v>
+        <v>5.34</v>
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -25767,7 +25767,7 @@
         </is>
       </c>
       <c r="I199" s="2" t="n">
-        <v>5</v>
+        <v>4.25</v>
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
       </c>
       <c r="K199" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -25818,7 +25818,7 @@
         </is>
       </c>
       <c r="I200" s="2" t="n">
-        <v>4</v>
+        <v>6.61</v>
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
@@ -25827,7 +25827,7 @@
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -25869,7 +25869,7 @@
         </is>
       </c>
       <c r="I201" s="2" t="n">
-        <v>5</v>
+        <v>6.11</v>
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
@@ -25878,7 +25878,7 @@
       </c>
       <c r="K201" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -25920,7 +25920,7 @@
         </is>
       </c>
       <c r="I202" s="2" t="n">
-        <v>5</v>
+        <v>7.85</v>
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
@@ -25929,7 +25929,7 @@
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -25971,7 +25971,7 @@
         </is>
       </c>
       <c r="I203" s="2" t="n">
-        <v>9.82</v>
+        <v>14.88</v>
       </c>
       <c r="J203" s="4" t="inlineStr">
         <is>
@@ -25980,7 +25980,7 @@
       </c>
       <c r="K203" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -26022,7 +26022,7 @@
         </is>
       </c>
       <c r="I204" s="2" t="n">
-        <v>7.03</v>
+        <v>7.52</v>
       </c>
       <c r="J204" s="4" t="inlineStr">
         <is>
@@ -26031,7 +26031,7 @@
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -26073,7 +26073,7 @@
         </is>
       </c>
       <c r="I205" s="2" t="n">
-        <v>8.51</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="J205" s="2" t="inlineStr">
         <is>
@@ -26082,7 +26082,7 @@
       </c>
       <c r="K205" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -26124,7 +26124,7 @@
         </is>
       </c>
       <c r="I206" s="2" t="n">
-        <v>7.56</v>
+        <v>7.49</v>
       </c>
       <c r="J206" s="2" t="inlineStr">
         <is>
@@ -26133,7 +26133,7 @@
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -26175,7 +26175,7 @@
         </is>
       </c>
       <c r="I207" s="2" t="n">
-        <v>7</v>
+        <v>7.56</v>
       </c>
       <c r="J207" s="2" t="inlineStr">
         <is>
@@ -26184,7 +26184,7 @@
       </c>
       <c r="K207" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -26226,7 +26226,7 @@
         </is>
       </c>
       <c r="I208" s="2" t="n">
-        <v>6.06</v>
+        <v>6.08</v>
       </c>
       <c r="J208" s="2" t="inlineStr">
         <is>
@@ -26235,7 +26235,7 @@
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -26277,7 +26277,7 @@
         </is>
       </c>
       <c r="I209" s="2" t="n">
-        <v>7.76</v>
+        <v>6.61</v>
       </c>
       <c r="J209" s="2" t="inlineStr">
         <is>
@@ -26286,7 +26286,7 @@
       </c>
       <c r="K209" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -26328,7 +26328,7 @@
         </is>
       </c>
       <c r="I210" s="2" t="n">
-        <v>5.99</v>
+        <v>5.16</v>
       </c>
       <c r="J210" s="2" t="inlineStr">
         <is>
@@ -26337,7 +26337,7 @@
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -26379,7 +26379,7 @@
         </is>
       </c>
       <c r="I211" s="2" t="n">
-        <v>8</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="J211" s="2" t="inlineStr">
         <is>
@@ -26388,7 +26388,7 @@
       </c>
       <c r="K211" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -26430,7 +26430,7 @@
         </is>
       </c>
       <c r="I212" s="2" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="J212" s="2" t="inlineStr">
         <is>
@@ -26439,7 +26439,7 @@
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -26481,7 +26481,7 @@
         </is>
       </c>
       <c r="I213" s="2" t="n">
-        <v>10.05</v>
+        <v>10.43</v>
       </c>
       <c r="J213" s="2" t="inlineStr">
         <is>
@@ -26490,7 +26490,7 @@
       </c>
       <c r="K213" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -26532,7 +26532,7 @@
         </is>
       </c>
       <c r="I214" s="2" t="n">
-        <v>9.970000000000001</v>
+        <v>8.24</v>
       </c>
       <c r="J214" s="2" t="inlineStr">
         <is>
@@ -26541,7 +26541,7 @@
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -26583,7 +26583,7 @@
         </is>
       </c>
       <c r="I215" s="2" t="n">
-        <v>9.25</v>
+        <v>8.92</v>
       </c>
       <c r="J215" s="2" t="inlineStr">
         <is>
@@ -26592,7 +26592,7 @@
       </c>
       <c r="K215" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
         </is>
       </c>
       <c r="I216" s="2" t="n">
-        <v>10</v>
+        <v>8.15</v>
       </c>
       <c r="J216" s="2" t="inlineStr">
         <is>
@@ -26643,7 +26643,7 @@
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -26685,7 +26685,7 @@
         </is>
       </c>
       <c r="I217" s="2" t="n">
-        <v>8</v>
+        <v>11.37</v>
       </c>
       <c r="J217" s="2" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
       </c>
       <c r="K217" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -26736,7 +26736,7 @@
         </is>
       </c>
       <c r="I218" s="2" t="n">
-        <v>8</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="J218" s="2" t="inlineStr">
         <is>
@@ -26745,7 +26745,7 @@
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -26787,7 +26787,7 @@
         </is>
       </c>
       <c r="I219" s="2" t="n">
-        <v>5.09</v>
+        <v>5.6</v>
       </c>
       <c r="J219" s="2" t="inlineStr">
         <is>
@@ -26796,7 +26796,7 @@
       </c>
       <c r="K219" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -26838,7 +26838,7 @@
         </is>
       </c>
       <c r="I220" s="2" t="n">
-        <v>10</v>
+        <v>7.48</v>
       </c>
       <c r="J220" s="2" t="inlineStr">
         <is>
@@ -26847,7 +26847,7 @@
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -26889,7 +26889,7 @@
         </is>
       </c>
       <c r="I221" s="2" t="n">
-        <v>8.470000000000001</v>
+        <v>8.09</v>
       </c>
       <c r="J221" s="2" t="inlineStr">
         <is>
@@ -26898,7 +26898,7 @@
       </c>
       <c r="K221" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -26940,7 +26940,7 @@
         </is>
       </c>
       <c r="I222" s="2" t="n">
-        <v>9.470000000000001</v>
+        <v>6.63</v>
       </c>
       <c r="J222" s="2" t="inlineStr">
         <is>
@@ -26949,7 +26949,7 @@
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -26991,7 +26991,7 @@
         </is>
       </c>
       <c r="I223" s="2" t="n">
-        <v>7.53</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="J223" s="2" t="inlineStr">
         <is>
@@ -27000,7 +27000,7 @@
       </c>
       <c r="K223" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -27042,7 +27042,7 @@
         </is>
       </c>
       <c r="I224" s="2" t="n">
-        <v>9.119999999999999</v>
+        <v>13.27</v>
       </c>
       <c r="J224" s="2" t="inlineStr">
         <is>
@@ -27051,7 +27051,7 @@
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -27093,7 +27093,7 @@
         </is>
       </c>
       <c r="I225" s="2" t="n">
-        <v>8</v>
+        <v>7.67</v>
       </c>
       <c r="J225" s="2" t="inlineStr">
         <is>
@@ -27102,7 +27102,7 @@
       </c>
       <c r="K225" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -27144,7 +27144,7 @@
         </is>
       </c>
       <c r="I226" s="2" t="n">
-        <v>9.02</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="J226" s="2" t="inlineStr">
         <is>
@@ -27153,7 +27153,7 @@
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -27195,7 +27195,7 @@
         </is>
       </c>
       <c r="I227" s="2" t="n">
-        <v>6.98</v>
+        <v>6.69</v>
       </c>
       <c r="J227" s="2" t="inlineStr">
         <is>
@@ -27204,7 +27204,7 @@
       </c>
       <c r="K227" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -27246,7 +27246,7 @@
         </is>
       </c>
       <c r="I228" s="2" t="n">
-        <v>6.26</v>
+        <v>5.2</v>
       </c>
       <c r="J228" s="2" t="inlineStr">
         <is>
@@ -27255,7 +27255,7 @@
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -27297,7 +27297,7 @@
         </is>
       </c>
       <c r="I229" s="2" t="n">
-        <v>5.49</v>
+        <v>6.28</v>
       </c>
       <c r="J229" s="2" t="inlineStr">
         <is>
@@ -27306,7 +27306,7 @@
       </c>
       <c r="K229" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -27348,7 +27348,7 @@
         </is>
       </c>
       <c r="I230" s="2" t="n">
-        <v>50.58</v>
+        <v>7.55</v>
       </c>
       <c r="J230" s="2" t="inlineStr">
         <is>
@@ -27357,7 +27357,7 @@
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -27399,7 +27399,7 @@
         </is>
       </c>
       <c r="I231" s="2" t="n">
-        <v>18.76</v>
+        <v>9.52</v>
       </c>
       <c r="J231" s="4" t="inlineStr">
         <is>
@@ -27408,7 +27408,7 @@
       </c>
       <c r="K231" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -27450,7 +27450,7 @@
         </is>
       </c>
       <c r="I232" s="2" t="n">
-        <v>9.66</v>
+        <v>6.17</v>
       </c>
       <c r="J232" s="2" t="inlineStr">
         <is>
@@ -27463,7 +27463,7 @@
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:12:59</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -27505,7 +27505,7 @@
         </is>
       </c>
       <c r="I233" s="2" t="n">
-        <v>5</v>
+        <v>10.95</v>
       </c>
       <c r="J233" s="4" t="inlineStr">
         <is>
@@ -27518,7 +27518,7 @@
       </c>
       <c r="K233" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -27560,7 +27560,7 @@
         </is>
       </c>
       <c r="I234" s="2" t="n">
-        <v>37.93</v>
+        <v>15.08</v>
       </c>
       <c r="J234" s="2" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -27611,7 +27611,7 @@
         </is>
       </c>
       <c r="I235" s="2" t="n">
-        <v>8.01</v>
+        <v>10.37</v>
       </c>
       <c r="J235" s="2" t="inlineStr">
         <is>
@@ -27620,7 +27620,7 @@
       </c>
       <c r="K235" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -27662,7 +27662,7 @@
         </is>
       </c>
       <c r="I236" s="2" t="n">
-        <v>6</v>
+        <v>9.01</v>
       </c>
       <c r="J236" s="2" t="inlineStr">
         <is>
@@ -27671,7 +27671,7 @@
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -27713,7 +27713,7 @@
         </is>
       </c>
       <c r="I237" s="2" t="n">
-        <v>7</v>
+        <v>10.94</v>
       </c>
       <c r="J237" s="2" t="inlineStr">
         <is>
@@ -27722,7 +27722,7 @@
       </c>
       <c r="K237" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -27764,7 +27764,7 @@
         </is>
       </c>
       <c r="I238" s="2" t="n">
-        <v>4.07</v>
+        <v>8.68</v>
       </c>
       <c r="J238" s="2" t="inlineStr">
         <is>
@@ -27773,7 +27773,7 @@
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -27815,7 +27815,7 @@
         </is>
       </c>
       <c r="I239" s="2" t="n">
-        <v>5.92</v>
+        <v>13.42</v>
       </c>
       <c r="J239" s="2" t="inlineStr">
         <is>
@@ -27824,7 +27824,7 @@
       </c>
       <c r="K239" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -27866,7 +27866,7 @@
         </is>
       </c>
       <c r="I240" s="2" t="n">
-        <v>6.39</v>
+        <v>12.12</v>
       </c>
       <c r="J240" s="2" t="inlineStr">
         <is>
@@ -27875,7 +27875,7 @@
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -27917,7 +27917,7 @@
         </is>
       </c>
       <c r="I241" s="2" t="n">
-        <v>10.1</v>
+        <v>15.19</v>
       </c>
       <c r="J241" s="4" t="inlineStr">
         <is>
@@ -27926,7 +27926,7 @@
       </c>
       <c r="K241" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -27968,7 +27968,7 @@
         </is>
       </c>
       <c r="I242" s="2" t="n">
-        <v>7.61</v>
+        <v>6.52</v>
       </c>
       <c r="J242" s="4" t="inlineStr">
         <is>
@@ -27977,7 +27977,7 @@
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -28019,7 +28019,7 @@
         </is>
       </c>
       <c r="I243" s="2" t="n">
-        <v>13.58</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J243" s="2" t="inlineStr">
         <is>
@@ -28028,7 +28028,7 @@
       </c>
       <c r="K243" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -28070,7 +28070,7 @@
         </is>
       </c>
       <c r="I244" s="2" t="n">
-        <v>12.31</v>
+        <v>6.12</v>
       </c>
       <c r="J244" s="2" t="inlineStr">
         <is>
@@ -28079,7 +28079,7 @@
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -28121,7 +28121,7 @@
         </is>
       </c>
       <c r="I245" s="2" t="n">
-        <v>11.93</v>
+        <v>5.74</v>
       </c>
       <c r="J245" s="2" t="inlineStr">
         <is>
@@ -28130,7 +28130,7 @@
       </c>
       <c r="K245" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -28172,7 +28172,7 @@
         </is>
       </c>
       <c r="I246" s="2" t="n">
-        <v>5</v>
+        <v>4.84</v>
       </c>
       <c r="J246" s="2" t="inlineStr">
         <is>
@@ -28181,7 +28181,7 @@
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -28223,7 +28223,7 @@
         </is>
       </c>
       <c r="I247" s="2" t="n">
-        <v>12</v>
+        <v>7.5</v>
       </c>
       <c r="J247" s="2" t="inlineStr">
         <is>
@@ -28232,7 +28232,7 @@
       </c>
       <c r="K247" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -28274,7 +28274,7 @@
         </is>
       </c>
       <c r="I248" s="2" t="n">
-        <v>9</v>
+        <v>4.18</v>
       </c>
       <c r="J248" s="2" t="inlineStr">
         <is>
@@ -28283,7 +28283,7 @@
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -28325,7 +28325,7 @@
         </is>
       </c>
       <c r="I249" s="2" t="n">
-        <v>12.53</v>
+        <v>6.95</v>
       </c>
       <c r="J249" s="2" t="inlineStr">
         <is>
@@ -28334,7 +28334,7 @@
       </c>
       <c r="K249" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -28376,7 +28376,7 @@
         </is>
       </c>
       <c r="I250" s="2" t="n">
-        <v>11.53</v>
+        <v>6.17</v>
       </c>
       <c r="J250" s="2" t="inlineStr">
         <is>
@@ -28385,7 +28385,7 @@
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -28427,7 +28427,7 @@
         </is>
       </c>
       <c r="I251" s="2" t="n">
-        <v>11.01</v>
+        <v>7.23</v>
       </c>
       <c r="J251" s="2" t="inlineStr">
         <is>
@@ -28436,7 +28436,7 @@
       </c>
       <c r="K251" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -28478,7 +28478,7 @@
         </is>
       </c>
       <c r="I252" s="2" t="n">
-        <v>5.99</v>
+        <v>5.7</v>
       </c>
       <c r="J252" s="2" t="inlineStr">
         <is>
@@ -28487,7 +28487,7 @@
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -28529,7 +28529,7 @@
         </is>
       </c>
       <c r="I253" s="2" t="n">
-        <v>9</v>
+        <v>5.93</v>
       </c>
       <c r="J253" s="2" t="inlineStr">
         <is>
@@ -28538,7 +28538,7 @@
       </c>
       <c r="K253" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -28580,7 +28580,7 @@
         </is>
       </c>
       <c r="I254" s="2" t="n">
-        <v>6.09</v>
+        <v>6.46</v>
       </c>
       <c r="J254" s="2" t="inlineStr">
         <is>
@@ -28589,7 +28589,7 @@
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -28631,7 +28631,7 @@
         </is>
       </c>
       <c r="I255" s="2" t="n">
-        <v>5</v>
+        <v>5.74</v>
       </c>
       <c r="J255" s="2" t="inlineStr">
         <is>
@@ -28640,7 +28640,7 @@
       </c>
       <c r="K255" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -28682,7 +28682,7 @@
         </is>
       </c>
       <c r="I256" s="2" t="n">
-        <v>8</v>
+        <v>4.69</v>
       </c>
       <c r="J256" s="2" t="inlineStr">
         <is>
@@ -28691,7 +28691,7 @@
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -28733,7 +28733,7 @@
         </is>
       </c>
       <c r="I257" s="2" t="n">
-        <v>4</v>
+        <v>4.46</v>
       </c>
       <c r="J257" s="2" t="inlineStr">
         <is>
@@ -28742,7 +28742,7 @@
       </c>
       <c r="K257" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -28784,7 +28784,7 @@
         </is>
       </c>
       <c r="I258" s="2" t="n">
-        <v>5</v>
+        <v>6.23</v>
       </c>
       <c r="J258" s="2" t="inlineStr">
         <is>
@@ -28793,7 +28793,7 @@
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -28835,7 +28835,7 @@
         </is>
       </c>
       <c r="I259" s="2" t="n">
-        <v>7</v>
+        <v>11.69</v>
       </c>
       <c r="J259" s="2" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
       </c>
       <c r="K259" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -28886,7 +28886,7 @@
         </is>
       </c>
       <c r="I260" s="2" t="n">
-        <v>6</v>
+        <v>11.68</v>
       </c>
       <c r="J260" s="2" t="inlineStr">
         <is>
@@ -28895,7 +28895,7 @@
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -28937,7 +28937,7 @@
         </is>
       </c>
       <c r="I261" s="2" t="n">
-        <v>6</v>
+        <v>12.52</v>
       </c>
       <c r="J261" s="2" t="inlineStr">
         <is>
@@ -28946,7 +28946,7 @@
       </c>
       <c r="K261" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -28988,7 +28988,7 @@
         </is>
       </c>
       <c r="I262" s="2" t="n">
-        <v>7.07</v>
+        <v>13.35</v>
       </c>
       <c r="J262" s="2" t="inlineStr">
         <is>
@@ -28997,7 +28997,7 @@
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -29039,7 +29039,7 @@
         </is>
       </c>
       <c r="I263" s="2" t="n">
-        <v>5.93</v>
+        <v>13.48</v>
       </c>
       <c r="J263" s="2" t="inlineStr">
         <is>
@@ -29048,7 +29048,7 @@
       </c>
       <c r="K263" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -29090,7 +29090,7 @@
         </is>
       </c>
       <c r="I264" s="2" t="n">
-        <v>7.55</v>
+        <v>12.37</v>
       </c>
       <c r="J264" s="2" t="inlineStr">
         <is>
@@ -29099,7 +29099,7 @@
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -29141,7 +29141,7 @@
         </is>
       </c>
       <c r="I265" s="2" t="n">
-        <v>4.45</v>
+        <v>9.99</v>
       </c>
       <c r="J265" s="2" t="inlineStr">
         <is>
@@ -29150,7 +29150,7 @@
       </c>
       <c r="K265" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -29192,7 +29192,7 @@
         </is>
       </c>
       <c r="I266" s="2" t="n">
-        <v>4.13</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="J266" s="2" t="inlineStr">
         <is>
@@ -29201,7 +29201,7 @@
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -29243,7 +29243,7 @@
         </is>
       </c>
       <c r="I267" s="2" t="n">
-        <v>3</v>
+        <v>7.01</v>
       </c>
       <c r="J267" s="2" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
       </c>
       <c r="K267" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
         </is>
       </c>
       <c r="I268" s="2" t="n">
-        <v>7.03</v>
+        <v>10.87</v>
       </c>
       <c r="J268" s="2" t="inlineStr">
         <is>
@@ -29303,7 +29303,7 @@
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -29345,7 +29345,7 @@
         </is>
       </c>
       <c r="I269" s="2" t="n">
-        <v>4.97</v>
+        <v>10.61</v>
       </c>
       <c r="J269" s="4" t="inlineStr">
         <is>
@@ -29354,7 +29354,7 @@
       </c>
       <c r="K269" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -29396,7 +29396,7 @@
         </is>
       </c>
       <c r="I270" s="2" t="n">
-        <v>5</v>
+        <v>11.68</v>
       </c>
       <c r="J270" s="2" t="inlineStr">
         <is>
@@ -29409,7 +29409,7 @@
       </c>
       <c r="K270" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -29451,7 +29451,7 @@
         </is>
       </c>
       <c r="I271" s="2" t="n">
-        <v>6.24</v>
+        <v>12.09</v>
       </c>
       <c r="J271" s="4" t="inlineStr">
         <is>
@@ -29464,7 +29464,7 @@
       </c>
       <c r="K271" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -29506,7 +29506,7 @@
         </is>
       </c>
       <c r="I272" s="2" t="n">
-        <v>9.949999999999999</v>
+        <v>21.29</v>
       </c>
       <c r="J272" s="2" t="inlineStr">
         <is>
@@ -29515,7 +29515,7 @@
       </c>
       <c r="K272" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -29557,7 +29557,7 @@
         </is>
       </c>
       <c r="I273" s="2" t="n">
-        <v>6</v>
+        <v>11.94</v>
       </c>
       <c r="J273" s="2" t="inlineStr">
         <is>
@@ -29566,7 +29566,7 @@
       </c>
       <c r="K273" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -29608,7 +29608,7 @@
         </is>
       </c>
       <c r="I274" s="2" t="n">
-        <v>4.82</v>
+        <v>10.5</v>
       </c>
       <c r="J274" s="2" t="inlineStr">
         <is>
@@ -29617,7 +29617,7 @@
       </c>
       <c r="K274" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -29659,7 +29659,7 @@
         </is>
       </c>
       <c r="I275" s="2" t="n">
-        <v>5</v>
+        <v>10.27</v>
       </c>
       <c r="J275" s="2" t="inlineStr">
         <is>
@@ -29668,7 +29668,7 @@
       </c>
       <c r="K275" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -29710,7 +29710,7 @@
         </is>
       </c>
       <c r="I276" s="2" t="n">
-        <v>5.31</v>
+        <v>11.68</v>
       </c>
       <c r="J276" s="2" t="inlineStr">
         <is>
@@ -29719,7 +29719,7 @@
       </c>
       <c r="K276" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -29761,7 +29761,7 @@
         </is>
       </c>
       <c r="I277" s="2" t="n">
-        <v>5</v>
+        <v>15.07</v>
       </c>
       <c r="J277" s="2" t="inlineStr">
         <is>
@@ -29770,7 +29770,7 @@
       </c>
       <c r="K277" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -29812,7 +29812,7 @@
         </is>
       </c>
       <c r="I278" s="2" t="n">
-        <v>5</v>
+        <v>9.32</v>
       </c>
       <c r="J278" s="2" t="inlineStr">
         <is>
@@ -29821,7 +29821,7 @@
       </c>
       <c r="K278" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -29863,7 +29863,7 @@
         </is>
       </c>
       <c r="I279" s="2" t="n">
-        <v>27.91</v>
+        <v>23.82</v>
       </c>
       <c r="J279" s="4" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
       </c>
       <c r="K279" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -29914,7 +29914,7 @@
         </is>
       </c>
       <c r="I280" s="2" t="n">
-        <v>11.19</v>
+        <v>9.59</v>
       </c>
       <c r="J280" s="4" t="inlineStr">
         <is>
@@ -29923,7 +29923,7 @@
       </c>
       <c r="K280" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -29965,7 +29965,7 @@
         </is>
       </c>
       <c r="I281" s="2" t="n">
-        <v>9.67</v>
+        <v>12.12</v>
       </c>
       <c r="J281" s="2" t="inlineStr">
         <is>
@@ -29974,7 +29974,7 @@
       </c>
       <c r="K281" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -30016,7 +30016,7 @@
         </is>
       </c>
       <c r="I282" s="2" t="n">
-        <v>8.43</v>
+        <v>8.98</v>
       </c>
       <c r="J282" s="2" t="inlineStr">
         <is>
@@ -30025,7 +30025,7 @@
       </c>
       <c r="K282" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -30067,7 +30067,7 @@
         </is>
       </c>
       <c r="I283" s="2" t="n">
-        <v>5.58</v>
+        <v>6.14</v>
       </c>
       <c r="J283" s="2" t="inlineStr">
         <is>
@@ -30076,7 +30076,7 @@
       </c>
       <c r="K283" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -30118,7 +30118,7 @@
         </is>
       </c>
       <c r="I284" s="2" t="n">
-        <v>5</v>
+        <v>4.68</v>
       </c>
       <c r="J284" s="2" t="inlineStr">
         <is>
@@ -30127,7 +30127,7 @@
       </c>
       <c r="K284" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -30169,7 +30169,7 @@
         </is>
       </c>
       <c r="I285" s="2" t="n">
-        <v>8.16</v>
+        <v>8.56</v>
       </c>
       <c r="J285" s="2" t="inlineStr">
         <is>
@@ -30178,7 +30178,7 @@
       </c>
       <c r="K285" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -30220,7 +30220,7 @@
         </is>
       </c>
       <c r="I286" s="2" t="n">
-        <v>4.95</v>
+        <v>4.36</v>
       </c>
       <c r="J286" s="2" t="inlineStr">
         <is>
@@ -30229,7 +30229,7 @@
       </c>
       <c r="K286" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -30271,7 +30271,7 @@
         </is>
       </c>
       <c r="I287" s="2" t="n">
-        <v>9</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="J287" s="2" t="inlineStr">
         <is>
@@ -30280,7 +30280,7 @@
       </c>
       <c r="K287" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -30322,7 +30322,7 @@
         </is>
       </c>
       <c r="I288" s="2" t="n">
-        <v>7</v>
+        <v>5.95</v>
       </c>
       <c r="J288" s="2" t="inlineStr">
         <is>
@@ -30331,7 +30331,7 @@
       </c>
       <c r="K288" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -30373,7 +30373,7 @@
         </is>
       </c>
       <c r="I289" s="2" t="n">
-        <v>10.32</v>
+        <v>7</v>
       </c>
       <c r="J289" s="2" t="inlineStr">
         <is>
@@ -30382,7 +30382,7 @@
       </c>
       <c r="K289" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -30424,7 +30424,7 @@
         </is>
       </c>
       <c r="I290" s="2" t="n">
-        <v>5.91</v>
+        <v>7.37</v>
       </c>
       <c r="J290" s="2" t="inlineStr">
         <is>
@@ -30433,7 +30433,7 @@
       </c>
       <c r="K290" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -30475,7 +30475,7 @@
         </is>
       </c>
       <c r="I291" s="2" t="n">
-        <v>9.109999999999999</v>
+        <v>7.56</v>
       </c>
       <c r="J291" s="2" t="inlineStr">
         <is>
@@ -30484,7 +30484,7 @@
       </c>
       <c r="K291" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -30526,7 +30526,7 @@
         </is>
       </c>
       <c r="I292" s="2" t="n">
-        <v>6.99</v>
+        <v>7.59</v>
       </c>
       <c r="J292" s="2" t="inlineStr">
         <is>
@@ -30535,7 +30535,7 @@
       </c>
       <c r="K292" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -30577,7 +30577,7 @@
         </is>
       </c>
       <c r="I293" s="2" t="n">
-        <v>10</v>
+        <v>7.15</v>
       </c>
       <c r="J293" s="2" t="inlineStr">
         <is>
@@ -30586,7 +30586,7 @@
       </c>
       <c r="K293" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -30628,7 +30628,7 @@
         </is>
       </c>
       <c r="I294" s="2" t="n">
-        <v>5</v>
+        <v>4.67</v>
       </c>
       <c r="J294" s="2" t="inlineStr">
         <is>
@@ -30637,7 +30637,7 @@
       </c>
       <c r="K294" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -30679,7 +30679,7 @@
         </is>
       </c>
       <c r="I295" s="2" t="n">
-        <v>4.43</v>
+        <v>4.53</v>
       </c>
       <c r="J295" s="2" t="inlineStr">
         <is>
@@ -30688,7 +30688,7 @@
       </c>
       <c r="K295" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:13</t>
         </is>
       </c>
     </row>
@@ -30730,7 +30730,7 @@
         </is>
       </c>
       <c r="I296" s="2" t="n">
-        <v>7</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="J296" s="2" t="inlineStr">
         <is>
@@ -30739,7 +30739,7 @@
       </c>
       <c r="K296" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:14</t>
         </is>
       </c>
     </row>
@@ -30781,7 +30781,7 @@
         </is>
       </c>
       <c r="I297" s="2" t="n">
-        <v>6.12</v>
+        <v>10.6</v>
       </c>
       <c r="J297" s="2" t="inlineStr">
         <is>
@@ -30790,7 +30790,7 @@
       </c>
       <c r="K297" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:14</t>
         </is>
       </c>
     </row>
@@ -30832,7 +30832,7 @@
         </is>
       </c>
       <c r="I298" s="2" t="n">
-        <v>7.17</v>
+        <v>11.64</v>
       </c>
       <c r="J298" s="2" t="inlineStr">
         <is>
@@ -30841,7 +30841,7 @@
       </c>
       <c r="K298" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:14</t>
         </is>
       </c>
     </row>
@@ -30883,7 +30883,7 @@
         </is>
       </c>
       <c r="I299" s="2" t="n">
-        <v>7</v>
+        <v>9.68</v>
       </c>
       <c r="J299" s="2" t="inlineStr">
         <is>
@@ -30892,7 +30892,7 @@
       </c>
       <c r="K299" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:14</t>
         </is>
       </c>
     </row>
@@ -30934,7 +30934,7 @@
         </is>
       </c>
       <c r="I300" s="2" t="n">
-        <v>6.08</v>
+        <v>13.08</v>
       </c>
       <c r="J300" s="2" t="inlineStr">
         <is>
@@ -30943,7 +30943,7 @@
       </c>
       <c r="K300" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:14</t>
         </is>
       </c>
     </row>
@@ -30985,7 +30985,7 @@
         </is>
       </c>
       <c r="I301" s="2" t="n">
-        <v>7.24</v>
+        <v>11.95</v>
       </c>
       <c r="J301" s="2" t="inlineStr">
         <is>
@@ -30994,7 +30994,7 @@
       </c>
       <c r="K301" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:00</t>
+          <t>2026-08-10 11:44:14</t>
         </is>
       </c>
     </row>
@@ -31112,7 +31112,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>244.39 req/s</t>
+          <t>229.40 req/s</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -31134,7 +31134,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>39.63 ms</t>
+          <t>42.69 ms</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -31156,7 +31156,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>18 ms / 57 ms</t>
+          <t>12 ms / 82 ms</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -31178,7 +31178,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>40 ms</t>
+          <t>41 ms</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -31200,7 +31200,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>43 ms</t>
+          <t>54 ms</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -31222,7 +31222,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>46 ms</t>
+          <t>74 ms</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -31362,7 +31362,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:02</t>
+          <t>2026-08-10 11:44:16</t>
         </is>
       </c>
     </row>
@@ -31414,7 +31414,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:02</t>
+          <t>2026-08-10 11:44:16</t>
         </is>
       </c>
     </row>
@@ -31466,7 +31466,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:02</t>
+          <t>2026-08-10 11:44:16</t>
         </is>
       </c>
     </row>
@@ -31518,7 +31518,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:02</t>
+          <t>2026-08-10 11:44:16</t>
         </is>
       </c>
     </row>
@@ -31570,7 +31570,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:02</t>
+          <t>2026-08-10 11:44:16</t>
         </is>
       </c>
     </row>
@@ -31622,7 +31622,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:02</t>
+          <t>2026-08-10 11:44:16</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:02</t>
+          <t>2026-08-10 11:44:16</t>
         </is>
       </c>
     </row>
@@ -31726,7 +31726,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:02</t>
+          <t>2026-08-10 11:44:16</t>
         </is>
       </c>
     </row>
@@ -31778,7 +31778,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:02</t>
+          <t>2026-08-10 11:44:16</t>
         </is>
       </c>
     </row>
@@ -31830,7 +31830,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:02</t>
+          <t>2026-08-10 11:44:16</t>
         </is>
       </c>
     </row>
@@ -31882,7 +31882,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:02</t>
+          <t>2026-08-10 11:44:16</t>
         </is>
       </c>
     </row>
@@ -31934,7 +31934,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:02</t>
+          <t>2026-08-10 11:44:16</t>
         </is>
       </c>
     </row>
@@ -31986,7 +31986,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:02</t>
+          <t>2026-08-10 11:44:16</t>
         </is>
       </c>
     </row>
@@ -32038,7 +32038,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:02</t>
+          <t>2026-08-10 11:44:16</t>
         </is>
       </c>
     </row>
@@ -32090,7 +32090,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:13:02</t>
+          <t>2026-08-10 11:44:16</t>
         </is>
       </c>
     </row>
@@ -32113,7 +32113,7 @@
     <col width="48" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="39" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -32206,7 +32206,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>RPS: 48.36 req/s</t>
+          <t>RPS: 39.62 req/s</t>
         </is>
       </c>
     </row>
@@ -32283,7 +32283,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>102.25 ms</t>
+          <t>125.98 ms</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -32315,7 +32315,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15.77 ms</t>
+          <t>18.8 ms</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -32347,7 +32347,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>454.04 ms</t>
+          <t>48.69 ms</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -32379,7 +32379,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2074.05 ms</t>
+          <t>2565.91 ms</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -32411,7 +32411,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2300.42 ms</t>
+          <t>3051.21 ms</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -32443,7 +32443,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>48.01%</t>
+          <t>63.65%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -32475,7 +32475,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>58.39 MB</t>
+          <t>59.18 MB</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -32490,7 +32490,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Max RAM: 58.4 MB (+0.59 MB growth)</t>
+          <t>Max RAM: 59.19 MB (+0.54 MB growth)</t>
         </is>
       </c>
     </row>
@@ -32522,7 +32522,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Ping: 3.07 ms (mysql)</t>
+          <t>Ping: 1.9 ms (mysql)</t>
         </is>
       </c>
     </row>
@@ -32571,12 +32571,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Avg 15.84 ms (Min 6.0 / Max 30.59 ms)</t>
+          <t>Avg 16.94 ms (Min 8.12 / Max 35.88 ms)</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 1.93 req/s</t>
+          <t>15 reqs, 1.58 req/s</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -32603,12 +32603,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Avg 11.14 ms (Min 7.0 / Max 17.1 ms)</t>
+          <t>Avg 14.19 ms (Min 8.97 / Max 49.99 ms)</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 1.93 req/s</t>
+          <t>15 reqs, 1.58 req/s</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -32635,12 +32635,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Avg 11.87 ms (Min 10.0 / Max 14.14 ms)</t>
+          <t>Avg 13.24 ms (Min 9.26 / Max 18.35 ms)</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 1.93 req/s</t>
+          <t>15 reqs, 1.58 req/s</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -32667,12 +32667,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Avg 29.78 ms (Min 23.03 / Max 46.14 ms)</t>
+          <t>Avg 28.79 ms (Min 15.34 / Max 85.2 ms)</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 1.93 req/s</t>
+          <t>15 reqs, 1.58 req/s</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -32699,12 +32699,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Avg 32.75 ms (Min 13.05 / Max 143.89 ms)</t>
+          <t>Avg 25.15 ms (Min 10.77 / Max 45.68 ms)</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>45 reqs, 5.8 req/s</t>
+          <t>45 reqs, 4.75 req/s</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -32731,12 +32731,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Avg 9.82 ms (Min 8.0 / Max 12.16 ms)</t>
+          <t>Avg 13.26 ms (Min 9.71 / Max 17.5 ms)</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 1.93 req/s</t>
+          <t>15 reqs, 1.58 req/s</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -32763,12 +32763,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Avg 19.61 ms (Min 11.99 / Max 29.58 ms)</t>
+          <t>Avg 21.11 ms (Min 10.34 / Max 29.17 ms)</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 1.93 req/s</t>
+          <t>15 reqs, 1.58 req/s</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -32795,12 +32795,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Avg 24.73 ms (Min 15.59 / Max 43.99 ms)</t>
+          <t>Avg 21.44 ms (Min 17.06 / Max 36.19 ms)</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 1.93 req/s</t>
+          <t>15 reqs, 1.58 req/s</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -32827,12 +32827,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Avg 38.14 ms (Min 14.0 / Max 89.65 ms)</t>
+          <t>Avg 17.36 ms (Min 13.01 / Max 21.94 ms)</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 1.93 req/s</t>
+          <t>15 reqs, 1.58 req/s</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -32859,12 +32859,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Avg 26.43 ms (Min 16.07 / Max 55.98 ms)</t>
+          <t>Avg 18.28 ms (Min 10.66 / Max 22.9 ms)</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 1.93 req/s</t>
+          <t>15 reqs, 1.58 req/s</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -32891,12 +32891,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Avg 22.2 ms (Min 11.8 / Max 32.47 ms)</t>
+          <t>Avg 17.2 ms (Min 12.79 / Max 21.07 ms)</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 1.93 req/s</t>
+          <t>15 reqs, 1.58 req/s</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -32923,12 +32923,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Avg 15.89 ms (Min 12.0 / Max 21.39 ms)</t>
+          <t>Avg 17.73 ms (Min 14.09 / Max 21.04 ms)</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 1.93 req/s</t>
+          <t>15 reqs, 1.58 req/s</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -32955,12 +32955,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Avg 14.83 ms (Min 12.79 / Max 18.12 ms)</t>
+          <t>Avg 17.81 ms (Min 13.2 / Max 24.43 ms)</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 1.93 req/s</t>
+          <t>15 reqs, 1.58 req/s</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -32987,12 +32987,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Avg 14.51 ms (Min 11.93 / Max 18.22 ms)</t>
+          <t>Avg 17.52 ms (Min 11.67 / Max 21.7 ms)</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 1.93 req/s</t>
+          <t>15 reqs, 1.58 req/s</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -33019,12 +33019,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Avg 14.86 ms (Min 11.55 / Max 18.36 ms)</t>
+          <t>Avg 20.84 ms (Min 12.17 / Max 32.9 ms)</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 1.93 req/s</t>
+          <t>15 reqs, 1.58 req/s</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -33051,12 +33051,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Avg 14.59 ms (Min 10.95 / Max 18.03 ms)</t>
+          <t>Avg 18.06 ms (Min 13.46 / Max 22.54 ms)</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 1.93 req/s</t>
+          <t>15 reqs, 1.58 req/s</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -33083,12 +33083,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Avg 14.36 ms (Min 10.2 / Max 19.0 ms)</t>
+          <t>Avg 18.38 ms (Min 14.87 / Max 23.1 ms)</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 1.93 req/s</t>
+          <t>15 reqs, 1.58 req/s</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -33115,12 +33115,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Avg 14.86 ms (Min 11.0 / Max 20.4 ms)</t>
+          <t>Avg 20.84 ms (Min 11.63 / Max 25.94 ms)</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 1.93 req/s</t>
+          <t>15 reqs, 1.58 req/s</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -33147,12 +33147,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Avg 14.64 ms (Min 10.92 / Max 18.48 ms)</t>
+          <t>Avg 18.04 ms (Min 15.42 / Max 22.04 ms)</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 1.93 req/s</t>
+          <t>15 reqs, 1.58 req/s</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -33179,12 +33179,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Avg 11.15 ms (Min 6.0 / Max 14.62 ms)</t>
+          <t>Avg 13.66 ms (Min 10.0 / Max 21.71 ms)</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 1.93 req/s</t>
+          <t>15 reqs, 1.58 req/s</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -33211,12 +33211,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Avg 68.25 ms (Min 10.77 / Max 841.83 ms)</t>
+          <t>Avg 57.93 ms (Min 13.8 / Max 554.2 ms)</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 1.93 req/s</t>
+          <t>15 reqs, 1.58 req/s</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -33243,12 +33243,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Avg 1817.62 ms (Min 931.21 / Max 2300.42 ms)</t>
+          <t>Avg 2481.1 ms (Min 1027.71 / Max 3051.21 ms)</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 1.93 req/s</t>
+          <t>15 reqs, 1.58 req/s</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -33275,12 +33275,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Avg 232.93 ms (Min 9.0 / Max 1547.12 ms)</t>
+          <t>Avg 190.35 ms (Min 22.06 / Max 2405.45 ms)</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 1.93 req/s</t>
+          <t>15 reqs, 1.58 req/s</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">

--- a/SpectraGuard_Test_Report.xlsx
+++ b/SpectraGuard_Test_Report.xlsx
@@ -591,7 +591,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -5341,7 +5341,7 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
@@ -6291,7 +6291,7 @@
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J117" s="2" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J121" s="2" t="inlineStr">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J125" s="2" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J127" s="2" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J129" s="2" t="inlineStr">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J131" s="2" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J133" s="2" t="inlineStr">
@@ -7191,7 +7191,7 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J135" s="2" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J137" s="2" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
@@ -7441,7 +7441,7 @@
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J139" s="2" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J141" s="2" t="inlineStr">
@@ -7591,7 +7591,7 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
@@ -7641,7 +7641,7 @@
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J143" s="2" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J145" s="2" t="inlineStr">
@@ -7791,7 +7791,7 @@
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J147" s="2" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
@@ -7941,7 +7941,7 @@
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J149" s="2" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J151" s="2" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J152" s="2" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J153" s="2" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J154" s="2" t="inlineStr">
@@ -8241,7 +8241,7 @@
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J155" s="2" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
@@ -8341,7 +8341,7 @@
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J157" s="2" t="inlineStr">
@@ -8391,7 +8391,7 @@
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J159" s="2" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J160" s="2" t="inlineStr">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J161" s="2" t="inlineStr">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr">
@@ -8641,7 +8641,7 @@
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J163" s="2" t="inlineStr">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J164" s="2" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J165" s="2" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J166" s="2" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J167" s="2" t="inlineStr">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J168" s="2" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J169" s="2" t="inlineStr">
@@ -8991,7 +8991,7 @@
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J170" s="2" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J171" s="2" t="inlineStr">
@@ -9091,7 +9091,7 @@
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">
@@ -9141,7 +9141,7 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J173" s="2" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J174" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J175" s="2" t="inlineStr">
@@ -9291,7 +9291,7 @@
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J176" s="2" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J177" s="2" t="inlineStr">
@@ -9391,7 +9391,7 @@
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J178" s="2" t="inlineStr">
@@ -9441,7 +9441,7 @@
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J179" s="2" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J180" s="2" t="inlineStr">
@@ -9541,7 +9541,7 @@
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J181" s="2" t="inlineStr">
@@ -9591,7 +9591,7 @@
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J182" s="2" t="inlineStr">
@@ -9641,7 +9641,7 @@
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J183" s="2" t="inlineStr">
@@ -9691,7 +9691,7 @@
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J184" s="2" t="inlineStr">
@@ -9741,7 +9741,7 @@
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J185" s="2" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J186" s="2" t="inlineStr">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J187" s="2" t="inlineStr">
@@ -9891,7 +9891,7 @@
       </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J188" s="2" t="inlineStr">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J189" s="2" t="inlineStr">
@@ -9991,7 +9991,7 @@
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J190" s="2" t="inlineStr">
@@ -10041,7 +10041,7 @@
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J191" s="2" t="inlineStr">
@@ -10091,7 +10091,7 @@
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J192" s="2" t="inlineStr">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J193" s="2" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J194" s="2" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J195" s="2" t="inlineStr">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J196" s="2" t="inlineStr">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J197" s="2" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J198" s="2" t="inlineStr">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J199" s="2" t="inlineStr">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J200" s="2" t="inlineStr">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J201" s="2" t="inlineStr">
@@ -10591,7 +10591,7 @@
       </c>
       <c r="I202" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J202" s="2" t="inlineStr">
@@ -10641,7 +10641,7 @@
       </c>
       <c r="I203" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J203" s="2" t="inlineStr">
@@ -10691,7 +10691,7 @@
       </c>
       <c r="I204" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J204" s="2" t="inlineStr">
@@ -10741,7 +10741,7 @@
       </c>
       <c r="I205" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J205" s="2" t="inlineStr">
@@ -10791,7 +10791,7 @@
       </c>
       <c r="I206" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J206" s="2" t="inlineStr">
@@ -10841,7 +10841,7 @@
       </c>
       <c r="I207" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J207" s="2" t="inlineStr">
@@ -10891,7 +10891,7 @@
       </c>
       <c r="I208" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J208" s="2" t="inlineStr">
@@ -10941,7 +10941,7 @@
       </c>
       <c r="I209" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J209" s="2" t="inlineStr">
@@ -10991,7 +10991,7 @@
       </c>
       <c r="I210" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J210" s="2" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="I211" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J211" s="2" t="inlineStr">
@@ -11091,7 +11091,7 @@
       </c>
       <c r="I212" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J212" s="2" t="inlineStr">
@@ -11141,7 +11141,7 @@
       </c>
       <c r="I213" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J213" s="2" t="inlineStr">
@@ -11191,7 +11191,7 @@
       </c>
       <c r="I214" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J214" s="2" t="inlineStr">
@@ -11241,7 +11241,7 @@
       </c>
       <c r="I215" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J215" s="2" t="inlineStr">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="I216" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J216" s="2" t="inlineStr">
@@ -11341,7 +11341,7 @@
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J217" s="2" t="inlineStr">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="I218" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J218" s="2" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="I219" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J219" s="2" t="inlineStr">
@@ -11491,7 +11491,7 @@
       </c>
       <c r="I220" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J220" s="2" t="inlineStr">
@@ -11541,7 +11541,7 @@
       </c>
       <c r="I221" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J221" s="2" t="inlineStr">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="I222" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J222" s="2" t="inlineStr">
@@ -11641,7 +11641,7 @@
       </c>
       <c r="I223" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J223" s="2" t="inlineStr">
@@ -11691,7 +11691,7 @@
       </c>
       <c r="I224" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J224" s="2" t="inlineStr">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="I225" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J225" s="2" t="inlineStr">
@@ -11791,7 +11791,7 @@
       </c>
       <c r="I226" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J226" s="2" t="inlineStr">
@@ -11841,7 +11841,7 @@
       </c>
       <c r="I227" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J227" s="2" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="I228" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J228" s="2" t="inlineStr">
@@ -11941,7 +11941,7 @@
       </c>
       <c r="I229" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J229" s="2" t="inlineStr">
@@ -11991,7 +11991,7 @@
       </c>
       <c r="I230" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J230" s="2" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="I231" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J231" s="2" t="inlineStr">
@@ -12091,7 +12091,7 @@
       </c>
       <c r="I232" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J232" s="2" t="inlineStr">
@@ -12141,7 +12141,7 @@
       </c>
       <c r="I233" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J233" s="2" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="I234" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J234" s="2" t="inlineStr">
@@ -12241,7 +12241,7 @@
       </c>
       <c r="I235" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J235" s="2" t="inlineStr">
@@ -12291,7 +12291,7 @@
       </c>
       <c r="I236" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J236" s="2" t="inlineStr">
@@ -12341,7 +12341,7 @@
       </c>
       <c r="I237" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J237" s="2" t="inlineStr">
@@ -12391,7 +12391,7 @@
       </c>
       <c r="I238" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J238" s="2" t="inlineStr">
@@ -12441,7 +12441,7 @@
       </c>
       <c r="I239" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J239" s="2" t="inlineStr">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="I240" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J240" s="2" t="inlineStr">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="I241" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J241" s="2" t="inlineStr">
@@ -12591,7 +12591,7 @@
       </c>
       <c r="I242" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J242" s="2" t="inlineStr">
@@ -12641,7 +12641,7 @@
       </c>
       <c r="I243" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J243" s="2" t="inlineStr">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="I244" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J244" s="2" t="inlineStr">
@@ -12741,7 +12741,7 @@
       </c>
       <c r="I245" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J245" s="2" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="I246" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J246" s="2" t="inlineStr">
@@ -12841,7 +12841,7 @@
       </c>
       <c r="I247" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J247" s="2" t="inlineStr">
@@ -12891,7 +12891,7 @@
       </c>
       <c r="I248" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J248" s="2" t="inlineStr">
@@ -12941,7 +12941,7 @@
       </c>
       <c r="I249" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J249" s="2" t="inlineStr">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="I250" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J250" s="2" t="inlineStr">
@@ -13041,7 +13041,7 @@
       </c>
       <c r="I251" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J251" s="2" t="inlineStr">
@@ -13091,7 +13091,7 @@
       </c>
       <c r="I252" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J252" s="2" t="inlineStr">
@@ -13141,7 +13141,7 @@
       </c>
       <c r="I253" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J253" s="2" t="inlineStr">
@@ -13191,7 +13191,7 @@
       </c>
       <c r="I254" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J254" s="2" t="inlineStr">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="I255" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J255" s="2" t="inlineStr">
@@ -13291,7 +13291,7 @@
       </c>
       <c r="I256" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J256" s="2" t="inlineStr">
@@ -13341,7 +13341,7 @@
       </c>
       <c r="I257" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J257" s="2" t="inlineStr">
@@ -13391,7 +13391,7 @@
       </c>
       <c r="I258" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J258" s="2" t="inlineStr">
@@ -13441,7 +13441,7 @@
       </c>
       <c r="I259" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J259" s="2" t="inlineStr">
@@ -13491,7 +13491,7 @@
       </c>
       <c r="I260" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J260" s="2" t="inlineStr">
@@ -13541,7 +13541,7 @@
       </c>
       <c r="I261" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J261" s="2" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="I262" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J262" s="2" t="inlineStr">
@@ -13641,7 +13641,7 @@
       </c>
       <c r="I263" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J263" s="2" t="inlineStr">
@@ -13691,7 +13691,7 @@
       </c>
       <c r="I264" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J264" s="2" t="inlineStr">
@@ -13741,7 +13741,7 @@
       </c>
       <c r="I265" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J265" s="2" t="inlineStr">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="I266" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J266" s="2" t="inlineStr">
@@ -13841,7 +13841,7 @@
       </c>
       <c r="I267" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J267" s="2" t="inlineStr">
@@ -13891,7 +13891,7 @@
       </c>
       <c r="I268" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J268" s="2" t="inlineStr">
@@ -13941,7 +13941,7 @@
       </c>
       <c r="I269" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J269" s="2" t="inlineStr">
@@ -13991,7 +13991,7 @@
       </c>
       <c r="I270" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J270" s="2" t="inlineStr">
@@ -14041,7 +14041,7 @@
       </c>
       <c r="I271" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J271" s="2" t="inlineStr">
@@ -14091,7 +14091,7 @@
       </c>
       <c r="I272" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J272" s="2" t="inlineStr">
@@ -14141,7 +14141,7 @@
       </c>
       <c r="I273" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J273" s="2" t="inlineStr">
@@ -14191,7 +14191,7 @@
       </c>
       <c r="I274" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J274" s="2" t="inlineStr">
@@ -14241,7 +14241,7 @@
       </c>
       <c r="I275" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J275" s="2" t="inlineStr">
@@ -14291,7 +14291,7 @@
       </c>
       <c r="I276" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J276" s="2" t="inlineStr">
@@ -14341,7 +14341,7 @@
       </c>
       <c r="I277" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J277" s="2" t="inlineStr">
@@ -14391,7 +14391,7 @@
       </c>
       <c r="I278" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J278" s="2" t="inlineStr">
@@ -14441,7 +14441,7 @@
       </c>
       <c r="I279" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J279" s="2" t="inlineStr">
@@ -14491,7 +14491,7 @@
       </c>
       <c r="I280" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J280" s="2" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="I281" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J281" s="2" t="inlineStr">
@@ -14591,7 +14591,7 @@
       </c>
       <c r="I282" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J282" s="2" t="inlineStr">
@@ -14641,7 +14641,7 @@
       </c>
       <c r="I283" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J283" s="2" t="inlineStr">
@@ -14691,7 +14691,7 @@
       </c>
       <c r="I284" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J284" s="2" t="inlineStr">
@@ -14741,7 +14741,7 @@
       </c>
       <c r="I285" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J285" s="2" t="inlineStr">
@@ -14791,7 +14791,7 @@
       </c>
       <c r="I286" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J286" s="2" t="inlineStr">
@@ -14841,7 +14841,7 @@
       </c>
       <c r="I287" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J287" s="2" t="inlineStr">
@@ -14891,7 +14891,7 @@
       </c>
       <c r="I288" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J288" s="2" t="inlineStr">
@@ -14941,7 +14941,7 @@
       </c>
       <c r="I289" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J289" s="2" t="inlineStr">
@@ -14991,7 +14991,7 @@
       </c>
       <c r="I290" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J290" s="2" t="inlineStr">
@@ -15041,7 +15041,7 @@
       </c>
       <c r="I291" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J291" s="2" t="inlineStr">
@@ -15091,7 +15091,7 @@
       </c>
       <c r="I292" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J292" s="2" t="inlineStr">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="I293" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J293" s="2" t="inlineStr">
@@ -15191,7 +15191,7 @@
       </c>
       <c r="I294" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J294" s="2" t="inlineStr">
@@ -15241,7 +15241,7 @@
       </c>
       <c r="I295" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J295" s="2" t="inlineStr">
@@ -15291,7 +15291,7 @@
       </c>
       <c r="I296" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J296" s="2" t="inlineStr">
@@ -15341,7 +15341,7 @@
       </c>
       <c r="I297" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J297" s="2" t="inlineStr">
@@ -15391,7 +15391,7 @@
       </c>
       <c r="I298" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J298" s="2" t="inlineStr">
@@ -15441,7 +15441,7 @@
       </c>
       <c r="I299" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J299" s="2" t="inlineStr">
@@ -15491,7 +15491,7 @@
       </c>
       <c r="I300" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J300" s="2" t="inlineStr">
@@ -15541,7 +15541,7 @@
       </c>
       <c r="I301" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:00</t>
         </is>
       </c>
       <c r="J301" s="2" t="inlineStr">
@@ -15672,7 +15672,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>21.59</v>
+        <v>59.96</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -15681,7 +15681,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:14</t>
         </is>
       </c>
     </row>
@@ -15723,7 +15723,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>3.89</v>
+        <v>50</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
@@ -15732,7 +15732,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:14</t>
         </is>
       </c>
     </row>
@@ -15774,7 +15774,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>4.45</v>
+        <v>49.01</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -15787,7 +15787,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:14</t>
         </is>
       </c>
     </row>
@@ -15829,7 +15829,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>3.99</v>
+        <v>94.76000000000001</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
@@ -15842,7 +15842,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:14</t>
         </is>
       </c>
     </row>
@@ -15884,7 +15884,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>8.82</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:14</t>
         </is>
       </c>
     </row>
@@ -15935,7 +15935,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>4.45</v>
+        <v>10022.58</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -15944,7 +15944,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:24</t>
         </is>
       </c>
     </row>
@@ -15986,7 +15986,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>5.1</v>
+        <v>54.97</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -15995,7 +15995,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:25</t>
         </is>
       </c>
     </row>
@@ -16029,7 +16029,7 @@
         <v>401</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>422</v>
+        <v>500</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
@@ -16037,16 +16037,16 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>5.13</v>
+        <v>10016.36</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>{"detail":[{"type":"model_attributes_type","loc":["body"],"msg":"Input should be</t>
+          <t>Simulated test fallback: ('Connection aborted.', ConnectionResetE</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:35</t>
         </is>
       </c>
     </row>
@@ -16088,7 +16088,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>4.51</v>
+        <v>10016.62</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -16097,7 +16097,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:44:45</t>
         </is>
       </c>
     </row>
@@ -16131,7 +16131,7 @@
         <v>200</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>403</v>
+        <v>500</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
@@ -16139,16 +16139,16 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>2.24</v>
+        <v>30067.1</v>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>{"detail":"Not authenticated"}</t>
+          <t>Simulated test fallback: ('Connection aborted.', RemoteDisconnect</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:45:15</t>
         </is>
       </c>
     </row>
@@ -16182,7 +16182,7 @@
         <v>401</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>403</v>
+        <v>500</v>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
@@ -16190,16 +16190,16 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>2.88</v>
+        <v>20021.59</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>{"detail":"Not authenticated"}</t>
+          <t>Simulated test fallback: HTTPConnectionPool(host='127.0.0.1', por</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:10</t>
+          <t>2026-08-10 17:45:35</t>
         </is>
       </c>
     </row>
@@ -16233,24 +16233,24 @@
         <v>400</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>409</v>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+        <v>500</v>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>283.78</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>{"detail":"Email already registered"}</t>
+        <v>30081.43</v>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Simulated test fallback: HTTPConnectionPool(host='127.0.0.1', por</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:46:05</t>
         </is>
       </c>
     </row>
@@ -16284,7 +16284,7 @@
         <v>401</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>401</v>
+        <v>500</v>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
@@ -16292,16 +16292,16 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>24.47</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>{"detail":"Invalid or expired refresh token"}</t>
+        <v>20060.99</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Simulated test fallback: HTTPConnectionPool(host='127.0.0.1', por</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:46:25</t>
         </is>
       </c>
     </row>
@@ -16343,7 +16343,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>19.92</v>
+        <v>20308.08</v>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
@@ -16352,7 +16352,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:46:45</t>
         </is>
       </c>
     </row>
@@ -16394,7 +16394,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>10.41</v>
+        <v>63.47</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
@@ -16403,7 +16403,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:46:45</t>
         </is>
       </c>
     </row>
@@ -16445,7 +16445,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>7.78</v>
+        <v>47.99</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
@@ -16454,7 +16454,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:46:45</t>
         </is>
       </c>
     </row>
@@ -16496,7 +16496,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>7.34</v>
+        <v>42.37</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:46:45</t>
         </is>
       </c>
     </row>
@@ -16547,7 +16547,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>6.3</v>
+        <v>54.94</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -16556,7 +16556,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:46:45</t>
         </is>
       </c>
     </row>
@@ -16598,7 +16598,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>5.87</v>
+        <v>53.38</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:46:45</t>
         </is>
       </c>
     </row>
@@ -16649,7 +16649,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>7.1</v>
+        <v>2294.7</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:46:48</t>
         </is>
       </c>
     </row>
@@ -16700,7 +16700,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>21.82</v>
+        <v>1990.2</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:46:50</t>
         </is>
       </c>
     </row>
@@ -16751,7 +16751,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>6.91</v>
+        <v>2981.35</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:46:53</t>
         </is>
       </c>
     </row>
@@ -16802,7 +16802,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>6.01</v>
+        <v>128.13</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
@@ -16811,7 +16811,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:46:53</t>
         </is>
       </c>
     </row>
@@ -16853,7 +16853,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>5.75</v>
+        <v>112.01</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:46:53</t>
         </is>
       </c>
     </row>
@@ -16904,7 +16904,7 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>7.5</v>
+        <v>92.29000000000001</v>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
@@ -16913,7 +16913,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:46:53</t>
         </is>
       </c>
     </row>
@@ -16955,7 +16955,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>6.34</v>
+        <v>88.87</v>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
@@ -16964,7 +16964,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:46:53</t>
         </is>
       </c>
     </row>
@@ -17006,7 +17006,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>4.4</v>
+        <v>62.17</v>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:46:53</t>
         </is>
       </c>
     </row>
@@ -17057,7 +17057,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>5.94</v>
+        <v>78.88</v>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
@@ -17066,7 +17066,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:46:53</t>
         </is>
       </c>
     </row>
@@ -17108,7 +17108,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>3.91</v>
+        <v>173.41</v>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:46:53</t>
         </is>
       </c>
     </row>
@@ -17159,7 +17159,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>5.22</v>
+        <v>108.89</v>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -17168,7 +17168,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:46:54</t>
         </is>
       </c>
     </row>
@@ -17210,7 +17210,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>6.06</v>
+        <v>105.22</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -17219,7 +17219,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:46:54</t>
         </is>
       </c>
     </row>
@@ -17261,7 +17261,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>5.84</v>
+        <v>136.74</v>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
@@ -17270,7 +17270,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:46:54</t>
         </is>
       </c>
     </row>
@@ -17312,7 +17312,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>4.9</v>
+        <v>107.81</v>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
@@ -17321,7 +17321,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:46:54</t>
         </is>
       </c>
     </row>
@@ -17363,7 +17363,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
@@ -17372,7 +17372,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:46:54</t>
         </is>
       </c>
     </row>
@@ -17414,7 +17414,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>4.33</v>
+        <v>181.71</v>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
@@ -17423,7 +17423,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:46:54</t>
         </is>
       </c>
     </row>
@@ -17465,7 +17465,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>4.58</v>
+        <v>14.96</v>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -17474,7 +17474,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:46:54</t>
         </is>
       </c>
     </row>
@@ -17516,7 +17516,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>5.8</v>
+        <v>16</v>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
@@ -17525,7 +17525,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:46:54</t>
         </is>
       </c>
     </row>
@@ -17567,7 +17567,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>3.83</v>
+        <v>14.11</v>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:46:54</t>
         </is>
       </c>
     </row>
@@ -17618,7 +17618,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>5.13</v>
+        <v>60.61</v>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
@@ -17627,7 +17627,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:46:54</t>
         </is>
       </c>
     </row>
@@ -17669,7 +17669,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>4.87</v>
+        <v>112.16</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
@@ -17678,7 +17678,7 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:46:54</t>
         </is>
       </c>
     </row>
@@ -17720,7 +17720,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>5.33</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
@@ -17733,7 +17733,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:46:54</t>
         </is>
       </c>
     </row>
@@ -17775,7 +17775,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>3.79</v>
+        <v>90.37</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
@@ -17788,7 +17788,7 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:46:54</t>
         </is>
       </c>
     </row>
@@ -17822,7 +17822,7 @@
         <v>200</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
@@ -17830,16 +17830,16 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>10.71</v>
+        <v>10035.18</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>{"openapi":"3.1.0","info":{"title":"SpectraGuard API","description":"AI-based ph</t>
+          <t>Simulated test fallback: ('Connection aborted.', RemoteDisconnect</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:04</t>
         </is>
       </c>
     </row>
@@ -17881,7 +17881,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>5.6</v>
+        <v>53.64</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:05</t>
         </is>
       </c>
     </row>
@@ -17932,7 +17932,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>4.54</v>
+        <v>26.42</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -17941,7 +17941,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:05</t>
         </is>
       </c>
     </row>
@@ -17983,7 +17983,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>6.82</v>
+        <v>24.51</v>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:05</t>
         </is>
       </c>
     </row>
@@ -18034,7 +18034,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>5.34</v>
+        <v>24</v>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
@@ -18043,7 +18043,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:05</t>
         </is>
       </c>
     </row>
@@ -18085,7 +18085,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>4.23</v>
+        <v>15</v>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:05</t>
         </is>
       </c>
     </row>
@@ -18136,7 +18136,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>6.78</v>
+        <v>11</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -18145,7 +18145,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:05</t>
         </is>
       </c>
     </row>
@@ -18187,7 +18187,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>15.7</v>
+        <v>39.95</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
@@ -18196,7 +18196,7 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:05</t>
         </is>
       </c>
     </row>
@@ -18238,7 +18238,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>6.65</v>
+        <v>22.45</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:05</t>
         </is>
       </c>
     </row>
@@ -18289,7 +18289,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>4.22</v>
+        <v>34.79</v>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -18298,7 +18298,7 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:05</t>
         </is>
       </c>
     </row>
@@ -18340,7 +18340,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>5.54</v>
+        <v>19.5</v>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
@@ -18349,7 +18349,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:05</t>
         </is>
       </c>
     </row>
@@ -18391,7 +18391,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>5.7</v>
+        <v>21.29</v>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:05</t>
         </is>
       </c>
     </row>
@@ -18442,7 +18442,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>4.89</v>
+        <v>21.56</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:05</t>
         </is>
       </c>
     </row>
@@ -18493,7 +18493,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>6.65</v>
+        <v>29.1</v>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
@@ -18502,7 +18502,7 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:05</t>
         </is>
       </c>
     </row>
@@ -18544,7 +18544,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>4.04</v>
+        <v>39.39</v>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -18553,7 +18553,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:05</t>
         </is>
       </c>
     </row>
@@ -18595,7 +18595,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>5.86</v>
+        <v>17.23</v>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
@@ -18604,7 +18604,7 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:05</t>
         </is>
       </c>
     </row>
@@ -18646,7 +18646,7 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>6.37</v>
+        <v>46.23</v>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
@@ -18655,7 +18655,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:05</t>
         </is>
       </c>
     </row>
@@ -18697,7 +18697,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>4.58</v>
+        <v>30.15</v>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
@@ -18706,7 +18706,7 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:05</t>
         </is>
       </c>
     </row>
@@ -18748,7 +18748,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>5.19</v>
+        <v>22.99</v>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
@@ -18757,7 +18757,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:05</t>
         </is>
       </c>
     </row>
@@ -18799,7 +18799,7 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>6.63</v>
+        <v>22.27</v>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
@@ -18808,7 +18808,7 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:05</t>
         </is>
       </c>
     </row>
@@ -18850,7 +18850,7 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>6.97</v>
+        <v>44.68</v>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
@@ -18859,7 +18859,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:05</t>
         </is>
       </c>
     </row>
@@ -18901,7 +18901,7 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>5.83</v>
+        <v>33.88</v>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
@@ -18910,7 +18910,7 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:05</t>
         </is>
       </c>
     </row>
@@ -18952,7 +18952,7 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>6.56</v>
+        <v>31.89</v>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
@@ -18961,7 +18961,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:05</t>
         </is>
       </c>
     </row>
@@ -19003,7 +19003,7 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>4.89</v>
+        <v>19.95</v>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
@@ -19012,7 +19012,7 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:05</t>
         </is>
       </c>
     </row>
@@ -19054,7 +19054,7 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>5.45</v>
+        <v>23.9</v>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
@@ -19063,7 +19063,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:05</t>
         </is>
       </c>
     </row>
@@ -19105,7 +19105,7 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>7.18</v>
+        <v>23</v>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:05</t>
         </is>
       </c>
     </row>
@@ -19156,7 +19156,7 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>5.28</v>
+        <v>24.28</v>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
@@ -19165,7 +19165,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:05</t>
         </is>
       </c>
     </row>
@@ -19207,7 +19207,7 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>7.61</v>
+        <v>27.57</v>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:05</t>
         </is>
       </c>
     </row>
@@ -19258,7 +19258,7 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>5.25</v>
+        <v>58.06</v>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
@@ -19267,7 +19267,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:05</t>
         </is>
       </c>
     </row>
@@ -19309,7 +19309,7 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>4.65</v>
+        <v>55.33</v>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
@@ -19318,7 +19318,7 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:05</t>
         </is>
       </c>
     </row>
@@ -19360,7 +19360,7 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>4.65</v>
+        <v>29.79</v>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
@@ -19369,7 +19369,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:05</t>
         </is>
       </c>
     </row>
@@ -19411,7 +19411,7 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>4.57</v>
+        <v>52.56</v>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -19420,7 +19420,7 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:05</t>
         </is>
       </c>
     </row>
@@ -19462,7 +19462,7 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>2.87</v>
+        <v>8.34</v>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
@@ -19471,7 +19471,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:05</t>
         </is>
       </c>
     </row>
@@ -19513,7 +19513,7 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>3.09</v>
+        <v>9</v>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
@@ -19522,7 +19522,7 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:05</t>
         </is>
       </c>
     </row>
@@ -19564,7 +19564,7 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>4.93</v>
+        <v>52.07</v>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:06</t>
         </is>
       </c>
     </row>
@@ -19615,7 +19615,7 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>4.91</v>
+        <v>3302.34</v>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
@@ -19624,7 +19624,7 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:09</t>
         </is>
       </c>
     </row>
@@ -19666,7 +19666,7 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>4.81</v>
+        <v>50.54</v>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
@@ -19679,7 +19679,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:09</t>
         </is>
       </c>
     </row>
@@ -19721,7 +19721,7 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>3.81</v>
+        <v>3691.7</v>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:13</t>
         </is>
       </c>
     </row>
@@ -19776,7 +19776,7 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>8.84</v>
+        <v>1970.01</v>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:15</t>
         </is>
       </c>
     </row>
@@ -19827,7 +19827,7 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>5.19</v>
+        <v>4791.97</v>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:19</t>
         </is>
       </c>
     </row>
@@ -19878,7 +19878,7 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>4.45</v>
+        <v>43.92</v>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
@@ -19887,7 +19887,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:19</t>
         </is>
       </c>
     </row>
@@ -19929,7 +19929,7 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>7.19</v>
+        <v>50.09</v>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
@@ -19938,7 +19938,7 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:19</t>
         </is>
       </c>
     </row>
@@ -19980,7 +19980,7 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>4.15</v>
+        <v>49.39</v>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
@@ -19989,7 +19989,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:19</t>
         </is>
       </c>
     </row>
@@ -20031,7 +20031,7 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>4.13</v>
+        <v>25.46</v>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
@@ -20040,7 +20040,7 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:19</t>
         </is>
       </c>
     </row>
@@ -20082,7 +20082,7 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>4.17</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
@@ -20091,7 +20091,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:20</t>
         </is>
       </c>
     </row>
@@ -20133,7 +20133,7 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>309.62</v>
+        <v>20.28</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
@@ -20142,7 +20142,7 @@
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:20</t>
         </is>
       </c>
     </row>
@@ -20184,7 +20184,7 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>20.23</v>
+        <v>13.16</v>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
@@ -20193,7 +20193,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:20</t>
         </is>
       </c>
     </row>
@@ -20235,7 +20235,7 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>14.75</v>
+        <v>25.15</v>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
@@ -20244,7 +20244,7 @@
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:20</t>
         </is>
       </c>
     </row>
@@ -20286,7 +20286,7 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>10.08</v>
+        <v>14.87</v>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
@@ -20295,7 +20295,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:20</t>
         </is>
       </c>
     </row>
@@ -20337,7 +20337,7 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>6.51</v>
+        <v>18.08</v>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
@@ -20346,7 +20346,7 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:20</t>
         </is>
       </c>
     </row>
@@ -20388,7 +20388,7 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>6.47</v>
+        <v>17.02</v>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
@@ -20397,7 +20397,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:20</t>
         </is>
       </c>
     </row>
@@ -20439,7 +20439,7 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>8.06</v>
+        <v>24</v>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
@@ -20448,7 +20448,7 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:20</t>
         </is>
       </c>
     </row>
@@ -20490,7 +20490,7 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>5</v>
+        <v>17.72</v>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
@@ -20499,7 +20499,7 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:20</t>
         </is>
       </c>
     </row>
@@ -20541,7 +20541,7 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>8.33</v>
+        <v>23.15</v>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
@@ -20550,7 +20550,7 @@
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:20</t>
         </is>
       </c>
     </row>
@@ -20592,7 +20592,7 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>6.44</v>
+        <v>16.81</v>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
@@ -20601,7 +20601,7 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:20</t>
         </is>
       </c>
     </row>
@@ -20643,7 +20643,7 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>6.49</v>
+        <v>15.72</v>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
@@ -20652,7 +20652,7 @@
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:20</t>
         </is>
       </c>
     </row>
@@ -20694,7 +20694,7 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>7.2</v>
+        <v>16.82</v>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
@@ -20703,7 +20703,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:20</t>
         </is>
       </c>
     </row>
@@ -20745,7 +20745,7 @@
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>6.22</v>
+        <v>16.56</v>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:20</t>
         </is>
       </c>
     </row>
@@ -20796,7 +20796,7 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>7.49</v>
+        <v>16.05</v>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:20</t>
         </is>
       </c>
     </row>
@@ -20847,7 +20847,7 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>6.22</v>
+        <v>15.96</v>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
@@ -20856,7 +20856,7 @@
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:20</t>
         </is>
       </c>
     </row>
@@ -20898,7 +20898,7 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>6.68</v>
+        <v>17.38</v>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
@@ -20907,7 +20907,7 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:20</t>
         </is>
       </c>
     </row>
@@ -20949,7 +20949,7 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>5.7</v>
+        <v>15.89</v>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
@@ -20958,7 +20958,7 @@
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:20</t>
         </is>
       </c>
     </row>
@@ -21000,7 +21000,7 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>5.01</v>
+        <v>16.67</v>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
@@ -21009,7 +21009,7 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:20</t>
         </is>
       </c>
     </row>
@@ -21051,7 +21051,7 @@
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>5.73</v>
+        <v>15.82</v>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
@@ -21060,7 +21060,7 @@
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:20</t>
         </is>
       </c>
     </row>
@@ -21102,7 +21102,7 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>5.14</v>
+        <v>20.85</v>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
@@ -21111,7 +21111,7 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:20</t>
         </is>
       </c>
     </row>
@@ -21153,7 +21153,7 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>5.33</v>
+        <v>15.55</v>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
@@ -21162,7 +21162,7 @@
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:20</t>
         </is>
       </c>
     </row>
@@ -21204,7 +21204,7 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>6.13</v>
+        <v>17.77</v>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
@@ -21213,7 +21213,7 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:20</t>
         </is>
       </c>
     </row>
@@ -21255,7 +21255,7 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>4.87</v>
+        <v>18.65</v>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:20</t>
         </is>
       </c>
     </row>
@@ -21306,7 +21306,7 @@
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>4.09</v>
+        <v>14.66</v>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:20</t>
         </is>
       </c>
     </row>
@@ -21357,7 +21357,7 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>5.76</v>
+        <v>17.25</v>
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
@@ -21366,7 +21366,7 @@
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:20</t>
         </is>
       </c>
     </row>
@@ -21408,7 +21408,7 @@
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>3.32</v>
+        <v>11.9</v>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
@@ -21417,7 +21417,7 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:20</t>
         </is>
       </c>
     </row>
@@ -21459,7 +21459,7 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>2.57</v>
+        <v>20.57</v>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
@@ -21468,7 +21468,7 @@
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:11</t>
+          <t>2026-08-10 17:47:20</t>
         </is>
       </c>
     </row>
@@ -21510,7 +21510,7 @@
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>5.95</v>
+        <v>15.1</v>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
@@ -21519,7 +21519,7 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:20</t>
         </is>
       </c>
     </row>
@@ -21561,7 +21561,7 @@
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>5.39</v>
+        <v>14.8</v>
       </c>
       <c r="J117" s="4" t="inlineStr">
         <is>
@@ -21570,7 +21570,7 @@
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:20</t>
         </is>
       </c>
     </row>
@@ -21612,7 +21612,7 @@
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>5.66</v>
+        <v>11.36</v>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
@@ -21625,7 +21625,7 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:20</t>
         </is>
       </c>
     </row>
@@ -21667,7 +21667,7 @@
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>19.06</v>
+        <v>14.23</v>
       </c>
       <c r="J119" s="4" t="inlineStr">
         <is>
@@ -21680,7 +21680,7 @@
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:20</t>
         </is>
       </c>
     </row>
@@ -21722,7 +21722,7 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>9.6</v>
+        <v>25.94</v>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
@@ -21731,7 +21731,7 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:20</t>
         </is>
       </c>
     </row>
@@ -21773,7 +21773,7 @@
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>27.99</v>
+        <v>19.25</v>
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
@@ -21782,7 +21782,7 @@
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:20</t>
         </is>
       </c>
     </row>
@@ -21824,7 +21824,7 @@
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>7.12</v>
+        <v>15.1</v>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
@@ -21833,7 +21833,7 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:20</t>
         </is>
       </c>
     </row>
@@ -21875,7 +21875,7 @@
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>6.54</v>
+        <v>17.01</v>
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
@@ -21884,7 +21884,7 @@
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:20</t>
         </is>
       </c>
     </row>
@@ -21926,7 +21926,7 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>6.76</v>
+        <v>15.33</v>
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
@@ -21935,7 +21935,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:20</t>
         </is>
       </c>
     </row>
@@ -21977,7 +21977,7 @@
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>4.66</v>
+        <v>12.9</v>
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
@@ -21986,7 +21986,7 @@
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:20</t>
         </is>
       </c>
     </row>
@@ -22028,7 +22028,7 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>6.25</v>
+        <v>17.35</v>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
@@ -22037,7 +22037,7 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:20</t>
         </is>
       </c>
     </row>
@@ -22079,7 +22079,7 @@
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>228.21</v>
+        <v>39.39</v>
       </c>
       <c r="J127" s="4" t="inlineStr">
         <is>
@@ -22088,7 +22088,7 @@
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:20</t>
         </is>
       </c>
     </row>
@@ -22130,7 +22130,7 @@
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>19.79</v>
+        <v>24.24</v>
       </c>
       <c r="J128" s="4" t="inlineStr">
         <is>
@@ -22139,7 +22139,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:20</t>
         </is>
       </c>
     </row>
@@ -22181,7 +22181,7 @@
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>26.66</v>
+        <v>29.72</v>
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
@@ -22190,7 +22190,7 @@
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:20</t>
         </is>
       </c>
     </row>
@@ -22232,7 +22232,7 @@
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>9.859999999999999</v>
+        <v>28.3</v>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
@@ -22241,7 +22241,7 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:20</t>
         </is>
       </c>
     </row>
@@ -22283,7 +22283,7 @@
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>9.550000000000001</v>
+        <v>21.18</v>
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:20</t>
         </is>
       </c>
     </row>
@@ -22334,7 +22334,7 @@
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>5.45</v>
+        <v>23.97</v>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
@@ -22343,7 +22343,7 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:20</t>
         </is>
       </c>
     </row>
@@ -22385,7 +22385,7 @@
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>8.84</v>
+        <v>26.39</v>
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
@@ -22394,7 +22394,7 @@
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:20</t>
         </is>
       </c>
     </row>
@@ -22436,7 +22436,7 @@
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>4.87</v>
+        <v>24.9</v>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
@@ -22445,7 +22445,7 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:20</t>
         </is>
       </c>
     </row>
@@ -22487,7 +22487,7 @@
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>7.12</v>
+        <v>24.87</v>
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
@@ -22496,7 +22496,7 @@
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:20</t>
         </is>
       </c>
     </row>
@@ -22538,7 +22538,7 @@
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>6.55</v>
+        <v>32.8</v>
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
@@ -22547,7 +22547,7 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:20</t>
         </is>
       </c>
     </row>
@@ -22589,7 +22589,7 @@
         </is>
       </c>
       <c r="I137" s="2" t="n">
-        <v>6.29</v>
+        <v>26.01</v>
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
@@ -22598,7 +22598,7 @@
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:20</t>
         </is>
       </c>
     </row>
@@ -22640,7 +22640,7 @@
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>7.55</v>
+        <v>23.79</v>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
@@ -22649,7 +22649,7 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:20</t>
         </is>
       </c>
     </row>
@@ -22691,7 +22691,7 @@
         </is>
       </c>
       <c r="I139" s="2" t="n">
-        <v>11.64</v>
+        <v>25.21</v>
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
@@ -22700,7 +22700,7 @@
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:21</t>
         </is>
       </c>
     </row>
@@ -22742,7 +22742,7 @@
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>7.25</v>
+        <v>22.29</v>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
@@ -22751,7 +22751,7 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:21</t>
         </is>
       </c>
     </row>
@@ -22793,7 +22793,7 @@
         </is>
       </c>
       <c r="I141" s="2" t="n">
-        <v>5.6</v>
+        <v>26.26</v>
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:21</t>
         </is>
       </c>
     </row>
@@ -22844,7 +22844,7 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>6.35</v>
+        <v>20.06</v>
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
@@ -22853,7 +22853,7 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:21</t>
         </is>
       </c>
     </row>
@@ -22895,7 +22895,7 @@
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>5.25</v>
+        <v>16.42</v>
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
@@ -22904,7 +22904,7 @@
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:21</t>
         </is>
       </c>
     </row>
@@ -22946,7 +22946,7 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>5.68</v>
+        <v>18</v>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
@@ -22955,7 +22955,7 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:21</t>
         </is>
       </c>
     </row>
@@ -22997,7 +22997,7 @@
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>8.74</v>
+        <v>27.42</v>
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
@@ -23006,7 +23006,7 @@
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:21</t>
         </is>
       </c>
     </row>
@@ -23048,7 +23048,7 @@
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>6.08</v>
+        <v>20.8</v>
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
@@ -23057,7 +23057,7 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:21</t>
         </is>
       </c>
     </row>
@@ -23099,7 +23099,7 @@
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>7.07</v>
+        <v>19.5</v>
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
@@ -23108,7 +23108,7 @@
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:21</t>
         </is>
       </c>
     </row>
@@ -23150,7 +23150,7 @@
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>6.51</v>
+        <v>22.91</v>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
@@ -23159,7 +23159,7 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:21</t>
         </is>
       </c>
     </row>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="I149" s="2" t="n">
-        <v>8.119999999999999</v>
+        <v>19.41</v>
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
@@ -23210,7 +23210,7 @@
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:21</t>
         </is>
       </c>
     </row>
@@ -23252,7 +23252,7 @@
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>6.04</v>
+        <v>16.24</v>
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
@@ -23261,7 +23261,7 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:21</t>
         </is>
       </c>
     </row>
@@ -23303,7 +23303,7 @@
         </is>
       </c>
       <c r="I151" s="2" t="n">
-        <v>6.49</v>
+        <v>16.8</v>
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
@@ -23312,7 +23312,7 @@
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:21</t>
         </is>
       </c>
     </row>
@@ -23354,7 +23354,7 @@
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>5</v>
+        <v>9.23</v>
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
@@ -23363,7 +23363,7 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:21</t>
         </is>
       </c>
     </row>
@@ -23405,7 +23405,7 @@
         </is>
       </c>
       <c r="I153" s="2" t="n">
-        <v>4.3</v>
+        <v>11.69</v>
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:21</t>
         </is>
       </c>
     </row>
@@ -23456,7 +23456,7 @@
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>5</v>
+        <v>26.15</v>
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
@@ -23465,7 +23465,7 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:21</t>
         </is>
       </c>
     </row>
@@ -23507,7 +23507,7 @@
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>6.49</v>
+        <v>36.5</v>
       </c>
       <c r="J155" s="4" t="inlineStr">
         <is>
@@ -23516,7 +23516,7 @@
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:21</t>
         </is>
       </c>
     </row>
@@ -23558,7 +23558,7 @@
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>6.11</v>
+        <v>31.13</v>
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
@@ -23571,7 +23571,7 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:21</t>
         </is>
       </c>
     </row>
@@ -23613,7 +23613,7 @@
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>5.97</v>
+        <v>16.54</v>
       </c>
       <c r="J157" s="4" t="inlineStr">
         <is>
@@ -23626,7 +23626,7 @@
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:21</t>
         </is>
       </c>
     </row>
@@ -23668,7 +23668,7 @@
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>36.97</v>
+        <v>25.58</v>
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
@@ -23677,7 +23677,7 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:21</t>
         </is>
       </c>
     </row>
@@ -23719,7 +23719,7 @@
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>6.85</v>
+        <v>18.52</v>
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
@@ -23728,7 +23728,7 @@
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:21</t>
         </is>
       </c>
     </row>
@@ -23770,7 +23770,7 @@
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>6.89</v>
+        <v>14.83</v>
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
@@ -23779,7 +23779,7 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:21</t>
         </is>
       </c>
     </row>
@@ -23821,7 +23821,7 @@
         </is>
       </c>
       <c r="I161" s="2" t="n">
-        <v>6.89</v>
+        <v>15.32</v>
       </c>
       <c r="J161" s="2" t="inlineStr">
         <is>
@@ -23830,7 +23830,7 @@
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:21</t>
         </is>
       </c>
     </row>
@@ -23872,7 +23872,7 @@
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>4.77</v>
+        <v>18.75</v>
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
@@ -23881,7 +23881,7 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:21</t>
         </is>
       </c>
     </row>
@@ -23923,7 +23923,7 @@
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>9.08</v>
+        <v>16.32</v>
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
@@ -23932,7 +23932,7 @@
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:21</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>9.199999999999999</v>
+        <v>19.06</v>
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
@@ -23983,7 +23983,7 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:21</t>
         </is>
       </c>
     </row>
@@ -24025,7 +24025,7 @@
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>213.28</v>
+        <v>27</v>
       </c>
       <c r="J165" s="4" t="inlineStr">
         <is>
@@ -24034,7 +24034,7 @@
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:21</t>
         </is>
       </c>
     </row>
@@ -24076,7 +24076,7 @@
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>11.03</v>
+        <v>14.15</v>
       </c>
       <c r="J166" s="4" t="inlineStr">
         <is>
@@ -24085,7 +24085,7 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:21</t>
         </is>
       </c>
     </row>
@@ -24127,7 +24127,7 @@
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>10.56</v>
+        <v>20.32</v>
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
@@ -24136,7 +24136,7 @@
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:21</t>
         </is>
       </c>
     </row>
@@ -24178,7 +24178,7 @@
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>9.23</v>
+        <v>43.87</v>
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
@@ -24187,7 +24187,7 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:21</t>
         </is>
       </c>
     </row>
@@ -24229,7 +24229,7 @@
         </is>
       </c>
       <c r="I169" s="2" t="n">
-        <v>6.83</v>
+        <v>19.11</v>
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
@@ -24238,7 +24238,7 @@
       </c>
       <c r="K169" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:21</t>
         </is>
       </c>
     </row>
@@ -24280,7 +24280,7 @@
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>6.05</v>
+        <v>14.75</v>
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
@@ -24289,7 +24289,7 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:21</t>
         </is>
       </c>
     </row>
@@ -24331,7 +24331,7 @@
         </is>
       </c>
       <c r="I171" s="2" t="n">
-        <v>7.31</v>
+        <v>39.65</v>
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
@@ -24340,7 +24340,7 @@
       </c>
       <c r="K171" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:21</t>
         </is>
       </c>
     </row>
@@ -24382,7 +24382,7 @@
         </is>
       </c>
       <c r="I172" s="2" t="n">
-        <v>5.18</v>
+        <v>21.94</v>
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
@@ -24391,7 +24391,7 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:21</t>
         </is>
       </c>
     </row>
@@ -24433,7 +24433,7 @@
         </is>
       </c>
       <c r="I173" s="2" t="n">
-        <v>7.96</v>
+        <v>42.76</v>
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
@@ -24442,7 +24442,7 @@
       </c>
       <c r="K173" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:21</t>
         </is>
       </c>
     </row>
@@ -24484,7 +24484,7 @@
         </is>
       </c>
       <c r="I174" s="2" t="n">
-        <v>6.92</v>
+        <v>35.53</v>
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
@@ -24493,7 +24493,7 @@
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:21</t>
         </is>
       </c>
     </row>
@@ -24535,7 +24535,7 @@
         </is>
       </c>
       <c r="I175" s="2" t="n">
-        <v>8.02</v>
+        <v>26.9</v>
       </c>
       <c r="J175" s="2" t="inlineStr">
         <is>
@@ -24544,7 +24544,7 @@
       </c>
       <c r="K175" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:21</t>
         </is>
       </c>
     </row>
@@ -24586,7 +24586,7 @@
         </is>
       </c>
       <c r="I176" s="2" t="n">
-        <v>7.15</v>
+        <v>19.05</v>
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
@@ -24595,7 +24595,7 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:21</t>
         </is>
       </c>
     </row>
@@ -24637,7 +24637,7 @@
         </is>
       </c>
       <c r="I177" s="2" t="n">
-        <v>8.6</v>
+        <v>34.58</v>
       </c>
       <c r="J177" s="2" t="inlineStr">
         <is>
@@ -24646,7 +24646,7 @@
       </c>
       <c r="K177" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:21</t>
         </is>
       </c>
     </row>
@@ -24688,7 +24688,7 @@
         </is>
       </c>
       <c r="I178" s="2" t="n">
-        <v>7.37</v>
+        <v>61.99</v>
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
@@ -24697,7 +24697,7 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:21</t>
         </is>
       </c>
     </row>
@@ -24739,7 +24739,7 @@
         </is>
       </c>
       <c r="I179" s="2" t="n">
-        <v>8.09</v>
+        <v>21.28</v>
       </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
@@ -24748,7 +24748,7 @@
       </c>
       <c r="K179" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:21</t>
         </is>
       </c>
     </row>
@@ -24790,7 +24790,7 @@
         </is>
       </c>
       <c r="I180" s="2" t="n">
-        <v>6.45</v>
+        <v>19.97</v>
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
@@ -24799,7 +24799,7 @@
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:21</t>
         </is>
       </c>
     </row>
@@ -24841,7 +24841,7 @@
         </is>
       </c>
       <c r="I181" s="2" t="n">
-        <v>5.59</v>
+        <v>13.07</v>
       </c>
       <c r="J181" s="2" t="inlineStr">
         <is>
@@ -24850,7 +24850,7 @@
       </c>
       <c r="K181" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:22</t>
         </is>
       </c>
     </row>
@@ -24892,7 +24892,7 @@
         </is>
       </c>
       <c r="I182" s="2" t="n">
-        <v>8.699999999999999</v>
+        <v>26.34</v>
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
@@ -24901,7 +24901,7 @@
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:12</t>
+          <t>2026-08-10 17:47:22</t>
         </is>
       </c>
     </row>
@@ -24943,7 +24943,7 @@
         </is>
       </c>
       <c r="I183" s="2" t="n">
-        <v>8.09</v>
+        <v>19.4</v>
       </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
@@ -24952,7 +24952,7 @@
       </c>
       <c r="K183" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:22</t>
         </is>
       </c>
     </row>
@@ -24994,7 +24994,7 @@
         </is>
       </c>
       <c r="I184" s="2" t="n">
-        <v>8.720000000000001</v>
+        <v>24.33</v>
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
@@ -25003,7 +25003,7 @@
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:22</t>
         </is>
       </c>
     </row>
@@ -25045,7 +25045,7 @@
         </is>
       </c>
       <c r="I185" s="2" t="n">
-        <v>11.23</v>
+        <v>114.63</v>
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
@@ -25054,7 +25054,7 @@
       </c>
       <c r="K185" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:22</t>
         </is>
       </c>
     </row>
@@ -25096,7 +25096,7 @@
         </is>
       </c>
       <c r="I186" s="2" t="n">
-        <v>9.119999999999999</v>
+        <v>51.73</v>
       </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
@@ -25105,7 +25105,7 @@
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:22</t>
         </is>
       </c>
     </row>
@@ -25147,7 +25147,7 @@
         </is>
       </c>
       <c r="I187" s="2" t="n">
-        <v>8.880000000000001</v>
+        <v>22.39</v>
       </c>
       <c r="J187" s="2" t="inlineStr">
         <is>
@@ -25156,7 +25156,7 @@
       </c>
       <c r="K187" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:22</t>
         </is>
       </c>
     </row>
@@ -25198,7 +25198,7 @@
         </is>
       </c>
       <c r="I188" s="2" t="n">
-        <v>6.31</v>
+        <v>16.46</v>
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
@@ -25207,7 +25207,7 @@
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:22</t>
         </is>
       </c>
     </row>
@@ -25249,7 +25249,7 @@
         </is>
       </c>
       <c r="I189" s="2" t="n">
-        <v>10.04</v>
+        <v>27.04</v>
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
       </c>
       <c r="K189" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:22</t>
         </is>
       </c>
     </row>
@@ -25300,7 +25300,7 @@
         </is>
       </c>
       <c r="I190" s="2" t="n">
-        <v>6.12</v>
+        <v>11.56</v>
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
@@ -25309,7 +25309,7 @@
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:22</t>
         </is>
       </c>
     </row>
@@ -25351,7 +25351,7 @@
         </is>
       </c>
       <c r="I191" s="2" t="n">
-        <v>4.2</v>
+        <v>12</v>
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
@@ -25360,7 +25360,7 @@
       </c>
       <c r="K191" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:22</t>
         </is>
       </c>
     </row>
@@ -25402,7 +25402,7 @@
         </is>
       </c>
       <c r="I192" s="2" t="n">
-        <v>7.99</v>
+        <v>17.18</v>
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:22</t>
         </is>
       </c>
     </row>
@@ -25453,7 +25453,7 @@
         </is>
       </c>
       <c r="I193" s="2" t="n">
-        <v>5.25</v>
+        <v>21.32</v>
       </c>
       <c r="J193" s="4" t="inlineStr">
         <is>
@@ -25462,7 +25462,7 @@
       </c>
       <c r="K193" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:22</t>
         </is>
       </c>
     </row>
@@ -25504,7 +25504,7 @@
         </is>
       </c>
       <c r="I194" s="2" t="n">
-        <v>10.44</v>
+        <v>15.94</v>
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
@@ -25517,7 +25517,7 @@
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:22</t>
         </is>
       </c>
     </row>
@@ -25559,7 +25559,7 @@
         </is>
       </c>
       <c r="I195" s="2" t="n">
-        <v>8.35</v>
+        <v>19.63</v>
       </c>
       <c r="J195" s="4" t="inlineStr">
         <is>
@@ -25572,7 +25572,7 @@
       </c>
       <c r="K195" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:22</t>
         </is>
       </c>
     </row>
@@ -25614,7 +25614,7 @@
         </is>
       </c>
       <c r="I196" s="2" t="n">
-        <v>13.18</v>
+        <v>34</v>
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
@@ -25623,7 +25623,7 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:22</t>
         </is>
       </c>
     </row>
@@ -25665,7 +25665,7 @@
         </is>
       </c>
       <c r="I197" s="2" t="n">
-        <v>9.59</v>
+        <v>17.88</v>
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
@@ -25674,7 +25674,7 @@
       </c>
       <c r="K197" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:22</t>
         </is>
       </c>
     </row>
@@ -25716,7 +25716,7 @@
         </is>
       </c>
       <c r="I198" s="2" t="n">
-        <v>5.34</v>
+        <v>16.37</v>
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:22</t>
         </is>
       </c>
     </row>
@@ -25767,7 +25767,7 @@
         </is>
       </c>
       <c r="I199" s="2" t="n">
-        <v>4.25</v>
+        <v>17.97</v>
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
       </c>
       <c r="K199" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:22</t>
         </is>
       </c>
     </row>
@@ -25818,7 +25818,7 @@
         </is>
       </c>
       <c r="I200" s="2" t="n">
-        <v>6.61</v>
+        <v>20.19</v>
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
@@ -25827,7 +25827,7 @@
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:22</t>
         </is>
       </c>
     </row>
@@ -25869,7 +25869,7 @@
         </is>
       </c>
       <c r="I201" s="2" t="n">
-        <v>6.11</v>
+        <v>15</v>
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
@@ -25878,7 +25878,7 @@
       </c>
       <c r="K201" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:22</t>
         </is>
       </c>
     </row>
@@ -25920,7 +25920,7 @@
         </is>
       </c>
       <c r="I202" s="2" t="n">
-        <v>7.85</v>
+        <v>23</v>
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
@@ -25929,7 +25929,7 @@
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:22</t>
         </is>
       </c>
     </row>
@@ -25971,7 +25971,7 @@
         </is>
       </c>
       <c r="I203" s="2" t="n">
-        <v>14.88</v>
+        <v>34.41</v>
       </c>
       <c r="J203" s="4" t="inlineStr">
         <is>
@@ -25980,7 +25980,7 @@
       </c>
       <c r="K203" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:22</t>
         </is>
       </c>
     </row>
@@ -26022,7 +26022,7 @@
         </is>
       </c>
       <c r="I204" s="2" t="n">
-        <v>7.52</v>
+        <v>17.86</v>
       </c>
       <c r="J204" s="4" t="inlineStr">
         <is>
@@ -26031,7 +26031,7 @@
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:22</t>
         </is>
       </c>
     </row>
@@ -26073,7 +26073,7 @@
         </is>
       </c>
       <c r="I205" s="2" t="n">
-        <v>9.470000000000001</v>
+        <v>30.64</v>
       </c>
       <c r="J205" s="2" t="inlineStr">
         <is>
@@ -26082,7 +26082,7 @@
       </c>
       <c r="K205" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:22</t>
         </is>
       </c>
     </row>
@@ -26124,7 +26124,7 @@
         </is>
       </c>
       <c r="I206" s="2" t="n">
-        <v>7.49</v>
+        <v>29.63</v>
       </c>
       <c r="J206" s="2" t="inlineStr">
         <is>
@@ -26133,7 +26133,7 @@
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:22</t>
         </is>
       </c>
     </row>
@@ -26175,7 +26175,7 @@
         </is>
       </c>
       <c r="I207" s="2" t="n">
-        <v>7.56</v>
+        <v>39.35</v>
       </c>
       <c r="J207" s="2" t="inlineStr">
         <is>
@@ -26184,7 +26184,7 @@
       </c>
       <c r="K207" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:22</t>
         </is>
       </c>
     </row>
@@ -26226,7 +26226,7 @@
         </is>
       </c>
       <c r="I208" s="2" t="n">
-        <v>6.08</v>
+        <v>14</v>
       </c>
       <c r="J208" s="2" t="inlineStr">
         <is>
@@ -26235,7 +26235,7 @@
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:22</t>
         </is>
       </c>
     </row>
@@ -26277,7 +26277,7 @@
         </is>
       </c>
       <c r="I209" s="2" t="n">
-        <v>6.61</v>
+        <v>33.62</v>
       </c>
       <c r="J209" s="2" t="inlineStr">
         <is>
@@ -26286,7 +26286,7 @@
       </c>
       <c r="K209" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:22</t>
         </is>
       </c>
     </row>
@@ -26328,7 +26328,7 @@
         </is>
       </c>
       <c r="I210" s="2" t="n">
-        <v>5.16</v>
+        <v>74.18000000000001</v>
       </c>
       <c r="J210" s="2" t="inlineStr">
         <is>
@@ -26337,7 +26337,7 @@
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:22</t>
         </is>
       </c>
     </row>
@@ -26379,7 +26379,7 @@
         </is>
       </c>
       <c r="I211" s="2" t="n">
-        <v>9.029999999999999</v>
+        <v>47.98</v>
       </c>
       <c r="J211" s="2" t="inlineStr">
         <is>
@@ -26388,7 +26388,7 @@
       </c>
       <c r="K211" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:22</t>
         </is>
       </c>
     </row>
@@ -26430,7 +26430,7 @@
         </is>
       </c>
       <c r="I212" s="2" t="n">
-        <v>8.5</v>
+        <v>24.47</v>
       </c>
       <c r="J212" s="2" t="inlineStr">
         <is>
@@ -26439,7 +26439,7 @@
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:22</t>
         </is>
       </c>
     </row>
@@ -26481,7 +26481,7 @@
         </is>
       </c>
       <c r="I213" s="2" t="n">
-        <v>10.43</v>
+        <v>25.95</v>
       </c>
       <c r="J213" s="2" t="inlineStr">
         <is>
@@ -26490,7 +26490,7 @@
       </c>
       <c r="K213" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:22</t>
         </is>
       </c>
     </row>
@@ -26532,7 +26532,7 @@
         </is>
       </c>
       <c r="I214" s="2" t="n">
-        <v>8.24</v>
+        <v>32.44</v>
       </c>
       <c r="J214" s="2" t="inlineStr">
         <is>
@@ -26541,7 +26541,7 @@
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:22</t>
         </is>
       </c>
     </row>
@@ -26583,7 +26583,7 @@
         </is>
       </c>
       <c r="I215" s="2" t="n">
-        <v>8.92</v>
+        <v>98.5</v>
       </c>
       <c r="J215" s="2" t="inlineStr">
         <is>
@@ -26592,7 +26592,7 @@
       </c>
       <c r="K215" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:23</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
         </is>
       </c>
       <c r="I216" s="2" t="n">
-        <v>8.15</v>
+        <v>267.96</v>
       </c>
       <c r="J216" s="2" t="inlineStr">
         <is>
@@ -26643,7 +26643,7 @@
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:23</t>
         </is>
       </c>
     </row>
@@ -26685,7 +26685,7 @@
         </is>
       </c>
       <c r="I217" s="2" t="n">
-        <v>11.37</v>
+        <v>134.31</v>
       </c>
       <c r="J217" s="2" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
       </c>
       <c r="K217" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:23</t>
         </is>
       </c>
     </row>
@@ -26736,7 +26736,7 @@
         </is>
       </c>
       <c r="I218" s="2" t="n">
-        <v>8.369999999999999</v>
+        <v>165.69</v>
       </c>
       <c r="J218" s="2" t="inlineStr">
         <is>
@@ -26745,7 +26745,7 @@
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:23</t>
         </is>
       </c>
     </row>
@@ -26787,7 +26787,7 @@
         </is>
       </c>
       <c r="I219" s="2" t="n">
-        <v>5.6</v>
+        <v>126.03</v>
       </c>
       <c r="J219" s="2" t="inlineStr">
         <is>
@@ -26796,7 +26796,7 @@
       </c>
       <c r="K219" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:23</t>
         </is>
       </c>
     </row>
@@ -26838,7 +26838,7 @@
         </is>
       </c>
       <c r="I220" s="2" t="n">
-        <v>7.48</v>
+        <v>121.44</v>
       </c>
       <c r="J220" s="2" t="inlineStr">
         <is>
@@ -26847,7 +26847,7 @@
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:23</t>
         </is>
       </c>
     </row>
@@ -26889,7 +26889,7 @@
         </is>
       </c>
       <c r="I221" s="2" t="n">
-        <v>8.09</v>
+        <v>153.17</v>
       </c>
       <c r="J221" s="2" t="inlineStr">
         <is>
@@ -26898,7 +26898,7 @@
       </c>
       <c r="K221" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:24</t>
         </is>
       </c>
     </row>
@@ -26940,7 +26940,7 @@
         </is>
       </c>
       <c r="I222" s="2" t="n">
-        <v>6.63</v>
+        <v>232.42</v>
       </c>
       <c r="J222" s="2" t="inlineStr">
         <is>
@@ -26949,7 +26949,7 @@
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:24</t>
         </is>
       </c>
     </row>
@@ -26991,7 +26991,7 @@
         </is>
       </c>
       <c r="I223" s="2" t="n">
-        <v>8.720000000000001</v>
+        <v>159.05</v>
       </c>
       <c r="J223" s="2" t="inlineStr">
         <is>
@@ -27000,7 +27000,7 @@
       </c>
       <c r="K223" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:24</t>
         </is>
       </c>
     </row>
@@ -27042,7 +27042,7 @@
         </is>
       </c>
       <c r="I224" s="2" t="n">
-        <v>13.27</v>
+        <v>236.97</v>
       </c>
       <c r="J224" s="2" t="inlineStr">
         <is>
@@ -27051,7 +27051,7 @@
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:24</t>
         </is>
       </c>
     </row>
@@ -27093,7 +27093,7 @@
         </is>
       </c>
       <c r="I225" s="2" t="n">
-        <v>7.67</v>
+        <v>210.99</v>
       </c>
       <c r="J225" s="2" t="inlineStr">
         <is>
@@ -27102,7 +27102,7 @@
       </c>
       <c r="K225" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:24</t>
         </is>
       </c>
     </row>
@@ -27144,7 +27144,7 @@
         </is>
       </c>
       <c r="I226" s="2" t="n">
-        <v>8.039999999999999</v>
+        <v>84.5</v>
       </c>
       <c r="J226" s="2" t="inlineStr">
         <is>
@@ -27153,7 +27153,7 @@
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:24</t>
         </is>
       </c>
     </row>
@@ -27195,7 +27195,7 @@
         </is>
       </c>
       <c r="I227" s="2" t="n">
-        <v>6.69</v>
+        <v>156.6</v>
       </c>
       <c r="J227" s="2" t="inlineStr">
         <is>
@@ -27204,7 +27204,7 @@
       </c>
       <c r="K227" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:25</t>
         </is>
       </c>
     </row>
@@ -27246,7 +27246,7 @@
         </is>
       </c>
       <c r="I228" s="2" t="n">
-        <v>5.2</v>
+        <v>165.97</v>
       </c>
       <c r="J228" s="2" t="inlineStr">
         <is>
@@ -27255,7 +27255,7 @@
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:25</t>
         </is>
       </c>
     </row>
@@ -27297,7 +27297,7 @@
         </is>
       </c>
       <c r="I229" s="2" t="n">
-        <v>6.28</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="J229" s="2" t="inlineStr">
         <is>
@@ -27306,7 +27306,7 @@
       </c>
       <c r="K229" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:25</t>
         </is>
       </c>
     </row>
@@ -27348,7 +27348,7 @@
         </is>
       </c>
       <c r="I230" s="2" t="n">
-        <v>7.55</v>
+        <v>119.57</v>
       </c>
       <c r="J230" s="2" t="inlineStr">
         <is>
@@ -27357,7 +27357,7 @@
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:25</t>
         </is>
       </c>
     </row>
@@ -27399,7 +27399,7 @@
         </is>
       </c>
       <c r="I231" s="2" t="n">
-        <v>9.52</v>
+        <v>122.72</v>
       </c>
       <c r="J231" s="4" t="inlineStr">
         <is>
@@ -27408,7 +27408,7 @@
       </c>
       <c r="K231" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:25</t>
         </is>
       </c>
     </row>
@@ -27450,7 +27450,7 @@
         </is>
       </c>
       <c r="I232" s="2" t="n">
-        <v>6.17</v>
+        <v>83.33</v>
       </c>
       <c r="J232" s="2" t="inlineStr">
         <is>
@@ -27463,7 +27463,7 @@
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:25</t>
         </is>
       </c>
     </row>
@@ -27505,7 +27505,7 @@
         </is>
       </c>
       <c r="I233" s="2" t="n">
-        <v>10.95</v>
+        <v>64.5</v>
       </c>
       <c r="J233" s="4" t="inlineStr">
         <is>
@@ -27518,7 +27518,7 @@
       </c>
       <c r="K233" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:25</t>
         </is>
       </c>
     </row>
@@ -27560,7 +27560,7 @@
         </is>
       </c>
       <c r="I234" s="2" t="n">
-        <v>15.08</v>
+        <v>99.22</v>
       </c>
       <c r="J234" s="2" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:25</t>
         </is>
       </c>
     </row>
@@ -27611,7 +27611,7 @@
         </is>
       </c>
       <c r="I235" s="2" t="n">
-        <v>10.37</v>
+        <v>122.4</v>
       </c>
       <c r="J235" s="2" t="inlineStr">
         <is>
@@ -27620,7 +27620,7 @@
       </c>
       <c r="K235" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:25</t>
         </is>
       </c>
     </row>
@@ -27662,7 +27662,7 @@
         </is>
       </c>
       <c r="I236" s="2" t="n">
-        <v>9.01</v>
+        <v>213.11</v>
       </c>
       <c r="J236" s="2" t="inlineStr">
         <is>
@@ -27671,7 +27671,7 @@
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:26</t>
         </is>
       </c>
     </row>
@@ -27713,7 +27713,7 @@
         </is>
       </c>
       <c r="I237" s="2" t="n">
-        <v>10.94</v>
+        <v>229.85</v>
       </c>
       <c r="J237" s="2" t="inlineStr">
         <is>
@@ -27722,7 +27722,7 @@
       </c>
       <c r="K237" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:26</t>
         </is>
       </c>
     </row>
@@ -27764,7 +27764,7 @@
         </is>
       </c>
       <c r="I238" s="2" t="n">
-        <v>8.68</v>
+        <v>187.1</v>
       </c>
       <c r="J238" s="2" t="inlineStr">
         <is>
@@ -27773,7 +27773,7 @@
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:26</t>
         </is>
       </c>
     </row>
@@ -27815,7 +27815,7 @@
         </is>
       </c>
       <c r="I239" s="2" t="n">
-        <v>13.42</v>
+        <v>135.36</v>
       </c>
       <c r="J239" s="2" t="inlineStr">
         <is>
@@ -27824,7 +27824,7 @@
       </c>
       <c r="K239" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:26</t>
         </is>
       </c>
     </row>
@@ -27866,7 +27866,7 @@
         </is>
       </c>
       <c r="I240" s="2" t="n">
-        <v>12.12</v>
+        <v>173.2</v>
       </c>
       <c r="J240" s="2" t="inlineStr">
         <is>
@@ -27875,7 +27875,7 @@
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:26</t>
         </is>
       </c>
     </row>
@@ -27917,7 +27917,7 @@
         </is>
       </c>
       <c r="I241" s="2" t="n">
-        <v>15.19</v>
+        <v>188.88</v>
       </c>
       <c r="J241" s="4" t="inlineStr">
         <is>
@@ -27926,7 +27926,7 @@
       </c>
       <c r="K241" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:27</t>
         </is>
       </c>
     </row>
@@ -27968,7 +27968,7 @@
         </is>
       </c>
       <c r="I242" s="2" t="n">
-        <v>6.52</v>
+        <v>107.03</v>
       </c>
       <c r="J242" s="4" t="inlineStr">
         <is>
@@ -27977,7 +27977,7 @@
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:27</t>
         </is>
       </c>
     </row>
@@ -28019,7 +28019,7 @@
         </is>
       </c>
       <c r="I243" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>129.36</v>
       </c>
       <c r="J243" s="2" t="inlineStr">
         <is>
@@ -28028,7 +28028,7 @@
       </c>
       <c r="K243" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:27</t>
         </is>
       </c>
     </row>
@@ -28070,7 +28070,7 @@
         </is>
       </c>
       <c r="I244" s="2" t="n">
-        <v>6.12</v>
+        <v>258.84</v>
       </c>
       <c r="J244" s="2" t="inlineStr">
         <is>
@@ -28079,7 +28079,7 @@
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:27</t>
         </is>
       </c>
     </row>
@@ -28121,7 +28121,7 @@
         </is>
       </c>
       <c r="I245" s="2" t="n">
-        <v>5.74</v>
+        <v>241.2</v>
       </c>
       <c r="J245" s="2" t="inlineStr">
         <is>
@@ -28130,7 +28130,7 @@
       </c>
       <c r="K245" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:27</t>
         </is>
       </c>
     </row>
@@ -28172,7 +28172,7 @@
         </is>
       </c>
       <c r="I246" s="2" t="n">
-        <v>4.84</v>
+        <v>130.58</v>
       </c>
       <c r="J246" s="2" t="inlineStr">
         <is>
@@ -28181,7 +28181,7 @@
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:27</t>
         </is>
       </c>
     </row>
@@ -28223,7 +28223,7 @@
         </is>
       </c>
       <c r="I247" s="2" t="n">
-        <v>7.5</v>
+        <v>274.18</v>
       </c>
       <c r="J247" s="2" t="inlineStr">
         <is>
@@ -28232,7 +28232,7 @@
       </c>
       <c r="K247" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:28</t>
         </is>
       </c>
     </row>
@@ -28274,7 +28274,7 @@
         </is>
       </c>
       <c r="I248" s="2" t="n">
-        <v>4.18</v>
+        <v>95.44</v>
       </c>
       <c r="J248" s="2" t="inlineStr">
         <is>
@@ -28283,7 +28283,7 @@
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:28</t>
         </is>
       </c>
     </row>
@@ -28325,7 +28325,7 @@
         </is>
       </c>
       <c r="I249" s="2" t="n">
-        <v>6.95</v>
+        <v>175.98</v>
       </c>
       <c r="J249" s="2" t="inlineStr">
         <is>
@@ -28334,7 +28334,7 @@
       </c>
       <c r="K249" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:28</t>
         </is>
       </c>
     </row>
@@ -28376,7 +28376,7 @@
         </is>
       </c>
       <c r="I250" s="2" t="n">
-        <v>6.17</v>
+        <v>152.48</v>
       </c>
       <c r="J250" s="2" t="inlineStr">
         <is>
@@ -28385,7 +28385,7 @@
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:28</t>
         </is>
       </c>
     </row>
@@ -28427,7 +28427,7 @@
         </is>
       </c>
       <c r="I251" s="2" t="n">
-        <v>7.23</v>
+        <v>178.77</v>
       </c>
       <c r="J251" s="2" t="inlineStr">
         <is>
@@ -28436,7 +28436,7 @@
       </c>
       <c r="K251" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:28</t>
         </is>
       </c>
     </row>
@@ -28478,7 +28478,7 @@
         </is>
       </c>
       <c r="I252" s="2" t="n">
-        <v>5.7</v>
+        <v>137.79</v>
       </c>
       <c r="J252" s="2" t="inlineStr">
         <is>
@@ -28487,7 +28487,7 @@
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:28</t>
         </is>
       </c>
     </row>
@@ -28529,7 +28529,7 @@
         </is>
       </c>
       <c r="I253" s="2" t="n">
-        <v>5.93</v>
+        <v>119.37</v>
       </c>
       <c r="J253" s="2" t="inlineStr">
         <is>
@@ -28538,7 +28538,7 @@
       </c>
       <c r="K253" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:29</t>
         </is>
       </c>
     </row>
@@ -28580,7 +28580,7 @@
         </is>
       </c>
       <c r="I254" s="2" t="n">
-        <v>6.46</v>
+        <v>107.3</v>
       </c>
       <c r="J254" s="2" t="inlineStr">
         <is>
@@ -28589,7 +28589,7 @@
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:29</t>
         </is>
       </c>
     </row>
@@ -28631,7 +28631,7 @@
         </is>
       </c>
       <c r="I255" s="2" t="n">
-        <v>5.74</v>
+        <v>112.56</v>
       </c>
       <c r="J255" s="2" t="inlineStr">
         <is>
@@ -28640,7 +28640,7 @@
       </c>
       <c r="K255" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:29</t>
         </is>
       </c>
     </row>
@@ -28682,7 +28682,7 @@
         </is>
       </c>
       <c r="I256" s="2" t="n">
-        <v>4.69</v>
+        <v>140.08</v>
       </c>
       <c r="J256" s="2" t="inlineStr">
         <is>
@@ -28691,7 +28691,7 @@
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:29</t>
         </is>
       </c>
     </row>
@@ -28733,7 +28733,7 @@
         </is>
       </c>
       <c r="I257" s="2" t="n">
-        <v>4.46</v>
+        <v>102.33</v>
       </c>
       <c r="J257" s="2" t="inlineStr">
         <is>
@@ -28742,7 +28742,7 @@
       </c>
       <c r="K257" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:29</t>
         </is>
       </c>
     </row>
@@ -28784,7 +28784,7 @@
         </is>
       </c>
       <c r="I258" s="2" t="n">
-        <v>6.23</v>
+        <v>91.8</v>
       </c>
       <c r="J258" s="2" t="inlineStr">
         <is>
@@ -28793,7 +28793,7 @@
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:29</t>
         </is>
       </c>
     </row>
@@ -28835,7 +28835,7 @@
         </is>
       </c>
       <c r="I259" s="2" t="n">
-        <v>11.69</v>
+        <v>105.32</v>
       </c>
       <c r="J259" s="2" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
       </c>
       <c r="K259" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:29</t>
         </is>
       </c>
     </row>
@@ -28886,7 +28886,7 @@
         </is>
       </c>
       <c r="I260" s="2" t="n">
-        <v>11.68</v>
+        <v>54.65</v>
       </c>
       <c r="J260" s="2" t="inlineStr">
         <is>
@@ -28895,7 +28895,7 @@
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:29</t>
         </is>
       </c>
     </row>
@@ -28937,7 +28937,7 @@
         </is>
       </c>
       <c r="I261" s="2" t="n">
-        <v>12.52</v>
+        <v>16.87</v>
       </c>
       <c r="J261" s="2" t="inlineStr">
         <is>
@@ -28946,7 +28946,7 @@
       </c>
       <c r="K261" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:29</t>
         </is>
       </c>
     </row>
@@ -28988,7 +28988,7 @@
         </is>
       </c>
       <c r="I262" s="2" t="n">
-        <v>13.35</v>
+        <v>15.23</v>
       </c>
       <c r="J262" s="2" t="inlineStr">
         <is>
@@ -28997,7 +28997,7 @@
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:29</t>
         </is>
       </c>
     </row>
@@ -29039,7 +29039,7 @@
         </is>
       </c>
       <c r="I263" s="2" t="n">
-        <v>13.48</v>
+        <v>21.77</v>
       </c>
       <c r="J263" s="2" t="inlineStr">
         <is>
@@ -29048,7 +29048,7 @@
       </c>
       <c r="K263" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:29</t>
         </is>
       </c>
     </row>
@@ -29090,7 +29090,7 @@
         </is>
       </c>
       <c r="I264" s="2" t="n">
-        <v>12.37</v>
+        <v>15</v>
       </c>
       <c r="J264" s="2" t="inlineStr">
         <is>
@@ -29099,7 +29099,7 @@
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:29</t>
         </is>
       </c>
     </row>
@@ -29141,7 +29141,7 @@
         </is>
       </c>
       <c r="I265" s="2" t="n">
-        <v>9.99</v>
+        <v>14.44</v>
       </c>
       <c r="J265" s="2" t="inlineStr">
         <is>
@@ -29150,7 +29150,7 @@
       </c>
       <c r="K265" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:29</t>
         </is>
       </c>
     </row>
@@ -29192,7 +29192,7 @@
         </is>
       </c>
       <c r="I266" s="2" t="n">
-        <v>9.279999999999999</v>
+        <v>12.02</v>
       </c>
       <c r="J266" s="2" t="inlineStr">
         <is>
@@ -29201,7 +29201,7 @@
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:29</t>
         </is>
       </c>
     </row>
@@ -29243,7 +29243,7 @@
         </is>
       </c>
       <c r="I267" s="2" t="n">
-        <v>7.01</v>
+        <v>9</v>
       </c>
       <c r="J267" s="2" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
       </c>
       <c r="K267" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:29</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
         </is>
       </c>
       <c r="I268" s="2" t="n">
-        <v>10.87</v>
+        <v>16.12</v>
       </c>
       <c r="J268" s="2" t="inlineStr">
         <is>
@@ -29303,7 +29303,7 @@
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:29</t>
         </is>
       </c>
     </row>
@@ -29345,7 +29345,7 @@
         </is>
       </c>
       <c r="I269" s="2" t="n">
-        <v>10.61</v>
+        <v>16.41</v>
       </c>
       <c r="J269" s="4" t="inlineStr">
         <is>
@@ -29354,7 +29354,7 @@
       </c>
       <c r="K269" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:29</t>
         </is>
       </c>
     </row>
@@ -29396,7 +29396,7 @@
         </is>
       </c>
       <c r="I270" s="2" t="n">
-        <v>11.68</v>
+        <v>16.58</v>
       </c>
       <c r="J270" s="2" t="inlineStr">
         <is>
@@ -29409,7 +29409,7 @@
       </c>
       <c r="K270" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:29</t>
         </is>
       </c>
     </row>
@@ -29451,7 +29451,7 @@
         </is>
       </c>
       <c r="I271" s="2" t="n">
-        <v>12.09</v>
+        <v>17.01</v>
       </c>
       <c r="J271" s="4" t="inlineStr">
         <is>
@@ -29464,7 +29464,7 @@
       </c>
       <c r="K271" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:29</t>
         </is>
       </c>
     </row>
@@ -29506,7 +29506,7 @@
         </is>
       </c>
       <c r="I272" s="2" t="n">
-        <v>21.29</v>
+        <v>30.81</v>
       </c>
       <c r="J272" s="2" t="inlineStr">
         <is>
@@ -29515,7 +29515,7 @@
       </c>
       <c r="K272" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:30</t>
         </is>
       </c>
     </row>
@@ -29557,7 +29557,7 @@
         </is>
       </c>
       <c r="I273" s="2" t="n">
-        <v>11.94</v>
+        <v>18.54</v>
       </c>
       <c r="J273" s="2" t="inlineStr">
         <is>
@@ -29566,7 +29566,7 @@
       </c>
       <c r="K273" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:30</t>
         </is>
       </c>
     </row>
@@ -29608,7 +29608,7 @@
         </is>
       </c>
       <c r="I274" s="2" t="n">
-        <v>10.5</v>
+        <v>18.02</v>
       </c>
       <c r="J274" s="2" t="inlineStr">
         <is>
@@ -29617,7 +29617,7 @@
       </c>
       <c r="K274" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:30</t>
         </is>
       </c>
     </row>
@@ -29659,7 +29659,7 @@
         </is>
       </c>
       <c r="I275" s="2" t="n">
-        <v>10.27</v>
+        <v>16.33</v>
       </c>
       <c r="J275" s="2" t="inlineStr">
         <is>
@@ -29668,7 +29668,7 @@
       </c>
       <c r="K275" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:30</t>
         </is>
       </c>
     </row>
@@ -29710,7 +29710,7 @@
         </is>
       </c>
       <c r="I276" s="2" t="n">
-        <v>11.68</v>
+        <v>16.85</v>
       </c>
       <c r="J276" s="2" t="inlineStr">
         <is>
@@ -29719,7 +29719,7 @@
       </c>
       <c r="K276" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:30</t>
         </is>
       </c>
     </row>
@@ -29761,7 +29761,7 @@
         </is>
       </c>
       <c r="I277" s="2" t="n">
-        <v>15.07</v>
+        <v>17.07</v>
       </c>
       <c r="J277" s="2" t="inlineStr">
         <is>
@@ -29770,7 +29770,7 @@
       </c>
       <c r="K277" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:30</t>
         </is>
       </c>
     </row>
@@ -29812,7 +29812,7 @@
         </is>
       </c>
       <c r="I278" s="2" t="n">
-        <v>9.32</v>
+        <v>15.8</v>
       </c>
       <c r="J278" s="2" t="inlineStr">
         <is>
@@ -29821,7 +29821,7 @@
       </c>
       <c r="K278" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:30</t>
         </is>
       </c>
     </row>
@@ -29863,7 +29863,7 @@
         </is>
       </c>
       <c r="I279" s="2" t="n">
-        <v>23.82</v>
+        <v>47.6</v>
       </c>
       <c r="J279" s="4" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
       </c>
       <c r="K279" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:30</t>
         </is>
       </c>
     </row>
@@ -29914,7 +29914,7 @@
         </is>
       </c>
       <c r="I280" s="2" t="n">
-        <v>9.59</v>
+        <v>36.81</v>
       </c>
       <c r="J280" s="4" t="inlineStr">
         <is>
@@ -29923,7 +29923,7 @@
       </c>
       <c r="K280" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:30</t>
         </is>
       </c>
     </row>
@@ -29965,7 +29965,7 @@
         </is>
       </c>
       <c r="I281" s="2" t="n">
-        <v>12.12</v>
+        <v>74.14</v>
       </c>
       <c r="J281" s="2" t="inlineStr">
         <is>
@@ -29974,7 +29974,7 @@
       </c>
       <c r="K281" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:30</t>
         </is>
       </c>
     </row>
@@ -30016,7 +30016,7 @@
         </is>
       </c>
       <c r="I282" s="2" t="n">
-        <v>8.98</v>
+        <v>56.71</v>
       </c>
       <c r="J282" s="2" t="inlineStr">
         <is>
@@ -30025,7 +30025,7 @@
       </c>
       <c r="K282" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:30</t>
         </is>
       </c>
     </row>
@@ -30067,7 +30067,7 @@
         </is>
       </c>
       <c r="I283" s="2" t="n">
-        <v>6.14</v>
+        <v>45.31</v>
       </c>
       <c r="J283" s="2" t="inlineStr">
         <is>
@@ -30076,7 +30076,7 @@
       </c>
       <c r="K283" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:30</t>
         </is>
       </c>
     </row>
@@ -30118,7 +30118,7 @@
         </is>
       </c>
       <c r="I284" s="2" t="n">
-        <v>4.68</v>
+        <v>71.88</v>
       </c>
       <c r="J284" s="2" t="inlineStr">
         <is>
@@ -30127,7 +30127,7 @@
       </c>
       <c r="K284" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:30</t>
         </is>
       </c>
     </row>
@@ -30169,7 +30169,7 @@
         </is>
       </c>
       <c r="I285" s="2" t="n">
-        <v>8.56</v>
+        <v>200.27</v>
       </c>
       <c r="J285" s="2" t="inlineStr">
         <is>
@@ -30178,7 +30178,7 @@
       </c>
       <c r="K285" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:30</t>
         </is>
       </c>
     </row>
@@ -30220,7 +30220,7 @@
         </is>
       </c>
       <c r="I286" s="2" t="n">
-        <v>4.36</v>
+        <v>103.12</v>
       </c>
       <c r="J286" s="2" t="inlineStr">
         <is>
@@ -30229,7 +30229,7 @@
       </c>
       <c r="K286" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:30</t>
         </is>
       </c>
     </row>
@@ -30271,7 +30271,7 @@
         </is>
       </c>
       <c r="I287" s="2" t="n">
-        <v>8.039999999999999</v>
+        <v>66.08</v>
       </c>
       <c r="J287" s="2" t="inlineStr">
         <is>
@@ -30280,7 +30280,7 @@
       </c>
       <c r="K287" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:30</t>
         </is>
       </c>
     </row>
@@ -30322,7 +30322,7 @@
         </is>
       </c>
       <c r="I288" s="2" t="n">
-        <v>5.95</v>
+        <v>75.5</v>
       </c>
       <c r="J288" s="2" t="inlineStr">
         <is>
@@ -30331,7 +30331,7 @@
       </c>
       <c r="K288" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:30</t>
         </is>
       </c>
     </row>
@@ -30373,7 +30373,7 @@
         </is>
       </c>
       <c r="I289" s="2" t="n">
-        <v>7</v>
+        <v>105.81</v>
       </c>
       <c r="J289" s="2" t="inlineStr">
         <is>
@@ -30382,7 +30382,7 @@
       </c>
       <c r="K289" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:30</t>
         </is>
       </c>
     </row>
@@ -30424,7 +30424,7 @@
         </is>
       </c>
       <c r="I290" s="2" t="n">
-        <v>7.37</v>
+        <v>90.27</v>
       </c>
       <c r="J290" s="2" t="inlineStr">
         <is>
@@ -30433,7 +30433,7 @@
       </c>
       <c r="K290" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:31</t>
         </is>
       </c>
     </row>
@@ -30475,7 +30475,7 @@
         </is>
       </c>
       <c r="I291" s="2" t="n">
-        <v>7.56</v>
+        <v>58.6</v>
       </c>
       <c r="J291" s="2" t="inlineStr">
         <is>
@@ -30484,7 +30484,7 @@
       </c>
       <c r="K291" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:31</t>
         </is>
       </c>
     </row>
@@ -30526,7 +30526,7 @@
         </is>
       </c>
       <c r="I292" s="2" t="n">
-        <v>7.59</v>
+        <v>74.22</v>
       </c>
       <c r="J292" s="2" t="inlineStr">
         <is>
@@ -30535,7 +30535,7 @@
       </c>
       <c r="K292" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:31</t>
         </is>
       </c>
     </row>
@@ -30577,7 +30577,7 @@
         </is>
       </c>
       <c r="I293" s="2" t="n">
-        <v>7.15</v>
+        <v>42.09</v>
       </c>
       <c r="J293" s="2" t="inlineStr">
         <is>
@@ -30586,7 +30586,7 @@
       </c>
       <c r="K293" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:31</t>
         </is>
       </c>
     </row>
@@ -30628,7 +30628,7 @@
         </is>
       </c>
       <c r="I294" s="2" t="n">
-        <v>4.67</v>
+        <v>49.44</v>
       </c>
       <c r="J294" s="2" t="inlineStr">
         <is>
@@ -30637,7 +30637,7 @@
       </c>
       <c r="K294" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:31</t>
         </is>
       </c>
     </row>
@@ -30679,7 +30679,7 @@
         </is>
       </c>
       <c r="I295" s="2" t="n">
-        <v>4.53</v>
+        <v>53.97</v>
       </c>
       <c r="J295" s="2" t="inlineStr">
         <is>
@@ -30688,7 +30688,7 @@
       </c>
       <c r="K295" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:13</t>
+          <t>2026-08-10 17:47:31</t>
         </is>
       </c>
     </row>
@@ -30730,7 +30730,7 @@
         </is>
       </c>
       <c r="I296" s="2" t="n">
-        <v>9.119999999999999</v>
+        <v>68.36</v>
       </c>
       <c r="J296" s="2" t="inlineStr">
         <is>
@@ -30739,7 +30739,7 @@
       </c>
       <c r="K296" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:14</t>
+          <t>2026-08-10 17:47:31</t>
         </is>
       </c>
     </row>
@@ -30781,7 +30781,7 @@
         </is>
       </c>
       <c r="I297" s="2" t="n">
-        <v>10.6</v>
+        <v>51.15</v>
       </c>
       <c r="J297" s="2" t="inlineStr">
         <is>
@@ -30790,7 +30790,7 @@
       </c>
       <c r="K297" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:14</t>
+          <t>2026-08-10 17:47:31</t>
         </is>
       </c>
     </row>
@@ -30832,7 +30832,7 @@
         </is>
       </c>
       <c r="I298" s="2" t="n">
-        <v>11.64</v>
+        <v>50.21</v>
       </c>
       <c r="J298" s="2" t="inlineStr">
         <is>
@@ -30841,7 +30841,7 @@
       </c>
       <c r="K298" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:14</t>
+          <t>2026-08-10 17:47:31</t>
         </is>
       </c>
     </row>
@@ -30883,7 +30883,7 @@
         </is>
       </c>
       <c r="I299" s="2" t="n">
-        <v>9.68</v>
+        <v>137.6</v>
       </c>
       <c r="J299" s="2" t="inlineStr">
         <is>
@@ -30892,7 +30892,7 @@
       </c>
       <c r="K299" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:14</t>
+          <t>2026-08-10 17:47:31</t>
         </is>
       </c>
     </row>
@@ -30934,7 +30934,7 @@
         </is>
       </c>
       <c r="I300" s="2" t="n">
-        <v>13.08</v>
+        <v>106.4</v>
       </c>
       <c r="J300" s="2" t="inlineStr">
         <is>
@@ -30943,7 +30943,7 @@
       </c>
       <c r="K300" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:14</t>
+          <t>2026-08-10 17:47:31</t>
         </is>
       </c>
     </row>
@@ -30985,7 +30985,7 @@
         </is>
       </c>
       <c r="I301" s="2" t="n">
-        <v>11.95</v>
+        <v>81.59</v>
       </c>
       <c r="J301" s="2" t="inlineStr">
         <is>
@@ -30994,7 +30994,7 @@
       </c>
       <c r="K301" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:14</t>
+          <t>2026-08-10 17:47:31</t>
         </is>
       </c>
     </row>
@@ -31090,7 +31090,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>500 (100.0%)</t>
+          <t>499 (99.8%)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -31112,7 +31112,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>229.40 req/s</t>
+          <t>24.60 req/s</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -31134,7 +31134,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>42.69 ms</t>
+          <t>401.31 ms</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -31156,7 +31156,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>12 ms / 82 ms</t>
+          <t>48 ms / 6529 ms</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -31178,7 +31178,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>41 ms</t>
+          <t>122 ms</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -31200,7 +31200,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>54 ms</t>
+          <t>269 ms</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -31222,7 +31222,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>74 ms</t>
+          <t>5217 ms</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -31362,7 +31362,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:16</t>
+          <t>2026-08-10 17:47:52</t>
         </is>
       </c>
     </row>
@@ -31414,7 +31414,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:16</t>
+          <t>2026-08-10 17:47:52</t>
         </is>
       </c>
     </row>
@@ -31466,7 +31466,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:16</t>
+          <t>2026-08-10 17:47:52</t>
         </is>
       </c>
     </row>
@@ -31518,7 +31518,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:16</t>
+          <t>2026-08-10 17:47:52</t>
         </is>
       </c>
     </row>
@@ -31570,7 +31570,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:16</t>
+          <t>2026-08-10 17:47:52</t>
         </is>
       </c>
     </row>
@@ -31622,7 +31622,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:16</t>
+          <t>2026-08-10 17:47:52</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:16</t>
+          <t>2026-08-10 17:47:52</t>
         </is>
       </c>
     </row>
@@ -31726,7 +31726,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:16</t>
+          <t>2026-08-10 17:47:52</t>
         </is>
       </c>
     </row>
@@ -31778,7 +31778,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:16</t>
+          <t>2026-08-10 17:47:52</t>
         </is>
       </c>
     </row>
@@ -31830,7 +31830,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:16</t>
+          <t>2026-08-10 17:47:52</t>
         </is>
       </c>
     </row>
@@ -31882,7 +31882,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:16</t>
+          <t>2026-08-10 17:47:52</t>
         </is>
       </c>
     </row>
@@ -31934,7 +31934,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:16</t>
+          <t>2026-08-10 17:47:52</t>
         </is>
       </c>
     </row>
@@ -31986,7 +31986,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:16</t>
+          <t>2026-08-10 17:47:52</t>
         </is>
       </c>
     </row>
@@ -32038,7 +32038,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:16</t>
+          <t>2026-08-10 17:47:52</t>
         </is>
       </c>
     </row>
@@ -32090,7 +32090,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:44:16</t>
+          <t>2026-08-10 17:47:52</t>
         </is>
       </c>
     </row>
@@ -32110,9 +32110,9 @@
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="49" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="39" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -32206,7 +32206,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>RPS: 39.62 req/s</t>
+          <t>RPS: 22.38 req/s</t>
         </is>
       </c>
     </row>
@@ -32222,7 +32222,7 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>375</v>
+        <v>345</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -32236,7 +32236,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Success Rate: 100.00%</t>
+          <t>Success Rate: 92.00%</t>
         </is>
       </c>
     </row>
@@ -32252,21 +32252,21 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Error Rate: 0.00%</t>
+          <t>Error Rate: 8.00%</t>
         </is>
       </c>
     </row>
@@ -32283,7 +32283,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>125.98 ms</t>
+          <t>220.06 ms</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -32315,7 +32315,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18.8 ms</t>
+          <t>41.7 ms</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -32347,7 +32347,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>48.69 ms</t>
+          <t>2048.1 ms</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -32355,9 +32355,9 @@
           <t>&lt; 500 ms</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -32379,7 +32379,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2565.91 ms</t>
+          <t>2520.67 ms</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -32411,7 +32411,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>3051.21 ms</t>
+          <t>2952.82 ms</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -32443,7 +32443,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>63.65%</t>
+          <t>56.38%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -32475,7 +32475,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>59.18 MB</t>
+          <t>59.13 MB</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -32490,7 +32490,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Max RAM: 59.19 MB (+0.54 MB growth)</t>
+          <t>Max RAM: 59.16 MB (+0.71 MB growth)</t>
         </is>
       </c>
     </row>
@@ -32522,7 +32522,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Ping: 1.9 ms (mysql)</t>
+          <t>Ping: 2.0 ms (sqlite)</t>
         </is>
       </c>
     </row>
@@ -32537,19 +32537,19 @@
           <t>Overall APM Evaluation</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>🟢 PASS</t>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>APM TESTING FAILED</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>PASS / WARNING</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+          <t>APM TESTING PASSED</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>APM TESTING FAILED</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -32571,12 +32571,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Avg 16.94 ms (Min 8.12 / Max 35.88 ms)</t>
+          <t>Avg 26.23 ms (Min 12.69 / Max 47.0 ms)</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 1.58 req/s</t>
+          <t>15 reqs, 0.9 req/s</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -32603,12 +32603,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Avg 14.19 ms (Min 8.97 / Max 49.99 ms)</t>
+          <t>Avg 30.57 ms (Min 22.0 / Max 63.08 ms)</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 1.58 req/s</t>
+          <t>15 reqs, 0.9 req/s</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -32635,12 +32635,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Avg 13.24 ms (Min 9.26 / Max 18.35 ms)</t>
+          <t>Avg 57.49 ms (Min 26.46 / Max 75.86 ms)</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 1.58 req/s</t>
+          <t>15 reqs, 0.9 req/s</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -32667,12 +32667,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Avg 28.79 ms (Min 15.34 / Max 85.2 ms)</t>
+          <t>Avg 92.97 ms (Min 62.2 / Max 158.12 ms)</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 1.58 req/s</t>
+          <t>15 reqs, 0.9 req/s</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -32699,12 +32699,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Avg 25.15 ms (Min 10.77 / Max 45.68 ms)</t>
+          <t>Avg 44.23 ms (Min 22.0 / Max 73.18 ms)</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>45 reqs, 4.75 req/s</t>
+          <t>45 reqs, 2.69 req/s</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -32731,12 +32731,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Avg 13.26 ms (Min 9.71 / Max 17.5 ms)</t>
+          <t>Avg 33.22 ms (Min 17.95 / Max 42.01 ms)</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 1.58 req/s</t>
+          <t>15 reqs, 0.9 req/s</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -32763,12 +32763,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Avg 21.11 ms (Min 10.34 / Max 29.17 ms)</t>
+          <t>Avg 38.62 ms (Min 29.25 / Max 47.53 ms)</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 1.58 req/s</t>
+          <t>15 reqs, 0.9 req/s</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -32795,12 +32795,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Avg 21.44 ms (Min 17.06 / Max 36.19 ms)</t>
+          <t>Avg 65.45 ms (Min 49.66 / Max 80.43 ms)</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 1.58 req/s</t>
+          <t>15 reqs, 0.9 req/s</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -32827,12 +32827,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Avg 17.36 ms (Min 13.01 / Max 21.94 ms)</t>
+          <t>Avg 41.71 ms (Min 22.39 / Max 49.83 ms)</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 1.58 req/s</t>
+          <t>15 reqs, 0.9 req/s</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -32859,12 +32859,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Avg 18.28 ms (Min 10.66 / Max 22.9 ms)</t>
+          <t>Avg 46.55 ms (Min 37.15 / Max 58.27 ms)</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 1.58 req/s</t>
+          <t>15 reqs, 0.9 req/s</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -32891,12 +32891,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Avg 17.2 ms (Min 12.79 / Max 21.07 ms)</t>
+          <t>Avg 39.03 ms (Min 17.38 / Max 50.19 ms)</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 1.58 req/s</t>
+          <t>15 reqs, 0.9 req/s</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -32923,12 +32923,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Avg 17.73 ms (Min 14.09 / Max 21.04 ms)</t>
+          <t>Avg 36.04 ms (Min 22.0 / Max 43.54 ms)</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 1.58 req/s</t>
+          <t>15 reqs, 0.9 req/s</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -32955,12 +32955,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Avg 17.81 ms (Min 13.2 / Max 24.43 ms)</t>
+          <t>Avg 33.81 ms (Min 19.16 / Max 43.09 ms)</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 1.58 req/s</t>
+          <t>15 reqs, 0.9 req/s</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -32987,12 +32987,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Avg 17.52 ms (Min 11.67 / Max 21.7 ms)</t>
+          <t>Avg 36.29 ms (Min 21.85 / Max 47.12 ms)</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 1.58 req/s</t>
+          <t>15 reqs, 0.9 req/s</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -33019,12 +33019,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Avg 20.84 ms (Min 12.17 / Max 32.9 ms)</t>
+          <t>Avg 53.84 ms (Min 44.02 / Max 66.64 ms)</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 1.58 req/s</t>
+          <t>15 reqs, 0.9 req/s</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -33051,12 +33051,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Avg 18.06 ms (Min 13.46 / Max 22.54 ms)</t>
+          <t>Avg 49.28 ms (Min 40.48 / Max 56.28 ms)</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 1.58 req/s</t>
+          <t>15 reqs, 0.9 req/s</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -33083,12 +33083,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Avg 18.38 ms (Min 14.87 / Max 23.1 ms)</t>
+          <t>Avg 42.08 ms (Min 33.88 / Max 50.46 ms)</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 1.58 req/s</t>
+          <t>15 reqs, 0.9 req/s</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -33115,12 +33115,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Avg 20.84 ms (Min 11.63 / Max 25.94 ms)</t>
+          <t>Avg 39.2 ms (Min 30.37 / Max 52.07 ms)</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 1.58 req/s</t>
+          <t>15 reqs, 0.9 req/s</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -33147,12 +33147,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Avg 18.04 ms (Min 15.42 / Max 22.04 ms)</t>
+          <t>Avg 36.1 ms (Min 29.05 / Max 43.29 ms)</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 1.58 req/s</t>
+          <t>15 reqs, 0.9 req/s</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -33179,12 +33179,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Avg 13.66 ms (Min 10.0 / Max 21.71 ms)</t>
+          <t>Avg 31.68 ms (Min 22.77 / Max 39.47 ms)</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 1.58 req/s</t>
+          <t>15 reqs, 0.9 req/s</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -33211,12 +33211,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Avg 57.93 ms (Min 13.8 / Max 554.2 ms)</t>
+          <t>Avg 138.93 ms (Min 30.75 / Max 1602.92 ms)</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 1.58 req/s</t>
+          <t>15 reqs, 0.9 req/s</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -33243,22 +33243,22 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Avg 2481.1 ms (Min 1027.71 / Max 3051.21 ms)</t>
+          <t>Avg 2351.61 ms (Min 1346.97 / Max 2952.82 ms)</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 1.58 req/s</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+          <t>15 reqs, 0.9 req/s</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>Errors: 0 (0.0%)</t>
+          <t>Errors: 15 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -33275,22 +33275,22 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Avg 190.35 ms (Min 22.06 / Max 2405.45 ms)</t>
+          <t>Avg 2048.16 ms (Min 2037.5 / Max 2067.2 ms)</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 1.58 req/s</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+          <t>15 reqs, 0.9 req/s</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>Errors: 0 (0.0%)</t>
+          <t>Errors: 15 (100.0%)</t>
         </is>
       </c>
     </row>

--- a/SpectraGuard_Test_Report.xlsx
+++ b/SpectraGuard_Test_Report.xlsx
@@ -591,7 +591,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -5341,7 +5341,7 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
@@ -6291,7 +6291,7 @@
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J117" s="2" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J121" s="2" t="inlineStr">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J125" s="2" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J127" s="2" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J129" s="2" t="inlineStr">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J131" s="2" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J133" s="2" t="inlineStr">
@@ -7191,7 +7191,7 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J135" s="2" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J137" s="2" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
@@ -7441,7 +7441,7 @@
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J139" s="2" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J141" s="2" t="inlineStr">
@@ -7591,7 +7591,7 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
@@ -7641,7 +7641,7 @@
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J143" s="2" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J145" s="2" t="inlineStr">
@@ -7791,7 +7791,7 @@
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J147" s="2" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
@@ -7941,7 +7941,7 @@
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J149" s="2" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J151" s="2" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J152" s="2" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J153" s="2" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J154" s="2" t="inlineStr">
@@ -8241,7 +8241,7 @@
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J155" s="2" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
@@ -8341,7 +8341,7 @@
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J157" s="2" t="inlineStr">
@@ -8391,7 +8391,7 @@
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J159" s="2" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J160" s="2" t="inlineStr">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J161" s="2" t="inlineStr">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr">
@@ -8641,7 +8641,7 @@
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J163" s="2" t="inlineStr">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J164" s="2" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J165" s="2" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J166" s="2" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J167" s="2" t="inlineStr">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J168" s="2" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J169" s="2" t="inlineStr">
@@ -8991,7 +8991,7 @@
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J170" s="2" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J171" s="2" t="inlineStr">
@@ -9091,7 +9091,7 @@
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">
@@ -9141,7 +9141,7 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J173" s="2" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J174" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J175" s="2" t="inlineStr">
@@ -9291,7 +9291,7 @@
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J176" s="2" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J177" s="2" t="inlineStr">
@@ -9391,7 +9391,7 @@
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J178" s="2" t="inlineStr">
@@ -9441,7 +9441,7 @@
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J179" s="2" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J180" s="2" t="inlineStr">
@@ -9541,7 +9541,7 @@
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J181" s="2" t="inlineStr">
@@ -9591,7 +9591,7 @@
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J182" s="2" t="inlineStr">
@@ -9641,7 +9641,7 @@
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J183" s="2" t="inlineStr">
@@ -9691,7 +9691,7 @@
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J184" s="2" t="inlineStr">
@@ -9741,7 +9741,7 @@
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J185" s="2" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J186" s="2" t="inlineStr">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J187" s="2" t="inlineStr">
@@ -9891,7 +9891,7 @@
       </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J188" s="2" t="inlineStr">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J189" s="2" t="inlineStr">
@@ -9991,7 +9991,7 @@
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J190" s="2" t="inlineStr">
@@ -10041,7 +10041,7 @@
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J191" s="2" t="inlineStr">
@@ -10091,7 +10091,7 @@
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J192" s="2" t="inlineStr">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J193" s="2" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J194" s="2" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J195" s="2" t="inlineStr">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J196" s="2" t="inlineStr">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J197" s="2" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J198" s="2" t="inlineStr">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J199" s="2" t="inlineStr">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J200" s="2" t="inlineStr">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J201" s="2" t="inlineStr">
@@ -10591,7 +10591,7 @@
       </c>
       <c r="I202" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J202" s="2" t="inlineStr">
@@ -10641,7 +10641,7 @@
       </c>
       <c r="I203" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J203" s="2" t="inlineStr">
@@ -10691,7 +10691,7 @@
       </c>
       <c r="I204" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J204" s="2" t="inlineStr">
@@ -10741,7 +10741,7 @@
       </c>
       <c r="I205" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J205" s="2" t="inlineStr">
@@ -10791,7 +10791,7 @@
       </c>
       <c r="I206" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J206" s="2" t="inlineStr">
@@ -10841,7 +10841,7 @@
       </c>
       <c r="I207" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J207" s="2" t="inlineStr">
@@ -10891,7 +10891,7 @@
       </c>
       <c r="I208" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J208" s="2" t="inlineStr">
@@ -10941,7 +10941,7 @@
       </c>
       <c r="I209" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J209" s="2" t="inlineStr">
@@ -10991,7 +10991,7 @@
       </c>
       <c r="I210" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J210" s="2" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="I211" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J211" s="2" t="inlineStr">
@@ -11091,7 +11091,7 @@
       </c>
       <c r="I212" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J212" s="2" t="inlineStr">
@@ -11141,7 +11141,7 @@
       </c>
       <c r="I213" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J213" s="2" t="inlineStr">
@@ -11191,7 +11191,7 @@
       </c>
       <c r="I214" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J214" s="2" t="inlineStr">
@@ -11241,7 +11241,7 @@
       </c>
       <c r="I215" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J215" s="2" t="inlineStr">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="I216" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J216" s="2" t="inlineStr">
@@ -11341,7 +11341,7 @@
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J217" s="2" t="inlineStr">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="I218" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J218" s="2" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="I219" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J219" s="2" t="inlineStr">
@@ -11491,7 +11491,7 @@
       </c>
       <c r="I220" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J220" s="2" t="inlineStr">
@@ -11541,7 +11541,7 @@
       </c>
       <c r="I221" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J221" s="2" t="inlineStr">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="I222" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J222" s="2" t="inlineStr">
@@ -11641,7 +11641,7 @@
       </c>
       <c r="I223" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J223" s="2" t="inlineStr">
@@ -11691,7 +11691,7 @@
       </c>
       <c r="I224" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J224" s="2" t="inlineStr">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="I225" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J225" s="2" t="inlineStr">
@@ -11791,7 +11791,7 @@
       </c>
       <c r="I226" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J226" s="2" t="inlineStr">
@@ -11841,7 +11841,7 @@
       </c>
       <c r="I227" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J227" s="2" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="I228" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J228" s="2" t="inlineStr">
@@ -11941,7 +11941,7 @@
       </c>
       <c r="I229" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J229" s="2" t="inlineStr">
@@ -11991,7 +11991,7 @@
       </c>
       <c r="I230" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J230" s="2" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="I231" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J231" s="2" t="inlineStr">
@@ -12091,7 +12091,7 @@
       </c>
       <c r="I232" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J232" s="2" t="inlineStr">
@@ -12141,7 +12141,7 @@
       </c>
       <c r="I233" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J233" s="2" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="I234" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J234" s="2" t="inlineStr">
@@ -12241,7 +12241,7 @@
       </c>
       <c r="I235" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J235" s="2" t="inlineStr">
@@ -12291,7 +12291,7 @@
       </c>
       <c r="I236" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J236" s="2" t="inlineStr">
@@ -12341,7 +12341,7 @@
       </c>
       <c r="I237" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J237" s="2" t="inlineStr">
@@ -12391,7 +12391,7 @@
       </c>
       <c r="I238" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J238" s="2" t="inlineStr">
@@ -12441,7 +12441,7 @@
       </c>
       <c r="I239" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J239" s="2" t="inlineStr">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="I240" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J240" s="2" t="inlineStr">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="I241" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J241" s="2" t="inlineStr">
@@ -12591,7 +12591,7 @@
       </c>
       <c r="I242" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J242" s="2" t="inlineStr">
@@ -12641,7 +12641,7 @@
       </c>
       <c r="I243" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J243" s="2" t="inlineStr">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="I244" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J244" s="2" t="inlineStr">
@@ -12741,7 +12741,7 @@
       </c>
       <c r="I245" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J245" s="2" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="I246" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J246" s="2" t="inlineStr">
@@ -12841,7 +12841,7 @@
       </c>
       <c r="I247" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J247" s="2" t="inlineStr">
@@ -12891,7 +12891,7 @@
       </c>
       <c r="I248" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J248" s="2" t="inlineStr">
@@ -12941,7 +12941,7 @@
       </c>
       <c r="I249" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J249" s="2" t="inlineStr">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="I250" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J250" s="2" t="inlineStr">
@@ -13041,7 +13041,7 @@
       </c>
       <c r="I251" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J251" s="2" t="inlineStr">
@@ -13091,7 +13091,7 @@
       </c>
       <c r="I252" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J252" s="2" t="inlineStr">
@@ -13141,7 +13141,7 @@
       </c>
       <c r="I253" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J253" s="2" t="inlineStr">
@@ -13191,7 +13191,7 @@
       </c>
       <c r="I254" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J254" s="2" t="inlineStr">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="I255" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J255" s="2" t="inlineStr">
@@ -13291,7 +13291,7 @@
       </c>
       <c r="I256" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J256" s="2" t="inlineStr">
@@ -13341,7 +13341,7 @@
       </c>
       <c r="I257" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J257" s="2" t="inlineStr">
@@ -13391,7 +13391,7 @@
       </c>
       <c r="I258" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J258" s="2" t="inlineStr">
@@ -13441,7 +13441,7 @@
       </c>
       <c r="I259" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J259" s="2" t="inlineStr">
@@ -13491,7 +13491,7 @@
       </c>
       <c r="I260" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J260" s="2" t="inlineStr">
@@ -13541,7 +13541,7 @@
       </c>
       <c r="I261" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J261" s="2" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="I262" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J262" s="2" t="inlineStr">
@@ -13641,7 +13641,7 @@
       </c>
       <c r="I263" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J263" s="2" t="inlineStr">
@@ -13691,7 +13691,7 @@
       </c>
       <c r="I264" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J264" s="2" t="inlineStr">
@@ -13741,7 +13741,7 @@
       </c>
       <c r="I265" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J265" s="2" t="inlineStr">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="I266" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J266" s="2" t="inlineStr">
@@ -13841,7 +13841,7 @@
       </c>
       <c r="I267" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J267" s="2" t="inlineStr">
@@ -13891,7 +13891,7 @@
       </c>
       <c r="I268" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J268" s="2" t="inlineStr">
@@ -13941,7 +13941,7 @@
       </c>
       <c r="I269" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J269" s="2" t="inlineStr">
@@ -13991,7 +13991,7 @@
       </c>
       <c r="I270" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J270" s="2" t="inlineStr">
@@ -14041,7 +14041,7 @@
       </c>
       <c r="I271" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J271" s="2" t="inlineStr">
@@ -14091,7 +14091,7 @@
       </c>
       <c r="I272" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J272" s="2" t="inlineStr">
@@ -14141,7 +14141,7 @@
       </c>
       <c r="I273" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J273" s="2" t="inlineStr">
@@ -14191,7 +14191,7 @@
       </c>
       <c r="I274" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J274" s="2" t="inlineStr">
@@ -14241,7 +14241,7 @@
       </c>
       <c r="I275" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J275" s="2" t="inlineStr">
@@ -14291,7 +14291,7 @@
       </c>
       <c r="I276" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J276" s="2" t="inlineStr">
@@ -14341,7 +14341,7 @@
       </c>
       <c r="I277" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J277" s="2" t="inlineStr">
@@ -14391,7 +14391,7 @@
       </c>
       <c r="I278" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J278" s="2" t="inlineStr">
@@ -14441,7 +14441,7 @@
       </c>
       <c r="I279" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J279" s="2" t="inlineStr">
@@ -14491,7 +14491,7 @@
       </c>
       <c r="I280" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J280" s="2" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="I281" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J281" s="2" t="inlineStr">
@@ -14591,7 +14591,7 @@
       </c>
       <c r="I282" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J282" s="2" t="inlineStr">
@@ -14641,7 +14641,7 @@
       </c>
       <c r="I283" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J283" s="2" t="inlineStr">
@@ -14691,7 +14691,7 @@
       </c>
       <c r="I284" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J284" s="2" t="inlineStr">
@@ -14741,7 +14741,7 @@
       </c>
       <c r="I285" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J285" s="2" t="inlineStr">
@@ -14791,7 +14791,7 @@
       </c>
       <c r="I286" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J286" s="2" t="inlineStr">
@@ -14841,7 +14841,7 @@
       </c>
       <c r="I287" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J287" s="2" t="inlineStr">
@@ -14891,7 +14891,7 @@
       </c>
       <c r="I288" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J288" s="2" t="inlineStr">
@@ -14941,7 +14941,7 @@
       </c>
       <c r="I289" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J289" s="2" t="inlineStr">
@@ -14991,7 +14991,7 @@
       </c>
       <c r="I290" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J290" s="2" t="inlineStr">
@@ -15041,7 +15041,7 @@
       </c>
       <c r="I291" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J291" s="2" t="inlineStr">
@@ -15091,7 +15091,7 @@
       </c>
       <c r="I292" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J292" s="2" t="inlineStr">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="I293" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J293" s="2" t="inlineStr">
@@ -15191,7 +15191,7 @@
       </c>
       <c r="I294" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J294" s="2" t="inlineStr">
@@ -15241,7 +15241,7 @@
       </c>
       <c r="I295" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J295" s="2" t="inlineStr">
@@ -15291,7 +15291,7 @@
       </c>
       <c r="I296" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J296" s="2" t="inlineStr">
@@ -15341,7 +15341,7 @@
       </c>
       <c r="I297" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J297" s="2" t="inlineStr">
@@ -15391,7 +15391,7 @@
       </c>
       <c r="I298" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J298" s="2" t="inlineStr">
@@ -15441,7 +15441,7 @@
       </c>
       <c r="I299" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J299" s="2" t="inlineStr">
@@ -15491,7 +15491,7 @@
       </c>
       <c r="I300" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J300" s="2" t="inlineStr">
@@ -15541,7 +15541,7 @@
       </c>
       <c r="I301" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:00</t>
+          <t>2026-08-10 18:06:17</t>
         </is>
       </c>
       <c r="J301" s="2" t="inlineStr">
@@ -15664,7 +15664,7 @@
         <v>200</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
@@ -15672,16 +15672,16 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>59.96</v>
+        <v>2043.17</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>{"status":"ok","service":"SpectraGuard API","version":"1.0.0","environment":"dev</t>
+          <t>Simulated test fallback: HTTPConnectionPool(host='127.0.0.1', por</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:14</t>
+          <t>2026-08-10 18:06:23</t>
         </is>
       </c>
     </row>
@@ -15723,7 +15723,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>50</v>
+        <v>2217.62</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
@@ -15732,7 +15732,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:14</t>
+          <t>2026-08-10 18:06:25</t>
         </is>
       </c>
     </row>
@@ -15774,7 +15774,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>49.01</v>
+        <v>6.99</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -15787,7 +15787,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:14</t>
+          <t>2026-08-10 18:06:25</t>
         </is>
       </c>
     </row>
@@ -15829,7 +15829,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>94.76000000000001</v>
+        <v>6</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
@@ -15842,7 +15842,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:14</t>
+          <t>2026-08-10 18:06:25</t>
         </is>
       </c>
     </row>
@@ -15884,7 +15884,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>70.06999999999999</v>
+        <v>134.19</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:14</t>
+          <t>2026-08-10 18:06:25</t>
         </is>
       </c>
     </row>
@@ -15935,7 +15935,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>10022.58</v>
+        <v>7</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -15944,7 +15944,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:24</t>
+          <t>2026-08-10 18:06:25</t>
         </is>
       </c>
     </row>
@@ -15986,7 +15986,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>54.97</v>
+        <v>6</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -15995,7 +15995,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:25</t>
+          <t>2026-08-10 18:06:25</t>
         </is>
       </c>
     </row>
@@ -16029,7 +16029,7 @@
         <v>401</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>500</v>
+        <v>422</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
@@ -16037,16 +16037,16 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>10016.36</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Simulated test fallback: ('Connection aborted.', ConnectionResetE</t>
+          <t>{"detail":[{"type":"model_attributes_type","loc":["body"],"msg":"Input should be</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:35</t>
+          <t>2026-08-10 18:06:25</t>
         </is>
       </c>
     </row>
@@ -16088,7 +16088,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>10016.62</v>
+        <v>6.16</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -16097,7 +16097,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:44:45</t>
+          <t>2026-08-10 18:06:25</t>
         </is>
       </c>
     </row>
@@ -16131,7 +16131,7 @@
         <v>200</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>500</v>
+        <v>403</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
@@ -16139,16 +16139,16 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>30067.1</v>
+        <v>4.99</v>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>Simulated test fallback: ('Connection aborted.', RemoteDisconnect</t>
+          <t>{"detail":"Not authenticated"}</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:45:15</t>
+          <t>2026-08-10 18:06:25</t>
         </is>
       </c>
     </row>
@@ -16182,7 +16182,7 @@
         <v>401</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>500</v>
+        <v>403</v>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
@@ -16190,16 +16190,16 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>20021.59</v>
+        <v>5</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Simulated test fallback: HTTPConnectionPool(host='127.0.0.1', por</t>
+          <t>{"detail":"Not authenticated"}</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:45:35</t>
+          <t>2026-08-10 18:06:25</t>
         </is>
       </c>
     </row>
@@ -16233,24 +16233,24 @@
         <v>400</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>500</v>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+        <v>409</v>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>30081.43</v>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>Simulated test fallback: HTTPConnectionPool(host='127.0.0.1', por</t>
+        <v>63.37</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>{"detail":"Email already registered"}</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:46:05</t>
+          <t>2026-08-10 18:06:25</t>
         </is>
       </c>
     </row>
@@ -16284,7 +16284,7 @@
         <v>401</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>500</v>
+        <v>401</v>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
@@ -16292,16 +16292,16 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>20060.99</v>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>Simulated test fallback: HTTPConnectionPool(host='127.0.0.1', por</t>
+        <v>6.12</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>{"detail":"Invalid or expired refresh token"}</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:46:25</t>
+          <t>2026-08-10 18:06:25</t>
         </is>
       </c>
     </row>
@@ -16343,7 +16343,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>20308.08</v>
+        <v>7.27</v>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
@@ -16352,7 +16352,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:46:45</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -16394,7 +16394,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>63.47</v>
+        <v>5.9</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
@@ -16403,7 +16403,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:46:45</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -16445,7 +16445,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>47.99</v>
+        <v>6</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
@@ -16454,7 +16454,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:46:45</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -16496,7 +16496,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>42.37</v>
+        <v>7</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:46:45</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -16547,7 +16547,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>54.94</v>
+        <v>7</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -16556,7 +16556,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:46:45</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -16598,7 +16598,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>53.38</v>
+        <v>6.54</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:46:45</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -16649,7 +16649,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>2294.7</v>
+        <v>6.46</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:46:48</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -16700,7 +16700,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1990.2</v>
+        <v>6</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:46:50</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -16751,7 +16751,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>2981.35</v>
+        <v>7</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:46:53</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -16802,7 +16802,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>128.13</v>
+        <v>6</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
@@ -16811,7 +16811,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:46:53</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -16853,7 +16853,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>112.01</v>
+        <v>5.6</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:46:53</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -16904,7 +16904,7 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>92.29000000000001</v>
+        <v>7.06</v>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
@@ -16913,7 +16913,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:46:53</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -16955,7 +16955,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>88.87</v>
+        <v>5.94</v>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
@@ -16964,7 +16964,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:46:53</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -17006,7 +17006,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>62.17</v>
+        <v>6.14</v>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:46:53</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -17057,7 +17057,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>78.88</v>
+        <v>7</v>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
@@ -17066,7 +17066,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:46:53</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -17108,7 +17108,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>173.41</v>
+        <v>5.22</v>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:46:53</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -17159,7 +17159,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>108.89</v>
+        <v>7</v>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -17168,7 +17168,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:46:54</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -17210,7 +17210,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>105.22</v>
+        <v>7</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -17219,7 +17219,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:46:54</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -17261,7 +17261,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>136.74</v>
+        <v>5.08</v>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
@@ -17270,7 +17270,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:46:54</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -17312,7 +17312,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>107.81</v>
+        <v>7.25</v>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
@@ -17321,7 +17321,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:46:54</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -17363,7 +17363,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>32</v>
+        <v>5.76</v>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
@@ -17372,7 +17372,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:46:54</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -17414,7 +17414,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>181.71</v>
+        <v>4.99</v>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
@@ -17423,7 +17423,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:46:54</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -17465,7 +17465,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>14.96</v>
+        <v>5.79</v>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -17474,7 +17474,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:46:54</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -17516,7 +17516,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>16</v>
+        <v>4.78</v>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
@@ -17525,7 +17525,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:46:54</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -17567,7 +17567,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>14.11</v>
+        <v>3.72</v>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:46:54</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -17618,7 +17618,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>60.61</v>
+        <v>7.19</v>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
@@ -17627,7 +17627,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:46:54</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -17669,7 +17669,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>112.16</v>
+        <v>4.82</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
@@ -17678,7 +17678,7 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:46:54</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -17720,7 +17720,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>72.09999999999999</v>
+        <v>4.14</v>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
@@ -17733,7 +17733,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:46:54</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -17775,7 +17775,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>90.37</v>
+        <v>5</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
@@ -17788,7 +17788,7 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:46:54</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -17822,7 +17822,7 @@
         <v>200</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
@@ -17830,16 +17830,16 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>10035.18</v>
+        <v>10</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>Simulated test fallback: ('Connection aborted.', RemoteDisconnect</t>
+          <t>{"openapi":"3.1.0","info":{"title":"SpectraGuard API","description":"AI-based ph</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:04</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -17881,7 +17881,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>53.64</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:05</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -17932,7 +17932,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>26.42</v>
+        <v>5.81</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -17941,7 +17941,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:05</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -17983,7 +17983,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>24.51</v>
+        <v>7</v>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:05</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -18034,7 +18034,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
@@ -18043,7 +18043,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:05</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -18085,7 +18085,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>15</v>
+        <v>3.99</v>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:05</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -18136,7 +18136,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -18145,7 +18145,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:05</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -18187,7 +18187,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>39.95</v>
+        <v>10.7</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
@@ -18196,7 +18196,7 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:05</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -18238,7 +18238,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>22.45</v>
+        <v>6</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:05</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -18289,7 +18289,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>34.79</v>
+        <v>8.23</v>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -18298,7 +18298,7 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:05</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -18340,7 +18340,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>19.5</v>
+        <v>5.77</v>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
@@ -18349,7 +18349,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:05</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -18391,7 +18391,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>21.29</v>
+        <v>7</v>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:05</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -18442,7 +18442,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>21.56</v>
+        <v>6</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:05</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -18493,7 +18493,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>29.1</v>
+        <v>6</v>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
@@ -18502,7 +18502,7 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:05</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -18544,7 +18544,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>39.39</v>
+        <v>8.31</v>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -18553,7 +18553,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:05</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -18595,7 +18595,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>17.23</v>
+        <v>6.68</v>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
@@ -18604,7 +18604,7 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:05</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -18646,7 +18646,7 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>46.23</v>
+        <v>7.76</v>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
@@ -18655,7 +18655,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:05</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -18697,7 +18697,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>30.15</v>
+        <v>5.6</v>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
@@ -18706,7 +18706,7 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:05</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -18748,7 +18748,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>22.99</v>
+        <v>6</v>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
@@ -18757,7 +18757,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:05</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -18799,7 +18799,7 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>22.27</v>
+        <v>7</v>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
@@ -18808,7 +18808,7 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:05</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -18850,7 +18850,7 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>44.68</v>
+        <v>6</v>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
@@ -18859,7 +18859,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:05</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -18901,7 +18901,7 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>33.88</v>
+        <v>7.24</v>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
@@ -18910,7 +18910,7 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:05</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -18952,7 +18952,7 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>31.89</v>
+        <v>6.76</v>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
@@ -18961,7 +18961,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:05</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -19003,7 +19003,7 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>19.95</v>
+        <v>7.99</v>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
@@ -19012,7 +19012,7 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:05</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -19054,7 +19054,7 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>23.9</v>
+        <v>6.01</v>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
@@ -19063,7 +19063,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:05</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -19105,7 +19105,7 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:05</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -19156,7 +19156,7 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>24.28</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
@@ -19165,7 +19165,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:05</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -19207,7 +19207,7 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>27.57</v>
+        <v>5.39</v>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:05</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -19258,7 +19258,7 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>58.06</v>
+        <v>8.73</v>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
@@ -19267,7 +19267,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:05</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -19309,7 +19309,7 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>55.33</v>
+        <v>6.26</v>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
@@ -19318,7 +19318,7 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:05</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -19360,7 +19360,7 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>29.79</v>
+        <v>4</v>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
@@ -19369,7 +19369,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:05</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -19411,7 +19411,7 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>52.56</v>
+        <v>6.37</v>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -19420,7 +19420,7 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:05</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -19462,7 +19462,7 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>8.34</v>
+        <v>5</v>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
@@ -19471,7 +19471,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:05</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -19513,7 +19513,7 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
@@ -19522,7 +19522,7 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:05</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -19564,7 +19564,7 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>52.07</v>
+        <v>7</v>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:06</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -19615,7 +19615,7 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>3302.34</v>
+        <v>5.5</v>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
@@ -19624,7 +19624,7 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:09</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -19666,7 +19666,7 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>50.54</v>
+        <v>4.5</v>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
@@ -19679,7 +19679,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:09</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -19721,7 +19721,7 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>3691.7</v>
+        <v>6.08</v>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:13</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -19776,7 +19776,7 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>1970.01</v>
+        <v>10.68</v>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:15</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -19827,7 +19827,7 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>4791.97</v>
+        <v>8</v>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:19</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -19878,7 +19878,7 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>43.92</v>
+        <v>7.47</v>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
@@ -19887,7 +19887,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:19</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -19929,7 +19929,7 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>50.09</v>
+        <v>7.75</v>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
@@ -19938,7 +19938,7 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:19</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -19980,7 +19980,7 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>49.39</v>
+        <v>6.24</v>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
@@ -19989,7 +19989,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:19</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -20031,7 +20031,7 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>25.46</v>
+        <v>3.76</v>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
@@ -20040,7 +20040,7 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:19</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -20082,7 +20082,7 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>9.369999999999999</v>
+        <v>6.32</v>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
@@ -20091,7 +20091,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:20</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -20133,7 +20133,7 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>20.28</v>
+        <v>10.47</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
@@ -20142,7 +20142,7 @@
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:20</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -20184,7 +20184,7 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>13.16</v>
+        <v>8.99</v>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
@@ -20193,7 +20193,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:20</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -20235,7 +20235,7 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>25.15</v>
+        <v>7</v>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
@@ -20244,7 +20244,7 @@
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:20</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -20286,7 +20286,7 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>14.87</v>
+        <v>7</v>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
@@ -20295,7 +20295,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:20</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -20337,7 +20337,7 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>18.08</v>
+        <v>6.23</v>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
@@ -20346,7 +20346,7 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:20</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -20388,7 +20388,7 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>17.02</v>
+        <v>7.78</v>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
@@ -20397,7 +20397,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:20</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -20439,7 +20439,7 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>24</v>
+        <v>7.03</v>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
@@ -20448,7 +20448,7 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:20</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -20490,7 +20490,7 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>17.72</v>
+        <v>5.97</v>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
@@ -20499,7 +20499,7 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:20</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -20541,7 +20541,7 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>23.15</v>
+        <v>7</v>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
@@ -20550,7 +20550,7 @@
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:20</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -20592,7 +20592,7 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>16.81</v>
+        <v>7</v>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
@@ -20601,7 +20601,7 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:20</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -20643,7 +20643,7 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>15.72</v>
+        <v>8</v>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
@@ -20652,7 +20652,7 @@
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:20</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -20694,7 +20694,7 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>16.82</v>
+        <v>6</v>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
@@ -20703,7 +20703,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:20</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -20745,7 +20745,7 @@
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>16.56</v>
+        <v>5.2</v>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:20</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -20796,7 +20796,7 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>16.05</v>
+        <v>8.01</v>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:20</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -20847,7 +20847,7 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>15.96</v>
+        <v>6.52</v>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
@@ -20856,7 +20856,7 @@
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:20</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -20898,7 +20898,7 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>17.38</v>
+        <v>7.65</v>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
@@ -20907,7 +20907,7 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:20</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -20949,7 +20949,7 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>15.89</v>
+        <v>6.16</v>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
@@ -20958,7 +20958,7 @@
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:20</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -21000,7 +21000,7 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>16.67</v>
+        <v>5.5</v>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
@@ -21009,7 +21009,7 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:20</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -21051,7 +21051,7 @@
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>15.82</v>
+        <v>7.15</v>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
@@ -21060,7 +21060,7 @@
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:20</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -21102,7 +21102,7 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>20.85</v>
+        <v>5.85</v>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
@@ -21111,7 +21111,7 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:20</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -21153,7 +21153,7 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>15.55</v>
+        <v>7.8</v>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
@@ -21162,7 +21162,7 @@
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:20</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -21204,7 +21204,7 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>17.77</v>
+        <v>5.4</v>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
@@ -21213,7 +21213,7 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:20</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -21255,7 +21255,7 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>18.65</v>
+        <v>8.01</v>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:20</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -21306,7 +21306,7 @@
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>14.66</v>
+        <v>5.06</v>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:20</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -21357,7 +21357,7 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>17.25</v>
+        <v>4.14</v>
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
@@ -21366,7 +21366,7 @@
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:20</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -21408,7 +21408,7 @@
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>11.9</v>
+        <v>5</v>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
@@ -21417,7 +21417,7 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:20</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -21459,7 +21459,7 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>20.57</v>
+        <v>6.51</v>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
@@ -21468,7 +21468,7 @@
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:20</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -21510,7 +21510,7 @@
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>15.1</v>
+        <v>5.18</v>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
@@ -21519,7 +21519,7 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:20</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -21561,7 +21561,7 @@
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>14.8</v>
+        <v>5.31</v>
       </c>
       <c r="J117" s="4" t="inlineStr">
         <is>
@@ -21570,7 +21570,7 @@
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:20</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -21612,7 +21612,7 @@
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>11.36</v>
+        <v>6.32</v>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
@@ -21625,7 +21625,7 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:20</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -21667,7 +21667,7 @@
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>14.23</v>
+        <v>5.03</v>
       </c>
       <c r="J119" s="4" t="inlineStr">
         <is>
@@ -21680,7 +21680,7 @@
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:20</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -21722,7 +21722,7 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>25.94</v>
+        <v>12.33</v>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
@@ -21731,7 +21731,7 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:20</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -21773,7 +21773,7 @@
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>19.25</v>
+        <v>6.57</v>
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
@@ -21782,7 +21782,7 @@
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:20</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -21824,7 +21824,7 @@
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>15.1</v>
+        <v>9</v>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
@@ -21833,7 +21833,7 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:20</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -21875,7 +21875,7 @@
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>17.01</v>
+        <v>7.2</v>
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
@@ -21884,7 +21884,7 @@
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:20</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -21926,7 +21926,7 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>15.33</v>
+        <v>8</v>
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
@@ -21935,7 +21935,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:20</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -21977,7 +21977,7 @@
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>12.9</v>
+        <v>5</v>
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
@@ -21986,7 +21986,7 @@
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:20</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -22028,7 +22028,7 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>17.35</v>
+        <v>4</v>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
@@ -22037,7 +22037,7 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:20</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -22079,7 +22079,7 @@
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>39.39</v>
+        <v>10.77</v>
       </c>
       <c r="J127" s="4" t="inlineStr">
         <is>
@@ -22088,7 +22088,7 @@
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:20</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -22130,7 +22130,7 @@
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>24.24</v>
+        <v>6.11</v>
       </c>
       <c r="J128" s="4" t="inlineStr">
         <is>
@@ -22139,7 +22139,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:20</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -22181,7 +22181,7 @@
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>29.72</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
@@ -22190,7 +22190,7 @@
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:20</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -22232,7 +22232,7 @@
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>28.3</v>
+        <v>4.85</v>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
@@ -22241,7 +22241,7 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:20</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -22283,7 +22283,7 @@
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>21.18</v>
+        <v>8</v>
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:20</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -22334,7 +22334,7 @@
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>23.97</v>
+        <v>6</v>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
@@ -22343,7 +22343,7 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:20</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -22385,7 +22385,7 @@
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>26.39</v>
+        <v>6</v>
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
@@ -22394,7 +22394,7 @@
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:20</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -22436,7 +22436,7 @@
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>24.9</v>
+        <v>7</v>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
@@ -22445,7 +22445,7 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:20</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -22487,7 +22487,7 @@
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>24.87</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
@@ -22496,7 +22496,7 @@
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:20</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -22538,7 +22538,7 @@
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>32.8</v>
+        <v>8.6</v>
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
@@ -22547,7 +22547,7 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:20</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -22589,7 +22589,7 @@
         </is>
       </c>
       <c r="I137" s="2" t="n">
-        <v>26.01</v>
+        <v>6.96</v>
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
@@ -22598,7 +22598,7 @@
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:20</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -22640,7 +22640,7 @@
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>23.79</v>
+        <v>9.01</v>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
@@ -22649,7 +22649,7 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:20</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -22691,7 +22691,7 @@
         </is>
       </c>
       <c r="I139" s="2" t="n">
-        <v>25.21</v>
+        <v>10.47</v>
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
@@ -22700,7 +22700,7 @@
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:21</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -22742,7 +22742,7 @@
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>22.29</v>
+        <v>7.8</v>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
@@ -22751,7 +22751,7 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:21</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -22793,7 +22793,7 @@
         </is>
       </c>
       <c r="I141" s="2" t="n">
-        <v>26.26</v>
+        <v>7.01</v>
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:21</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -22844,7 +22844,7 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>20.06</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
@@ -22853,7 +22853,7 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:21</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -22895,7 +22895,7 @@
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>16.42</v>
+        <v>7.07</v>
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
@@ -22904,7 +22904,7 @@
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:21</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -22946,7 +22946,7 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>18</v>
+        <v>10.93</v>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
@@ -22955,7 +22955,7 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:21</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -22997,7 +22997,7 @@
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>27.42</v>
+        <v>7</v>
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
@@ -23006,7 +23006,7 @@
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:21</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -23048,7 +23048,7 @@
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>20.8</v>
+        <v>9.42</v>
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
@@ -23057,7 +23057,7 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:21</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -23099,7 +23099,7 @@
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>19.5</v>
+        <v>6.58</v>
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
@@ -23108,7 +23108,7 @@
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:21</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -23150,7 +23150,7 @@
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>22.91</v>
+        <v>9.34</v>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
@@ -23159,7 +23159,7 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:21</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="I149" s="2" t="n">
-        <v>19.41</v>
+        <v>6</v>
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
@@ -23210,7 +23210,7 @@
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:21</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -23252,7 +23252,7 @@
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>16.24</v>
+        <v>5.19</v>
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
@@ -23261,7 +23261,7 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:21</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -23303,7 +23303,7 @@
         </is>
       </c>
       <c r="I151" s="2" t="n">
-        <v>16.8</v>
+        <v>6.61</v>
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
@@ -23312,7 +23312,7 @@
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:21</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -23354,7 +23354,7 @@
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>9.23</v>
+        <v>5.83</v>
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
@@ -23363,7 +23363,7 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:21</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -23405,7 +23405,7 @@
         </is>
       </c>
       <c r="I153" s="2" t="n">
-        <v>11.69</v>
+        <v>7.01</v>
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:21</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -23456,7 +23456,7 @@
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>26.15</v>
+        <v>6.27</v>
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
@@ -23465,7 +23465,7 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:21</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -23507,7 +23507,7 @@
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>36.5</v>
+        <v>5.4</v>
       </c>
       <c r="J155" s="4" t="inlineStr">
         <is>
@@ -23516,7 +23516,7 @@
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:21</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -23558,7 +23558,7 @@
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>31.13</v>
+        <v>6.77</v>
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
@@ -23571,7 +23571,7 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:21</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -23613,7 +23613,7 @@
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>16.54</v>
+        <v>7.21</v>
       </c>
       <c r="J157" s="4" t="inlineStr">
         <is>
@@ -23626,7 +23626,7 @@
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:21</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -23668,7 +23668,7 @@
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>25.58</v>
+        <v>16.87</v>
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
@@ -23677,7 +23677,7 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:21</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -23719,7 +23719,7 @@
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>18.52</v>
+        <v>12.37</v>
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
@@ -23728,7 +23728,7 @@
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:21</t>
+          <t>2026-08-10 18:06:26</t>
         </is>
       </c>
     </row>
@@ -23770,7 +23770,7 @@
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>14.83</v>
+        <v>11.77</v>
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
@@ -23779,7 +23779,7 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:21</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -23821,7 +23821,7 @@
         </is>
       </c>
       <c r="I161" s="2" t="n">
-        <v>15.32</v>
+        <v>11.23</v>
       </c>
       <c r="J161" s="2" t="inlineStr">
         <is>
@@ -23830,7 +23830,7 @@
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:21</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -23872,7 +23872,7 @@
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>18.75</v>
+        <v>10.61</v>
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
@@ -23881,7 +23881,7 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:21</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -23923,7 +23923,7 @@
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>16.32</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
@@ -23932,7 +23932,7 @@
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:21</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>19.06</v>
+        <v>7.89</v>
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
@@ -23983,7 +23983,7 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:21</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -24025,7 +24025,7 @@
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>27</v>
+        <v>16.12</v>
       </c>
       <c r="J165" s="4" t="inlineStr">
         <is>
@@ -24034,7 +24034,7 @@
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:21</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -24076,7 +24076,7 @@
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>14.15</v>
+        <v>11.25</v>
       </c>
       <c r="J166" s="4" t="inlineStr">
         <is>
@@ -24085,7 +24085,7 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:21</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -24127,7 +24127,7 @@
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>20.32</v>
+        <v>10.21</v>
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
@@ -24136,7 +24136,7 @@
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:21</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -24178,7 +24178,7 @@
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>43.87</v>
+        <v>10.77</v>
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
@@ -24187,7 +24187,7 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:21</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -24229,7 +24229,7 @@
         </is>
       </c>
       <c r="I169" s="2" t="n">
-        <v>19.11</v>
+        <v>8.1</v>
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
@@ -24238,7 +24238,7 @@
       </c>
       <c r="K169" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:21</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -24280,7 +24280,7 @@
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>14.75</v>
+        <v>9.02</v>
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
@@ -24289,7 +24289,7 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:21</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -24331,7 +24331,7 @@
         </is>
       </c>
       <c r="I171" s="2" t="n">
-        <v>39.65</v>
+        <v>11.17</v>
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
@@ -24340,7 +24340,7 @@
       </c>
       <c r="K171" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:21</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -24382,7 +24382,7 @@
         </is>
       </c>
       <c r="I172" s="2" t="n">
-        <v>21.94</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
@@ -24391,7 +24391,7 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:21</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -24433,7 +24433,7 @@
         </is>
       </c>
       <c r="I173" s="2" t="n">
-        <v>42.76</v>
+        <v>9.82</v>
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
@@ -24442,7 +24442,7 @@
       </c>
       <c r="K173" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:21</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -24484,7 +24484,7 @@
         </is>
       </c>
       <c r="I174" s="2" t="n">
-        <v>35.53</v>
+        <v>9.02</v>
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
@@ -24493,7 +24493,7 @@
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:21</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -24535,7 +24535,7 @@
         </is>
       </c>
       <c r="I175" s="2" t="n">
-        <v>26.9</v>
+        <v>10.2</v>
       </c>
       <c r="J175" s="2" t="inlineStr">
         <is>
@@ -24544,7 +24544,7 @@
       </c>
       <c r="K175" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:21</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -24586,7 +24586,7 @@
         </is>
       </c>
       <c r="I176" s="2" t="n">
-        <v>19.05</v>
+        <v>8.09</v>
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
@@ -24595,7 +24595,7 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:21</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -24637,7 +24637,7 @@
         </is>
       </c>
       <c r="I177" s="2" t="n">
-        <v>34.58</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="J177" s="2" t="inlineStr">
         <is>
@@ -24646,7 +24646,7 @@
       </c>
       <c r="K177" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:21</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -24688,7 +24688,7 @@
         </is>
       </c>
       <c r="I178" s="2" t="n">
-        <v>61.99</v>
+        <v>6.47</v>
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
@@ -24697,7 +24697,7 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:21</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -24739,7 +24739,7 @@
         </is>
       </c>
       <c r="I179" s="2" t="n">
-        <v>21.28</v>
+        <v>10.28</v>
       </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
@@ -24748,7 +24748,7 @@
       </c>
       <c r="K179" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:21</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -24790,7 +24790,7 @@
         </is>
       </c>
       <c r="I180" s="2" t="n">
-        <v>19.97</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
@@ -24799,7 +24799,7 @@
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:21</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -24841,7 +24841,7 @@
         </is>
       </c>
       <c r="I181" s="2" t="n">
-        <v>13.07</v>
+        <v>8.06</v>
       </c>
       <c r="J181" s="2" t="inlineStr">
         <is>
@@ -24850,7 +24850,7 @@
       </c>
       <c r="K181" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:22</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -24892,7 +24892,7 @@
         </is>
       </c>
       <c r="I182" s="2" t="n">
-        <v>26.34</v>
+        <v>9.27</v>
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
@@ -24901,7 +24901,7 @@
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:22</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -24943,7 +24943,7 @@
         </is>
       </c>
       <c r="I183" s="2" t="n">
-        <v>19.4</v>
+        <v>8.1</v>
       </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
@@ -24952,7 +24952,7 @@
       </c>
       <c r="K183" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:22</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -24994,7 +24994,7 @@
         </is>
       </c>
       <c r="I184" s="2" t="n">
-        <v>24.33</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
@@ -25003,7 +25003,7 @@
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:22</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -25045,7 +25045,7 @@
         </is>
       </c>
       <c r="I185" s="2" t="n">
-        <v>114.63</v>
+        <v>7.61</v>
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
@@ -25054,7 +25054,7 @@
       </c>
       <c r="K185" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:22</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -25096,7 +25096,7 @@
         </is>
       </c>
       <c r="I186" s="2" t="n">
-        <v>51.73</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
@@ -25105,7 +25105,7 @@
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:22</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -25147,7 +25147,7 @@
         </is>
       </c>
       <c r="I187" s="2" t="n">
-        <v>22.39</v>
+        <v>10.11</v>
       </c>
       <c r="J187" s="2" t="inlineStr">
         <is>
@@ -25156,7 +25156,7 @@
       </c>
       <c r="K187" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:22</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -25198,7 +25198,7 @@
         </is>
       </c>
       <c r="I188" s="2" t="n">
-        <v>16.46</v>
+        <v>7.09</v>
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
@@ -25207,7 +25207,7 @@
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:22</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -25249,7 +25249,7 @@
         </is>
       </c>
       <c r="I189" s="2" t="n">
-        <v>27.04</v>
+        <v>5.95</v>
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
       </c>
       <c r="K189" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:22</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -25300,7 +25300,7 @@
         </is>
       </c>
       <c r="I190" s="2" t="n">
-        <v>11.56</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
@@ -25309,7 +25309,7 @@
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:22</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -25351,7 +25351,7 @@
         </is>
       </c>
       <c r="I191" s="2" t="n">
-        <v>12</v>
+        <v>6.66</v>
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
@@ -25360,7 +25360,7 @@
       </c>
       <c r="K191" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:22</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -25402,7 +25402,7 @@
         </is>
       </c>
       <c r="I192" s="2" t="n">
-        <v>17.18</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:22</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -25453,7 +25453,7 @@
         </is>
       </c>
       <c r="I193" s="2" t="n">
-        <v>21.32</v>
+        <v>7.22</v>
       </c>
       <c r="J193" s="4" t="inlineStr">
         <is>
@@ -25462,7 +25462,7 @@
       </c>
       <c r="K193" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:22</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -25504,7 +25504,7 @@
         </is>
       </c>
       <c r="I194" s="2" t="n">
-        <v>15.94</v>
+        <v>6.04</v>
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
@@ -25517,7 +25517,7 @@
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:22</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -25559,7 +25559,7 @@
         </is>
       </c>
       <c r="I195" s="2" t="n">
-        <v>19.63</v>
+        <v>8.83</v>
       </c>
       <c r="J195" s="4" t="inlineStr">
         <is>
@@ -25572,7 +25572,7 @@
       </c>
       <c r="K195" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:22</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -25614,7 +25614,7 @@
         </is>
       </c>
       <c r="I196" s="2" t="n">
-        <v>34</v>
+        <v>17.38</v>
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
@@ -25623,7 +25623,7 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:22</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -25665,7 +25665,7 @@
         </is>
       </c>
       <c r="I197" s="2" t="n">
-        <v>17.88</v>
+        <v>11.71</v>
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
@@ -25674,7 +25674,7 @@
       </c>
       <c r="K197" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:22</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -25716,7 +25716,7 @@
         </is>
       </c>
       <c r="I198" s="2" t="n">
-        <v>16.37</v>
+        <v>11.26</v>
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:22</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -25767,7 +25767,7 @@
         </is>
       </c>
       <c r="I199" s="2" t="n">
-        <v>17.97</v>
+        <v>9.65</v>
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
       </c>
       <c r="K199" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:22</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -25818,7 +25818,7 @@
         </is>
       </c>
       <c r="I200" s="2" t="n">
-        <v>20.19</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
@@ -25827,7 +25827,7 @@
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:22</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -25869,7 +25869,7 @@
         </is>
       </c>
       <c r="I201" s="2" t="n">
-        <v>15</v>
+        <v>7.71</v>
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
@@ -25878,7 +25878,7 @@
       </c>
       <c r="K201" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:22</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -25920,7 +25920,7 @@
         </is>
       </c>
       <c r="I202" s="2" t="n">
-        <v>23</v>
+        <v>6.02</v>
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
@@ -25929,7 +25929,7 @@
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:22</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -25971,7 +25971,7 @@
         </is>
       </c>
       <c r="I203" s="2" t="n">
-        <v>34.41</v>
+        <v>12.61</v>
       </c>
       <c r="J203" s="4" t="inlineStr">
         <is>
@@ -25980,7 +25980,7 @@
       </c>
       <c r="K203" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:22</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -26022,7 +26022,7 @@
         </is>
       </c>
       <c r="I204" s="2" t="n">
-        <v>17.86</v>
+        <v>6.23</v>
       </c>
       <c r="J204" s="4" t="inlineStr">
         <is>
@@ -26031,7 +26031,7 @@
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:22</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -26073,7 +26073,7 @@
         </is>
       </c>
       <c r="I205" s="2" t="n">
-        <v>30.64</v>
+        <v>10.38</v>
       </c>
       <c r="J205" s="2" t="inlineStr">
         <is>
@@ -26082,7 +26082,7 @@
       </c>
       <c r="K205" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:22</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -26124,7 +26124,7 @@
         </is>
       </c>
       <c r="I206" s="2" t="n">
-        <v>29.63</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="J206" s="2" t="inlineStr">
         <is>
@@ -26133,7 +26133,7 @@
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:22</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -26175,7 +26175,7 @@
         </is>
       </c>
       <c r="I207" s="2" t="n">
-        <v>39.35</v>
+        <v>7.78</v>
       </c>
       <c r="J207" s="2" t="inlineStr">
         <is>
@@ -26184,7 +26184,7 @@
       </c>
       <c r="K207" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:22</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -26226,7 +26226,7 @@
         </is>
       </c>
       <c r="I208" s="2" t="n">
-        <v>14</v>
+        <v>7.8</v>
       </c>
       <c r="J208" s="2" t="inlineStr">
         <is>
@@ -26235,7 +26235,7 @@
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:22</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -26277,7 +26277,7 @@
         </is>
       </c>
       <c r="I209" s="2" t="n">
-        <v>33.62</v>
+        <v>8.02</v>
       </c>
       <c r="J209" s="2" t="inlineStr">
         <is>
@@ -26286,7 +26286,7 @@
       </c>
       <c r="K209" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:22</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -26328,7 +26328,7 @@
         </is>
       </c>
       <c r="I210" s="2" t="n">
-        <v>74.18000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="J210" s="2" t="inlineStr">
         <is>
@@ -26337,7 +26337,7 @@
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:22</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -26379,7 +26379,7 @@
         </is>
       </c>
       <c r="I211" s="2" t="n">
-        <v>47.98</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="J211" s="2" t="inlineStr">
         <is>
@@ -26388,7 +26388,7 @@
       </c>
       <c r="K211" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:22</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -26430,7 +26430,7 @@
         </is>
       </c>
       <c r="I212" s="2" t="n">
-        <v>24.47</v>
+        <v>7.58</v>
       </c>
       <c r="J212" s="2" t="inlineStr">
         <is>
@@ -26439,7 +26439,7 @@
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:22</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -26481,7 +26481,7 @@
         </is>
       </c>
       <c r="I213" s="2" t="n">
-        <v>25.95</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="J213" s="2" t="inlineStr">
         <is>
@@ -26490,7 +26490,7 @@
       </c>
       <c r="K213" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:22</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -26532,7 +26532,7 @@
         </is>
       </c>
       <c r="I214" s="2" t="n">
-        <v>32.44</v>
+        <v>6.09</v>
       </c>
       <c r="J214" s="2" t="inlineStr">
         <is>
@@ -26541,7 +26541,7 @@
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:22</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -26583,7 +26583,7 @@
         </is>
       </c>
       <c r="I215" s="2" t="n">
-        <v>98.5</v>
+        <v>8.69</v>
       </c>
       <c r="J215" s="2" t="inlineStr">
         <is>
@@ -26592,7 +26592,7 @@
       </c>
       <c r="K215" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:23</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
         </is>
       </c>
       <c r="I216" s="2" t="n">
-        <v>267.96</v>
+        <v>7.3</v>
       </c>
       <c r="J216" s="2" t="inlineStr">
         <is>
@@ -26643,7 +26643,7 @@
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:23</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -26685,7 +26685,7 @@
         </is>
       </c>
       <c r="I217" s="2" t="n">
-        <v>134.31</v>
+        <v>7.7</v>
       </c>
       <c r="J217" s="2" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
       </c>
       <c r="K217" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:23</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -26736,7 +26736,7 @@
         </is>
       </c>
       <c r="I218" s="2" t="n">
-        <v>165.69</v>
+        <v>7.09</v>
       </c>
       <c r="J218" s="2" t="inlineStr">
         <is>
@@ -26745,7 +26745,7 @@
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:23</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -26787,7 +26787,7 @@
         </is>
       </c>
       <c r="I219" s="2" t="n">
-        <v>126.03</v>
+        <v>7.92</v>
       </c>
       <c r="J219" s="2" t="inlineStr">
         <is>
@@ -26796,7 +26796,7 @@
       </c>
       <c r="K219" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:23</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -26838,7 +26838,7 @@
         </is>
       </c>
       <c r="I220" s="2" t="n">
-        <v>121.44</v>
+        <v>7.27</v>
       </c>
       <c r="J220" s="2" t="inlineStr">
         <is>
@@ -26847,7 +26847,7 @@
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:23</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -26889,7 +26889,7 @@
         </is>
       </c>
       <c r="I221" s="2" t="n">
-        <v>153.17</v>
+        <v>7.73</v>
       </c>
       <c r="J221" s="2" t="inlineStr">
         <is>
@@ -26898,7 +26898,7 @@
       </c>
       <c r="K221" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:24</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -26940,7 +26940,7 @@
         </is>
       </c>
       <c r="I222" s="2" t="n">
-        <v>232.42</v>
+        <v>6.12</v>
       </c>
       <c r="J222" s="2" t="inlineStr">
         <is>
@@ -26949,7 +26949,7 @@
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:24</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -26991,7 +26991,7 @@
         </is>
       </c>
       <c r="I223" s="2" t="n">
-        <v>159.05</v>
+        <v>7.24</v>
       </c>
       <c r="J223" s="2" t="inlineStr">
         <is>
@@ -27000,7 +27000,7 @@
       </c>
       <c r="K223" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:24</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -27042,7 +27042,7 @@
         </is>
       </c>
       <c r="I224" s="2" t="n">
-        <v>236.97</v>
+        <v>9.07</v>
       </c>
       <c r="J224" s="2" t="inlineStr">
         <is>
@@ -27051,7 +27051,7 @@
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:24</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -27093,7 +27093,7 @@
         </is>
       </c>
       <c r="I225" s="2" t="n">
-        <v>210.99</v>
+        <v>6.55</v>
       </c>
       <c r="J225" s="2" t="inlineStr">
         <is>
@@ -27102,7 +27102,7 @@
       </c>
       <c r="K225" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:24</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -27144,7 +27144,7 @@
         </is>
       </c>
       <c r="I226" s="2" t="n">
-        <v>84.5</v>
+        <v>6.92</v>
       </c>
       <c r="J226" s="2" t="inlineStr">
         <is>
@@ -27153,7 +27153,7 @@
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:24</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -27195,7 +27195,7 @@
         </is>
       </c>
       <c r="I227" s="2" t="n">
-        <v>156.6</v>
+        <v>5.19</v>
       </c>
       <c r="J227" s="2" t="inlineStr">
         <is>
@@ -27204,7 +27204,7 @@
       </c>
       <c r="K227" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:25</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -27246,7 +27246,7 @@
         </is>
       </c>
       <c r="I228" s="2" t="n">
-        <v>165.97</v>
+        <v>4.7</v>
       </c>
       <c r="J228" s="2" t="inlineStr">
         <is>
@@ -27255,7 +27255,7 @@
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:25</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -27297,7 +27297,7 @@
         </is>
       </c>
       <c r="I229" s="2" t="n">
-        <v>70.20999999999999</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="J229" s="2" t="inlineStr">
         <is>
@@ -27306,7 +27306,7 @@
       </c>
       <c r="K229" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:25</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -27348,7 +27348,7 @@
         </is>
       </c>
       <c r="I230" s="2" t="n">
-        <v>119.57</v>
+        <v>4.97</v>
       </c>
       <c r="J230" s="2" t="inlineStr">
         <is>
@@ -27357,7 +27357,7 @@
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:25</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -27399,7 +27399,7 @@
         </is>
       </c>
       <c r="I231" s="2" t="n">
-        <v>122.72</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="J231" s="4" t="inlineStr">
         <is>
@@ -27408,7 +27408,7 @@
       </c>
       <c r="K231" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:25</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -27450,7 +27450,7 @@
         </is>
       </c>
       <c r="I232" s="2" t="n">
-        <v>83.33</v>
+        <v>5.97</v>
       </c>
       <c r="J232" s="2" t="inlineStr">
         <is>
@@ -27463,7 +27463,7 @@
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:25</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -27505,7 +27505,7 @@
         </is>
       </c>
       <c r="I233" s="2" t="n">
-        <v>64.5</v>
+        <v>5.64</v>
       </c>
       <c r="J233" s="4" t="inlineStr">
         <is>
@@ -27518,7 +27518,7 @@
       </c>
       <c r="K233" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:25</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -27560,7 +27560,7 @@
         </is>
       </c>
       <c r="I234" s="2" t="n">
-        <v>99.22</v>
+        <v>14.5</v>
       </c>
       <c r="J234" s="2" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:25</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -27611,7 +27611,7 @@
         </is>
       </c>
       <c r="I235" s="2" t="n">
-        <v>122.4</v>
+        <v>9</v>
       </c>
       <c r="J235" s="2" t="inlineStr">
         <is>
@@ -27620,7 +27620,7 @@
       </c>
       <c r="K235" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:25</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -27662,7 +27662,7 @@
         </is>
       </c>
       <c r="I236" s="2" t="n">
-        <v>213.11</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="J236" s="2" t="inlineStr">
         <is>
@@ -27671,7 +27671,7 @@
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:26</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -27713,7 +27713,7 @@
         </is>
       </c>
       <c r="I237" s="2" t="n">
-        <v>229.85</v>
+        <v>9.65</v>
       </c>
       <c r="J237" s="2" t="inlineStr">
         <is>
@@ -27722,7 +27722,7 @@
       </c>
       <c r="K237" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:26</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -27764,7 +27764,7 @@
         </is>
       </c>
       <c r="I238" s="2" t="n">
-        <v>187.1</v>
+        <v>7.1</v>
       </c>
       <c r="J238" s="2" t="inlineStr">
         <is>
@@ -27773,7 +27773,7 @@
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:26</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -27815,7 +27815,7 @@
         </is>
       </c>
       <c r="I239" s="2" t="n">
-        <v>135.36</v>
+        <v>6.71</v>
       </c>
       <c r="J239" s="2" t="inlineStr">
         <is>
@@ -27824,7 +27824,7 @@
       </c>
       <c r="K239" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:26</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -27866,7 +27866,7 @@
         </is>
       </c>
       <c r="I240" s="2" t="n">
-        <v>173.2</v>
+        <v>5.49</v>
       </c>
       <c r="J240" s="2" t="inlineStr">
         <is>
@@ -27875,7 +27875,7 @@
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:26</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -27917,7 +27917,7 @@
         </is>
       </c>
       <c r="I241" s="2" t="n">
-        <v>188.88</v>
+        <v>12.34</v>
       </c>
       <c r="J241" s="4" t="inlineStr">
         <is>
@@ -27926,7 +27926,7 @@
       </c>
       <c r="K241" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:27</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -27968,7 +27968,7 @@
         </is>
       </c>
       <c r="I242" s="2" t="n">
-        <v>107.03</v>
+        <v>6.82</v>
       </c>
       <c r="J242" s="4" t="inlineStr">
         <is>
@@ -27977,7 +27977,7 @@
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:27</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -28019,7 +28019,7 @@
         </is>
       </c>
       <c r="I243" s="2" t="n">
-        <v>129.36</v>
+        <v>9.84</v>
       </c>
       <c r="J243" s="2" t="inlineStr">
         <is>
@@ -28028,7 +28028,7 @@
       </c>
       <c r="K243" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:27</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -28070,7 +28070,7 @@
         </is>
       </c>
       <c r="I244" s="2" t="n">
-        <v>258.84</v>
+        <v>6.52</v>
       </c>
       <c r="J244" s="2" t="inlineStr">
         <is>
@@ -28079,7 +28079,7 @@
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:27</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -28121,7 +28121,7 @@
         </is>
       </c>
       <c r="I245" s="2" t="n">
-        <v>241.2</v>
+        <v>8.26</v>
       </c>
       <c r="J245" s="2" t="inlineStr">
         <is>
@@ -28130,7 +28130,7 @@
       </c>
       <c r="K245" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:27</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -28172,7 +28172,7 @@
         </is>
       </c>
       <c r="I246" s="2" t="n">
-        <v>130.58</v>
+        <v>7.04</v>
       </c>
       <c r="J246" s="2" t="inlineStr">
         <is>
@@ -28181,7 +28181,7 @@
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:27</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -28223,7 +28223,7 @@
         </is>
       </c>
       <c r="I247" s="2" t="n">
-        <v>274.18</v>
+        <v>7.96</v>
       </c>
       <c r="J247" s="2" t="inlineStr">
         <is>
@@ -28232,7 +28232,7 @@
       </c>
       <c r="K247" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:28</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -28274,7 +28274,7 @@
         </is>
       </c>
       <c r="I248" s="2" t="n">
-        <v>95.44</v>
+        <v>7.19</v>
       </c>
       <c r="J248" s="2" t="inlineStr">
         <is>
@@ -28283,7 +28283,7 @@
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:28</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -28325,7 +28325,7 @@
         </is>
       </c>
       <c r="I249" s="2" t="n">
-        <v>175.98</v>
+        <v>6.91</v>
       </c>
       <c r="J249" s="2" t="inlineStr">
         <is>
@@ -28334,7 +28334,7 @@
       </c>
       <c r="K249" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:28</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -28376,7 +28376,7 @@
         </is>
       </c>
       <c r="I250" s="2" t="n">
-        <v>152.48</v>
+        <v>8.44</v>
       </c>
       <c r="J250" s="2" t="inlineStr">
         <is>
@@ -28385,7 +28385,7 @@
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:28</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -28427,7 +28427,7 @@
         </is>
       </c>
       <c r="I251" s="2" t="n">
-        <v>178.77</v>
+        <v>6.67</v>
       </c>
       <c r="J251" s="2" t="inlineStr">
         <is>
@@ -28436,7 +28436,7 @@
       </c>
       <c r="K251" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:28</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -28478,7 +28478,7 @@
         </is>
       </c>
       <c r="I252" s="2" t="n">
-        <v>137.79</v>
+        <v>8.24</v>
       </c>
       <c r="J252" s="2" t="inlineStr">
         <is>
@@ -28487,7 +28487,7 @@
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:28</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -28529,7 +28529,7 @@
         </is>
       </c>
       <c r="I253" s="2" t="n">
-        <v>119.37</v>
+        <v>5.68</v>
       </c>
       <c r="J253" s="2" t="inlineStr">
         <is>
@@ -28538,7 +28538,7 @@
       </c>
       <c r="K253" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:29</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -28580,7 +28580,7 @@
         </is>
       </c>
       <c r="I254" s="2" t="n">
-        <v>107.3</v>
+        <v>8.34</v>
       </c>
       <c r="J254" s="2" t="inlineStr">
         <is>
@@ -28589,7 +28589,7 @@
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:29</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -28631,7 +28631,7 @@
         </is>
       </c>
       <c r="I255" s="2" t="n">
-        <v>112.56</v>
+        <v>5.82</v>
       </c>
       <c r="J255" s="2" t="inlineStr">
         <is>
@@ -28640,7 +28640,7 @@
       </c>
       <c r="K255" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:29</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -28682,7 +28682,7 @@
         </is>
       </c>
       <c r="I256" s="2" t="n">
-        <v>140.08</v>
+        <v>10</v>
       </c>
       <c r="J256" s="2" t="inlineStr">
         <is>
@@ -28691,7 +28691,7 @@
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:29</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -28733,7 +28733,7 @@
         </is>
       </c>
       <c r="I257" s="2" t="n">
-        <v>102.33</v>
+        <v>7.37</v>
       </c>
       <c r="J257" s="2" t="inlineStr">
         <is>
@@ -28742,7 +28742,7 @@
       </c>
       <c r="K257" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:29</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -28784,7 +28784,7 @@
         </is>
       </c>
       <c r="I258" s="2" t="n">
-        <v>91.8</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="J258" s="2" t="inlineStr">
         <is>
@@ -28793,7 +28793,7 @@
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:29</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -28835,7 +28835,7 @@
         </is>
       </c>
       <c r="I259" s="2" t="n">
-        <v>105.32</v>
+        <v>6</v>
       </c>
       <c r="J259" s="2" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
       </c>
       <c r="K259" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:29</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -28886,7 +28886,7 @@
         </is>
       </c>
       <c r="I260" s="2" t="n">
-        <v>54.65</v>
+        <v>7</v>
       </c>
       <c r="J260" s="2" t="inlineStr">
         <is>
@@ -28895,7 +28895,7 @@
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:29</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -28937,7 +28937,7 @@
         </is>
       </c>
       <c r="I261" s="2" t="n">
-        <v>16.87</v>
+        <v>9</v>
       </c>
       <c r="J261" s="2" t="inlineStr">
         <is>
@@ -28946,7 +28946,7 @@
       </c>
       <c r="K261" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:29</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -28988,7 +28988,7 @@
         </is>
       </c>
       <c r="I262" s="2" t="n">
-        <v>15.23</v>
+        <v>6.86</v>
       </c>
       <c r="J262" s="2" t="inlineStr">
         <is>
@@ -28997,7 +28997,7 @@
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:29</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -29039,7 +29039,7 @@
         </is>
       </c>
       <c r="I263" s="2" t="n">
-        <v>21.77</v>
+        <v>8.1</v>
       </c>
       <c r="J263" s="2" t="inlineStr">
         <is>
@@ -29048,7 +29048,7 @@
       </c>
       <c r="K263" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:29</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -29090,7 +29090,7 @@
         </is>
       </c>
       <c r="I264" s="2" t="n">
-        <v>15</v>
+        <v>5.25</v>
       </c>
       <c r="J264" s="2" t="inlineStr">
         <is>
@@ -29099,7 +29099,7 @@
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:29</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -29141,7 +29141,7 @@
         </is>
       </c>
       <c r="I265" s="2" t="n">
-        <v>14.44</v>
+        <v>8.16</v>
       </c>
       <c r="J265" s="2" t="inlineStr">
         <is>
@@ -29150,7 +29150,7 @@
       </c>
       <c r="K265" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:29</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -29192,7 +29192,7 @@
         </is>
       </c>
       <c r="I266" s="2" t="n">
-        <v>12.02</v>
+        <v>5</v>
       </c>
       <c r="J266" s="2" t="inlineStr">
         <is>
@@ -29201,7 +29201,7 @@
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:29</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -29243,7 +29243,7 @@
         </is>
       </c>
       <c r="I267" s="2" t="n">
-        <v>9</v>
+        <v>5.47</v>
       </c>
       <c r="J267" s="2" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
       </c>
       <c r="K267" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:29</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
         </is>
       </c>
       <c r="I268" s="2" t="n">
-        <v>16.12</v>
+        <v>7.3</v>
       </c>
       <c r="J268" s="2" t="inlineStr">
         <is>
@@ -29303,7 +29303,7 @@
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:29</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -29345,7 +29345,7 @@
         </is>
       </c>
       <c r="I269" s="2" t="n">
-        <v>16.41</v>
+        <v>5.94</v>
       </c>
       <c r="J269" s="4" t="inlineStr">
         <is>
@@ -29354,7 +29354,7 @@
       </c>
       <c r="K269" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:29</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -29396,7 +29396,7 @@
         </is>
       </c>
       <c r="I270" s="2" t="n">
-        <v>16.58</v>
+        <v>5.37</v>
       </c>
       <c r="J270" s="2" t="inlineStr">
         <is>
@@ -29409,7 +29409,7 @@
       </c>
       <c r="K270" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:29</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -29451,7 +29451,7 @@
         </is>
       </c>
       <c r="I271" s="2" t="n">
-        <v>17.01</v>
+        <v>7.95</v>
       </c>
       <c r="J271" s="4" t="inlineStr">
         <is>
@@ -29464,7 +29464,7 @@
       </c>
       <c r="K271" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:29</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -29506,7 +29506,7 @@
         </is>
       </c>
       <c r="I272" s="2" t="n">
-        <v>30.81</v>
+        <v>14.39</v>
       </c>
       <c r="J272" s="2" t="inlineStr">
         <is>
@@ -29515,7 +29515,7 @@
       </c>
       <c r="K272" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:30</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -29557,7 +29557,7 @@
         </is>
       </c>
       <c r="I273" s="2" t="n">
-        <v>18.54</v>
+        <v>8.23</v>
       </c>
       <c r="J273" s="2" t="inlineStr">
         <is>
@@ -29566,7 +29566,7 @@
       </c>
       <c r="K273" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:30</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -29608,7 +29608,7 @@
         </is>
       </c>
       <c r="I274" s="2" t="n">
-        <v>18.02</v>
+        <v>10.59</v>
       </c>
       <c r="J274" s="2" t="inlineStr">
         <is>
@@ -29617,7 +29617,7 @@
       </c>
       <c r="K274" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:30</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -29659,7 +29659,7 @@
         </is>
       </c>
       <c r="I275" s="2" t="n">
-        <v>16.33</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J275" s="2" t="inlineStr">
         <is>
@@ -29668,7 +29668,7 @@
       </c>
       <c r="K275" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:30</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -29710,7 +29710,7 @@
         </is>
       </c>
       <c r="I276" s="2" t="n">
-        <v>16.85</v>
+        <v>10.04</v>
       </c>
       <c r="J276" s="2" t="inlineStr">
         <is>
@@ -29719,7 +29719,7 @@
       </c>
       <c r="K276" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:30</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -29761,7 +29761,7 @@
         </is>
       </c>
       <c r="I277" s="2" t="n">
-        <v>17.07</v>
+        <v>5.4</v>
       </c>
       <c r="J277" s="2" t="inlineStr">
         <is>
@@ -29770,7 +29770,7 @@
       </c>
       <c r="K277" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:30</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -29812,7 +29812,7 @@
         </is>
       </c>
       <c r="I278" s="2" t="n">
-        <v>15.8</v>
+        <v>8</v>
       </c>
       <c r="J278" s="2" t="inlineStr">
         <is>
@@ -29821,7 +29821,7 @@
       </c>
       <c r="K278" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:30</t>
+          <t>2026-08-10 18:06:27</t>
         </is>
       </c>
     </row>
@@ -29863,7 +29863,7 @@
         </is>
       </c>
       <c r="I279" s="2" t="n">
-        <v>47.6</v>
+        <v>13.04</v>
       </c>
       <c r="J279" s="4" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
       </c>
       <c r="K279" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:30</t>
+          <t>2026-08-10 18:06:28</t>
         </is>
       </c>
     </row>
@@ -29914,7 +29914,7 @@
         </is>
       </c>
       <c r="I280" s="2" t="n">
-        <v>36.81</v>
+        <v>8.07</v>
       </c>
       <c r="J280" s="4" t="inlineStr">
         <is>
@@ -29923,7 +29923,7 @@
       </c>
       <c r="K280" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:30</t>
+          <t>2026-08-10 18:06:28</t>
         </is>
       </c>
     </row>
@@ -29965,7 +29965,7 @@
         </is>
       </c>
       <c r="I281" s="2" t="n">
-        <v>74.14</v>
+        <v>10.41</v>
       </c>
       <c r="J281" s="2" t="inlineStr">
         <is>
@@ -29974,7 +29974,7 @@
       </c>
       <c r="K281" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:30</t>
+          <t>2026-08-10 18:06:28</t>
         </is>
       </c>
     </row>
@@ -30016,7 +30016,7 @@
         </is>
       </c>
       <c r="I282" s="2" t="n">
-        <v>56.71</v>
+        <v>6.76</v>
       </c>
       <c r="J282" s="2" t="inlineStr">
         <is>
@@ -30025,7 +30025,7 @@
       </c>
       <c r="K282" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:30</t>
+          <t>2026-08-10 18:06:28</t>
         </is>
       </c>
     </row>
@@ -30067,7 +30067,7 @@
         </is>
       </c>
       <c r="I283" s="2" t="n">
-        <v>45.31</v>
+        <v>10.72</v>
       </c>
       <c r="J283" s="2" t="inlineStr">
         <is>
@@ -30076,7 +30076,7 @@
       </c>
       <c r="K283" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:30</t>
+          <t>2026-08-10 18:06:28</t>
         </is>
       </c>
     </row>
@@ -30118,7 +30118,7 @@
         </is>
       </c>
       <c r="I284" s="2" t="n">
-        <v>71.88</v>
+        <v>6.28</v>
       </c>
       <c r="J284" s="2" t="inlineStr">
         <is>
@@ -30127,7 +30127,7 @@
       </c>
       <c r="K284" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:30</t>
+          <t>2026-08-10 18:06:28</t>
         </is>
       </c>
     </row>
@@ -30169,7 +30169,7 @@
         </is>
       </c>
       <c r="I285" s="2" t="n">
-        <v>200.27</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="J285" s="2" t="inlineStr">
         <is>
@@ -30178,7 +30178,7 @@
       </c>
       <c r="K285" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:30</t>
+          <t>2026-08-10 18:06:28</t>
         </is>
       </c>
     </row>
@@ -30220,7 +30220,7 @@
         </is>
       </c>
       <c r="I286" s="2" t="n">
-        <v>103.12</v>
+        <v>7.51</v>
       </c>
       <c r="J286" s="2" t="inlineStr">
         <is>
@@ -30229,7 +30229,7 @@
       </c>
       <c r="K286" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:30</t>
+          <t>2026-08-10 18:06:28</t>
         </is>
       </c>
     </row>
@@ -30271,7 +30271,7 @@
         </is>
       </c>
       <c r="I287" s="2" t="n">
-        <v>66.08</v>
+        <v>9.56</v>
       </c>
       <c r="J287" s="2" t="inlineStr">
         <is>
@@ -30280,7 +30280,7 @@
       </c>
       <c r="K287" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:30</t>
+          <t>2026-08-10 18:06:28</t>
         </is>
       </c>
     </row>
@@ -30322,7 +30322,7 @@
         </is>
       </c>
       <c r="I288" s="2" t="n">
-        <v>75.5</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="J288" s="2" t="inlineStr">
         <is>
@@ -30331,7 +30331,7 @@
       </c>
       <c r="K288" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:30</t>
+          <t>2026-08-10 18:06:28</t>
         </is>
       </c>
     </row>
@@ -30373,7 +30373,7 @@
         </is>
       </c>
       <c r="I289" s="2" t="n">
-        <v>105.81</v>
+        <v>10.22</v>
       </c>
       <c r="J289" s="2" t="inlineStr">
         <is>
@@ -30382,7 +30382,7 @@
       </c>
       <c r="K289" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:30</t>
+          <t>2026-08-10 18:06:28</t>
         </is>
       </c>
     </row>
@@ -30424,7 +30424,7 @@
         </is>
       </c>
       <c r="I290" s="2" t="n">
-        <v>90.27</v>
+        <v>6.81</v>
       </c>
       <c r="J290" s="2" t="inlineStr">
         <is>
@@ -30433,7 +30433,7 @@
       </c>
       <c r="K290" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:31</t>
+          <t>2026-08-10 18:06:28</t>
         </is>
       </c>
     </row>
@@ -30475,7 +30475,7 @@
         </is>
       </c>
       <c r="I291" s="2" t="n">
-        <v>58.6</v>
+        <v>10.17</v>
       </c>
       <c r="J291" s="2" t="inlineStr">
         <is>
@@ -30484,7 +30484,7 @@
       </c>
       <c r="K291" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:31</t>
+          <t>2026-08-10 18:06:28</t>
         </is>
       </c>
     </row>
@@ -30526,7 +30526,7 @@
         </is>
       </c>
       <c r="I292" s="2" t="n">
-        <v>74.22</v>
+        <v>7.3</v>
       </c>
       <c r="J292" s="2" t="inlineStr">
         <is>
@@ -30535,7 +30535,7 @@
       </c>
       <c r="K292" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:31</t>
+          <t>2026-08-10 18:06:28</t>
         </is>
       </c>
     </row>
@@ -30577,7 +30577,7 @@
         </is>
       </c>
       <c r="I293" s="2" t="n">
-        <v>42.09</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="J293" s="2" t="inlineStr">
         <is>
@@ -30586,7 +30586,7 @@
       </c>
       <c r="K293" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:31</t>
+          <t>2026-08-10 18:06:28</t>
         </is>
       </c>
     </row>
@@ -30628,7 +30628,7 @@
         </is>
       </c>
       <c r="I294" s="2" t="n">
-        <v>49.44</v>
+        <v>10.7</v>
       </c>
       <c r="J294" s="2" t="inlineStr">
         <is>
@@ -30637,7 +30637,7 @@
       </c>
       <c r="K294" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:31</t>
+          <t>2026-08-10 18:06:28</t>
         </is>
       </c>
     </row>
@@ -30679,7 +30679,7 @@
         </is>
       </c>
       <c r="I295" s="2" t="n">
-        <v>53.97</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="J295" s="2" t="inlineStr">
         <is>
@@ -30688,7 +30688,7 @@
       </c>
       <c r="K295" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:31</t>
+          <t>2026-08-10 18:06:28</t>
         </is>
       </c>
     </row>
@@ -30730,7 +30730,7 @@
         </is>
       </c>
       <c r="I296" s="2" t="n">
-        <v>68.36</v>
+        <v>10.38</v>
       </c>
       <c r="J296" s="2" t="inlineStr">
         <is>
@@ -30739,7 +30739,7 @@
       </c>
       <c r="K296" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:31</t>
+          <t>2026-08-10 18:06:28</t>
         </is>
       </c>
     </row>
@@ -30781,7 +30781,7 @@
         </is>
       </c>
       <c r="I297" s="2" t="n">
-        <v>51.15</v>
+        <v>6.88</v>
       </c>
       <c r="J297" s="2" t="inlineStr">
         <is>
@@ -30790,7 +30790,7 @@
       </c>
       <c r="K297" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:31</t>
+          <t>2026-08-10 18:06:28</t>
         </is>
       </c>
     </row>
@@ -30832,7 +30832,7 @@
         </is>
       </c>
       <c r="I298" s="2" t="n">
-        <v>50.21</v>
+        <v>10.09</v>
       </c>
       <c r="J298" s="2" t="inlineStr">
         <is>
@@ -30841,7 +30841,7 @@
       </c>
       <c r="K298" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:31</t>
+          <t>2026-08-10 18:06:28</t>
         </is>
       </c>
     </row>
@@ -30883,7 +30883,7 @@
         </is>
       </c>
       <c r="I299" s="2" t="n">
-        <v>137.6</v>
+        <v>7</v>
       </c>
       <c r="J299" s="2" t="inlineStr">
         <is>
@@ -30892,7 +30892,7 @@
       </c>
       <c r="K299" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:31</t>
+          <t>2026-08-10 18:06:28</t>
         </is>
       </c>
     </row>
@@ -30934,7 +30934,7 @@
         </is>
       </c>
       <c r="I300" s="2" t="n">
-        <v>106.4</v>
+        <v>9</v>
       </c>
       <c r="J300" s="2" t="inlineStr">
         <is>
@@ -30943,7 +30943,7 @@
       </c>
       <c r="K300" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:31</t>
+          <t>2026-08-10 18:06:28</t>
         </is>
       </c>
     </row>
@@ -30985,7 +30985,7 @@
         </is>
       </c>
       <c r="I301" s="2" t="n">
-        <v>81.59</v>
+        <v>6.82</v>
       </c>
       <c r="J301" s="2" t="inlineStr">
         <is>
@@ -30994,7 +30994,7 @@
       </c>
       <c r="K301" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:31</t>
+          <t>2026-08-10 18:06:28</t>
         </is>
       </c>
     </row>
@@ -31090,7 +31090,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>499 (99.8%)</t>
+          <t>500 (100.0%)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -31112,7 +31112,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>24.60 req/s</t>
+          <t>101.13 req/s</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -31134,7 +31134,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>401.31 ms</t>
+          <t>96.98 ms</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -31156,7 +31156,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>48 ms / 6529 ms</t>
+          <t>23 ms / 202 ms</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -31178,7 +31178,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>122 ms</t>
+          <t>91 ms</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -31200,7 +31200,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>269 ms</t>
+          <t>143 ms</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -31222,7 +31222,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>5217 ms</t>
+          <t>191 ms</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -31362,7 +31362,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:52</t>
+          <t>2026-08-10 18:06:33</t>
         </is>
       </c>
     </row>
@@ -31414,7 +31414,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:52</t>
+          <t>2026-08-10 18:06:33</t>
         </is>
       </c>
     </row>
@@ -31466,7 +31466,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:52</t>
+          <t>2026-08-10 18:06:33</t>
         </is>
       </c>
     </row>
@@ -31518,7 +31518,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:52</t>
+          <t>2026-08-10 18:06:33</t>
         </is>
       </c>
     </row>
@@ -31570,7 +31570,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:52</t>
+          <t>2026-08-10 18:06:33</t>
         </is>
       </c>
     </row>
@@ -31622,7 +31622,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:52</t>
+          <t>2026-08-10 18:06:33</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:52</t>
+          <t>2026-08-10 18:06:33</t>
         </is>
       </c>
     </row>
@@ -31726,7 +31726,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:52</t>
+          <t>2026-08-10 18:06:33</t>
         </is>
       </c>
     </row>
@@ -31778,7 +31778,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:52</t>
+          <t>2026-08-10 18:06:33</t>
         </is>
       </c>
     </row>
@@ -31830,7 +31830,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:52</t>
+          <t>2026-08-10 18:06:33</t>
         </is>
       </c>
     </row>
@@ -31882,7 +31882,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:52</t>
+          <t>2026-08-10 18:06:33</t>
         </is>
       </c>
     </row>
@@ -31934,7 +31934,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:52</t>
+          <t>2026-08-10 18:06:33</t>
         </is>
       </c>
     </row>
@@ -31986,7 +31986,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:52</t>
+          <t>2026-08-10 18:06:33</t>
         </is>
       </c>
     </row>
@@ -32038,7 +32038,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:52</t>
+          <t>2026-08-10 18:06:33</t>
         </is>
       </c>
     </row>
@@ -32090,7 +32090,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:52</t>
+          <t>2026-08-10 18:06:33</t>
         </is>
       </c>
     </row>
@@ -32206,7 +32206,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>RPS: 22.38 req/s</t>
+          <t>RPS: 19.91 req/s</t>
         </is>
       </c>
     </row>
@@ -32222,7 +32222,7 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>345</v>
+        <v>369</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -32236,7 +32236,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Success Rate: 92.00%</t>
+          <t>Success Rate: 98.40%</t>
         </is>
       </c>
     </row>
@@ -32252,7 +32252,7 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -32266,7 +32266,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Error Rate: 8.00%</t>
+          <t>Error Rate: 1.60%</t>
         </is>
       </c>
     </row>
@@ -32283,7 +32283,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>220.06 ms</t>
+          <t>249.94 ms</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -32315,7 +32315,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>41.7 ms</t>
+          <t>39.42 ms</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -32347,7 +32347,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2048.1 ms</t>
+          <t>531.13 ms</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -32379,7 +32379,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2520.67 ms</t>
+          <t>5032.38 ms</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -32411,7 +32411,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2952.82 ms</t>
+          <t>5798.12 ms</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -32443,7 +32443,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>56.38%</t>
+          <t>62.78%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -32475,7 +32475,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>59.13 MB</t>
+          <t>59.02 MB</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -32490,7 +32490,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Max RAM: 59.16 MB (+0.71 MB growth)</t>
+          <t>Max RAM: 59.04 MB (+0.43 MB growth)</t>
         </is>
       </c>
     </row>
@@ -32522,7 +32522,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Ping: 2.0 ms (sqlite)</t>
+          <t>Ping: 12.0 ms (sqlite)</t>
         </is>
       </c>
     </row>
@@ -32571,12 +32571,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Avg 26.23 ms (Min 12.69 / Max 47.0 ms)</t>
+          <t>Avg 56.11 ms (Min 12.9 / Max 103.48 ms)</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 0.9 req/s</t>
+          <t>15 reqs, 0.8 req/s</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -32603,12 +32603,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Avg 30.57 ms (Min 22.0 / Max 63.08 ms)</t>
+          <t>Avg 60.57 ms (Min 41.26 / Max 83.17 ms)</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 0.9 req/s</t>
+          <t>15 reqs, 0.8 req/s</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -32635,12 +32635,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Avg 57.49 ms (Min 26.46 / Max 75.86 ms)</t>
+          <t>Avg 54.56 ms (Min 46.91 / Max 71.45 ms)</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 0.9 req/s</t>
+          <t>15 reqs, 0.8 req/s</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -32667,12 +32667,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Avg 92.97 ms (Min 62.2 / Max 158.12 ms)</t>
+          <t>Avg 89.38 ms (Min 67.34 / Max 172.23 ms)</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 0.9 req/s</t>
+          <t>15 reqs, 0.8 req/s</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -32699,12 +32699,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Avg 44.23 ms (Min 22.0 / Max 73.18 ms)</t>
+          <t>Avg 81.52 ms (Min 33.69 / Max 273.92 ms)</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>45 reqs, 2.69 req/s</t>
+          <t>45 reqs, 2.39 req/s</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -32731,12 +32731,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Avg 33.22 ms (Min 17.95 / Max 42.01 ms)</t>
+          <t>Avg 31.73 ms (Min 21.02 / Max 39.18 ms)</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 0.9 req/s</t>
+          <t>15 reqs, 0.8 req/s</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -32763,12 +32763,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Avg 38.62 ms (Min 29.25 / Max 47.53 ms)</t>
+          <t>Avg 38.72 ms (Min 28.08 / Max 49.06 ms)</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 0.9 req/s</t>
+          <t>15 reqs, 0.8 req/s</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -32795,12 +32795,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Avg 65.45 ms (Min 49.66 / Max 80.43 ms)</t>
+          <t>Avg 44.01 ms (Min 33.7 / Max 56.82 ms)</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 0.9 req/s</t>
+          <t>15 reqs, 0.8 req/s</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -32827,12 +32827,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Avg 41.71 ms (Min 22.39 / Max 49.83 ms)</t>
+          <t>Avg 32.13 ms (Min 24.48 / Max 36.71 ms)</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 0.9 req/s</t>
+          <t>15 reqs, 0.8 req/s</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -32859,12 +32859,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Avg 46.55 ms (Min 37.15 / Max 58.27 ms)</t>
+          <t>Avg 33.63 ms (Min 26.92 / Max 43.41 ms)</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 0.9 req/s</t>
+          <t>15 reqs, 0.8 req/s</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -32891,12 +32891,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Avg 39.03 ms (Min 17.38 / Max 50.19 ms)</t>
+          <t>Avg 31.78 ms (Min 26.3 / Max 37.35 ms)</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 0.9 req/s</t>
+          <t>15 reqs, 0.8 req/s</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -32923,12 +32923,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Avg 36.04 ms (Min 22.0 / Max 43.54 ms)</t>
+          <t>Avg 32.38 ms (Min 29.6 / Max 36.48 ms)</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 0.9 req/s</t>
+          <t>15 reqs, 0.8 req/s</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -32955,12 +32955,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Avg 33.81 ms (Min 19.16 / Max 43.09 ms)</t>
+          <t>Avg 32.28 ms (Min 26.91 / Max 38.26 ms)</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 0.9 req/s</t>
+          <t>15 reqs, 0.8 req/s</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -32987,12 +32987,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Avg 36.29 ms (Min 21.85 / Max 47.12 ms)</t>
+          <t>Avg 37.21 ms (Min 31.83 / Max 46.61 ms)</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 0.9 req/s</t>
+          <t>15 reqs, 0.8 req/s</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -33019,12 +33019,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Avg 53.84 ms (Min 44.02 / Max 66.64 ms)</t>
+          <t>Avg 45.38 ms (Min 36.55 / Max 51.72 ms)</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 0.9 req/s</t>
+          <t>15 reqs, 0.8 req/s</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -33051,12 +33051,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Avg 49.28 ms (Min 40.48 / Max 56.28 ms)</t>
+          <t>Avg 43.04 ms (Min 39.18 / Max 47.04 ms)</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 0.9 req/s</t>
+          <t>15 reqs, 0.8 req/s</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -33083,12 +33083,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Avg 42.08 ms (Min 33.88 / Max 50.46 ms)</t>
+          <t>Avg 39.43 ms (Min 34.23 / Max 46.25 ms)</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 0.9 req/s</t>
+          <t>15 reqs, 0.8 req/s</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -33115,12 +33115,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Avg 39.2 ms (Min 30.37 / Max 52.07 ms)</t>
+          <t>Avg 34.85 ms (Min 26.75 / Max 41.12 ms)</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 0.9 req/s</t>
+          <t>15 reqs, 0.8 req/s</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -33147,12 +33147,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Avg 36.1 ms (Min 29.05 / Max 43.29 ms)</t>
+          <t>Avg 34.03 ms (Min 26.5 / Max 42.55 ms)</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 0.9 req/s</t>
+          <t>15 reqs, 0.8 req/s</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -33179,12 +33179,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Avg 31.68 ms (Min 22.77 / Max 39.47 ms)</t>
+          <t>Avg 25.84 ms (Min 20.34 / Max 30.34 ms)</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 0.9 req/s</t>
+          <t>15 reqs, 0.8 req/s</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -33211,12 +33211,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Avg 138.93 ms (Min 30.75 / Max 1602.92 ms)</t>
+          <t>Avg 372.79 ms (Min 25.0 / Max 1747.34 ms)</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 0.9 req/s</t>
+          <t>15 reqs, 0.8 req/s</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -33243,12 +33243,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Avg 2351.61 ms (Min 1346.97 / Max 2952.82 ms)</t>
+          <t>Avg 4721.67 ms (Min 2993.66 / Max 5798.12 ms)</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 0.9 req/s</t>
+          <t>15 reqs, 0.8 req/s</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
@@ -33258,7 +33258,7 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>Errors: 15 (100.0%)</t>
+          <t>Errors: 6 (40.0%)</t>
         </is>
       </c>
     </row>
@@ -33275,22 +33275,22 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Avg 2048.16 ms (Min 2037.5 / Max 2067.2 ms)</t>
+          <t>Avg 112.4 ms (Min 29.24 / Max 1131.3 ms)</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 0.9 req/s</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+          <t>15 reqs, 0.8 req/s</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>Errors: 15 (100.0%)</t>
+          <t>Errors: 0 (0.0%)</t>
         </is>
       </c>
     </row>

--- a/SpectraGuard_Test_Report.xlsx
+++ b/SpectraGuard_Test_Report.xlsx
@@ -591,7 +591,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -5341,7 +5341,7 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
@@ -6291,7 +6291,7 @@
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J117" s="2" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J121" s="2" t="inlineStr">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J125" s="2" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J127" s="2" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J129" s="2" t="inlineStr">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J131" s="2" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J133" s="2" t="inlineStr">
@@ -7191,7 +7191,7 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J135" s="2" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J137" s="2" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
@@ -7441,7 +7441,7 @@
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J139" s="2" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J141" s="2" t="inlineStr">
@@ -7591,7 +7591,7 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
@@ -7641,7 +7641,7 @@
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J143" s="2" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J145" s="2" t="inlineStr">
@@ -7791,7 +7791,7 @@
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J147" s="2" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
@@ -7941,7 +7941,7 @@
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J149" s="2" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J151" s="2" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J152" s="2" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J153" s="2" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J154" s="2" t="inlineStr">
@@ -8241,7 +8241,7 @@
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J155" s="2" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
@@ -8341,7 +8341,7 @@
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J157" s="2" t="inlineStr">
@@ -8391,7 +8391,7 @@
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J159" s="2" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J160" s="2" t="inlineStr">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J161" s="2" t="inlineStr">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr">
@@ -8641,7 +8641,7 @@
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J163" s="2" t="inlineStr">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J164" s="2" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J165" s="2" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J166" s="2" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J167" s="2" t="inlineStr">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J168" s="2" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J169" s="2" t="inlineStr">
@@ -8991,7 +8991,7 @@
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J170" s="2" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J171" s="2" t="inlineStr">
@@ -9091,7 +9091,7 @@
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">
@@ -9141,7 +9141,7 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J173" s="2" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J174" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J175" s="2" t="inlineStr">
@@ -9291,7 +9291,7 @@
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J176" s="2" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J177" s="2" t="inlineStr">
@@ -9391,7 +9391,7 @@
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J178" s="2" t="inlineStr">
@@ -9441,7 +9441,7 @@
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J179" s="2" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J180" s="2" t="inlineStr">
@@ -9541,7 +9541,7 @@
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J181" s="2" t="inlineStr">
@@ -9591,7 +9591,7 @@
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J182" s="2" t="inlineStr">
@@ -9641,7 +9641,7 @@
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J183" s="2" t="inlineStr">
@@ -9691,7 +9691,7 @@
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J184" s="2" t="inlineStr">
@@ -9741,7 +9741,7 @@
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J185" s="2" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J186" s="2" t="inlineStr">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J187" s="2" t="inlineStr">
@@ -9891,7 +9891,7 @@
       </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J188" s="2" t="inlineStr">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J189" s="2" t="inlineStr">
@@ -9991,7 +9991,7 @@
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J190" s="2" t="inlineStr">
@@ -10041,7 +10041,7 @@
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J191" s="2" t="inlineStr">
@@ -10091,7 +10091,7 @@
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J192" s="2" t="inlineStr">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J193" s="2" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J194" s="2" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J195" s="2" t="inlineStr">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J196" s="2" t="inlineStr">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J197" s="2" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J198" s="2" t="inlineStr">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J199" s="2" t="inlineStr">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J200" s="2" t="inlineStr">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J201" s="2" t="inlineStr">
@@ -10591,7 +10591,7 @@
       </c>
       <c r="I202" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J202" s="2" t="inlineStr">
@@ -10641,7 +10641,7 @@
       </c>
       <c r="I203" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J203" s="2" t="inlineStr">
@@ -10691,7 +10691,7 @@
       </c>
       <c r="I204" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J204" s="2" t="inlineStr">
@@ -10741,7 +10741,7 @@
       </c>
       <c r="I205" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J205" s="2" t="inlineStr">
@@ -10791,7 +10791,7 @@
       </c>
       <c r="I206" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J206" s="2" t="inlineStr">
@@ -10841,7 +10841,7 @@
       </c>
       <c r="I207" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J207" s="2" t="inlineStr">
@@ -10891,7 +10891,7 @@
       </c>
       <c r="I208" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J208" s="2" t="inlineStr">
@@ -10941,7 +10941,7 @@
       </c>
       <c r="I209" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J209" s="2" t="inlineStr">
@@ -10991,7 +10991,7 @@
       </c>
       <c r="I210" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J210" s="2" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="I211" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J211" s="2" t="inlineStr">
@@ -11091,7 +11091,7 @@
       </c>
       <c r="I212" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J212" s="2" t="inlineStr">
@@ -11141,7 +11141,7 @@
       </c>
       <c r="I213" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J213" s="2" t="inlineStr">
@@ -11191,7 +11191,7 @@
       </c>
       <c r="I214" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J214" s="2" t="inlineStr">
@@ -11241,7 +11241,7 @@
       </c>
       <c r="I215" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J215" s="2" t="inlineStr">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="I216" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J216" s="2" t="inlineStr">
@@ -11341,7 +11341,7 @@
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J217" s="2" t="inlineStr">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="I218" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J218" s="2" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="I219" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J219" s="2" t="inlineStr">
@@ -11491,7 +11491,7 @@
       </c>
       <c r="I220" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J220" s="2" t="inlineStr">
@@ -11541,7 +11541,7 @@
       </c>
       <c r="I221" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J221" s="2" t="inlineStr">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="I222" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J222" s="2" t="inlineStr">
@@ -11641,7 +11641,7 @@
       </c>
       <c r="I223" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J223" s="2" t="inlineStr">
@@ -11691,7 +11691,7 @@
       </c>
       <c r="I224" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J224" s="2" t="inlineStr">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="I225" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J225" s="2" t="inlineStr">
@@ -11791,7 +11791,7 @@
       </c>
       <c r="I226" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J226" s="2" t="inlineStr">
@@ -11841,7 +11841,7 @@
       </c>
       <c r="I227" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J227" s="2" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="I228" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J228" s="2" t="inlineStr">
@@ -11941,7 +11941,7 @@
       </c>
       <c r="I229" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J229" s="2" t="inlineStr">
@@ -11991,7 +11991,7 @@
       </c>
       <c r="I230" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J230" s="2" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="I231" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J231" s="2" t="inlineStr">
@@ -12091,7 +12091,7 @@
       </c>
       <c r="I232" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J232" s="2" t="inlineStr">
@@ -12141,7 +12141,7 @@
       </c>
       <c r="I233" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J233" s="2" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="I234" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J234" s="2" t="inlineStr">
@@ -12241,7 +12241,7 @@
       </c>
       <c r="I235" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J235" s="2" t="inlineStr">
@@ -12291,7 +12291,7 @@
       </c>
       <c r="I236" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J236" s="2" t="inlineStr">
@@ -12341,7 +12341,7 @@
       </c>
       <c r="I237" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J237" s="2" t="inlineStr">
@@ -12391,7 +12391,7 @@
       </c>
       <c r="I238" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J238" s="2" t="inlineStr">
@@ -12441,7 +12441,7 @@
       </c>
       <c r="I239" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J239" s="2" t="inlineStr">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="I240" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J240" s="2" t="inlineStr">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="I241" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J241" s="2" t="inlineStr">
@@ -12591,7 +12591,7 @@
       </c>
       <c r="I242" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J242" s="2" t="inlineStr">
@@ -12641,7 +12641,7 @@
       </c>
       <c r="I243" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J243" s="2" t="inlineStr">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="I244" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J244" s="2" t="inlineStr">
@@ -12741,7 +12741,7 @@
       </c>
       <c r="I245" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J245" s="2" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="I246" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J246" s="2" t="inlineStr">
@@ -12841,7 +12841,7 @@
       </c>
       <c r="I247" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J247" s="2" t="inlineStr">
@@ -12891,7 +12891,7 @@
       </c>
       <c r="I248" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J248" s="2" t="inlineStr">
@@ -12941,7 +12941,7 @@
       </c>
       <c r="I249" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J249" s="2" t="inlineStr">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="I250" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J250" s="2" t="inlineStr">
@@ -13041,7 +13041,7 @@
       </c>
       <c r="I251" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J251" s="2" t="inlineStr">
@@ -13091,7 +13091,7 @@
       </c>
       <c r="I252" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J252" s="2" t="inlineStr">
@@ -13141,7 +13141,7 @@
       </c>
       <c r="I253" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J253" s="2" t="inlineStr">
@@ -13191,7 +13191,7 @@
       </c>
       <c r="I254" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J254" s="2" t="inlineStr">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="I255" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J255" s="2" t="inlineStr">
@@ -13291,7 +13291,7 @@
       </c>
       <c r="I256" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J256" s="2" t="inlineStr">
@@ -13341,7 +13341,7 @@
       </c>
       <c r="I257" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J257" s="2" t="inlineStr">
@@ -13391,7 +13391,7 @@
       </c>
       <c r="I258" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J258" s="2" t="inlineStr">
@@ -13441,7 +13441,7 @@
       </c>
       <c r="I259" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J259" s="2" t="inlineStr">
@@ -13491,7 +13491,7 @@
       </c>
       <c r="I260" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J260" s="2" t="inlineStr">
@@ -13541,7 +13541,7 @@
       </c>
       <c r="I261" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J261" s="2" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="I262" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J262" s="2" t="inlineStr">
@@ -13641,7 +13641,7 @@
       </c>
       <c r="I263" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J263" s="2" t="inlineStr">
@@ -13691,7 +13691,7 @@
       </c>
       <c r="I264" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J264" s="2" t="inlineStr">
@@ -13741,7 +13741,7 @@
       </c>
       <c r="I265" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J265" s="2" t="inlineStr">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="I266" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J266" s="2" t="inlineStr">
@@ -13841,7 +13841,7 @@
       </c>
       <c r="I267" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J267" s="2" t="inlineStr">
@@ -13891,7 +13891,7 @@
       </c>
       <c r="I268" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J268" s="2" t="inlineStr">
@@ -13941,7 +13941,7 @@
       </c>
       <c r="I269" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J269" s="2" t="inlineStr">
@@ -13991,7 +13991,7 @@
       </c>
       <c r="I270" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J270" s="2" t="inlineStr">
@@ -14041,7 +14041,7 @@
       </c>
       <c r="I271" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J271" s="2" t="inlineStr">
@@ -14091,7 +14091,7 @@
       </c>
       <c r="I272" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J272" s="2" t="inlineStr">
@@ -14141,7 +14141,7 @@
       </c>
       <c r="I273" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J273" s="2" t="inlineStr">
@@ -14191,7 +14191,7 @@
       </c>
       <c r="I274" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J274" s="2" t="inlineStr">
@@ -14241,7 +14241,7 @@
       </c>
       <c r="I275" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J275" s="2" t="inlineStr">
@@ -14291,7 +14291,7 @@
       </c>
       <c r="I276" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J276" s="2" t="inlineStr">
@@ -14341,7 +14341,7 @@
       </c>
       <c r="I277" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J277" s="2" t="inlineStr">
@@ -14391,7 +14391,7 @@
       </c>
       <c r="I278" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J278" s="2" t="inlineStr">
@@ -14441,7 +14441,7 @@
       </c>
       <c r="I279" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J279" s="2" t="inlineStr">
@@ -14491,7 +14491,7 @@
       </c>
       <c r="I280" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J280" s="2" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="I281" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J281" s="2" t="inlineStr">
@@ -14591,7 +14591,7 @@
       </c>
       <c r="I282" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J282" s="2" t="inlineStr">
@@ -14641,7 +14641,7 @@
       </c>
       <c r="I283" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J283" s="2" t="inlineStr">
@@ -14691,7 +14691,7 @@
       </c>
       <c r="I284" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J284" s="2" t="inlineStr">
@@ -14741,7 +14741,7 @@
       </c>
       <c r="I285" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J285" s="2" t="inlineStr">
@@ -14791,7 +14791,7 @@
       </c>
       <c r="I286" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J286" s="2" t="inlineStr">
@@ -14841,7 +14841,7 @@
       </c>
       <c r="I287" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J287" s="2" t="inlineStr">
@@ -14891,7 +14891,7 @@
       </c>
       <c r="I288" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J288" s="2" t="inlineStr">
@@ -14941,7 +14941,7 @@
       </c>
       <c r="I289" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J289" s="2" t="inlineStr">
@@ -14991,7 +14991,7 @@
       </c>
       <c r="I290" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J290" s="2" t="inlineStr">
@@ -15041,7 +15041,7 @@
       </c>
       <c r="I291" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J291" s="2" t="inlineStr">
@@ -15091,7 +15091,7 @@
       </c>
       <c r="I292" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J292" s="2" t="inlineStr">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="I293" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J293" s="2" t="inlineStr">
@@ -15191,7 +15191,7 @@
       </c>
       <c r="I294" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J294" s="2" t="inlineStr">
@@ -15241,7 +15241,7 @@
       </c>
       <c r="I295" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J295" s="2" t="inlineStr">
@@ -15291,7 +15291,7 @@
       </c>
       <c r="I296" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J296" s="2" t="inlineStr">
@@ -15341,7 +15341,7 @@
       </c>
       <c r="I297" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J297" s="2" t="inlineStr">
@@ -15391,7 +15391,7 @@
       </c>
       <c r="I298" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J298" s="2" t="inlineStr">
@@ -15441,7 +15441,7 @@
       </c>
       <c r="I299" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J299" s="2" t="inlineStr">
@@ -15491,7 +15491,7 @@
       </c>
       <c r="I300" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J300" s="2" t="inlineStr">
@@ -15541,7 +15541,7 @@
       </c>
       <c r="I301" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:17</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
       <c r="J301" s="2" t="inlineStr">
@@ -15664,7 +15664,7 @@
         <v>200</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
@@ -15672,16 +15672,16 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>2043.17</v>
+        <v>10</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Simulated test fallback: HTTPConnectionPool(host='127.0.0.1', por</t>
+          <t>{"status":"ok","service":"SpectraGuard API","version":"1.0.0","environment":"dev</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:23</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
     </row>
@@ -15723,7 +15723,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>2217.62</v>
+        <v>19.15</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
@@ -15732,7 +15732,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:25</t>
+          <t>2026-08-10 22:52:00</t>
         </is>
       </c>
     </row>
@@ -15774,7 +15774,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>6.99</v>
+        <v>794.83</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -15787,7 +15787,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:25</t>
+          <t>2026-08-10 22:52:01</t>
         </is>
       </c>
     </row>
@@ -15829,7 +15829,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>6</v>
+        <v>186.58</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
@@ -15842,7 +15842,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:25</t>
+          <t>2026-08-10 22:52:01</t>
         </is>
       </c>
     </row>
@@ -15884,7 +15884,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>134.19</v>
+        <v>280.72</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:25</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -15935,7 +15935,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>7</v>
+        <v>6.82</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -15944,7 +15944,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:25</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -15986,7 +15986,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -15995,7 +15995,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:25</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -16037,7 +16037,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>8.220000000000001</v>
+        <v>6</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:25</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -16088,7 +16088,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>6.16</v>
+        <v>5.23</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -16097,7 +16097,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:25</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -16139,7 +16139,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>4.99</v>
+        <v>2.77</v>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
@@ -16148,7 +16148,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:25</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -16190,7 +16190,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -16199,7 +16199,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:25</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -16241,7 +16241,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>63.37</v>
+        <v>235.86</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
@@ -16250,7 +16250,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:25</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -16292,7 +16292,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>6.12</v>
+        <v>6</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:25</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -16343,7 +16343,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>7.27</v>
+        <v>6</v>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
@@ -16352,7 +16352,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -16394,7 +16394,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>5.9</v>
+        <v>7.19</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
@@ -16403,7 +16403,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -16445,7 +16445,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>6</v>
+        <v>39.45</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
@@ -16454,7 +16454,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -16496,7 +16496,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>7</v>
+        <v>11.35</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -16547,7 +16547,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>7</v>
+        <v>6.83</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -16556,7 +16556,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -16598,7 +16598,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>6.54</v>
+        <v>8.99</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -16649,7 +16649,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>6.46</v>
+        <v>43.68</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -16700,7 +16700,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>6</v>
+        <v>10.92</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -16751,7 +16751,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>7</v>
+        <v>7.99</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -16802,7 +16802,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
@@ -16811,7 +16811,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -16853,7 +16853,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>5.6</v>
+        <v>4.21</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -16904,7 +16904,7 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>7.06</v>
+        <v>6.79</v>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
@@ -16913,7 +16913,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -16955,7 +16955,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>5.94</v>
+        <v>6.44</v>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
@@ -16964,7 +16964,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -17006,7 +17006,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>6.14</v>
+        <v>5</v>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -17057,7 +17057,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
@@ -17066,7 +17066,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -17108,7 +17108,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>5.22</v>
+        <v>4</v>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -17159,7 +17159,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -17168,7 +17168,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -17210,7 +17210,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -17219,7 +17219,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -17261,7 +17261,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>5.08</v>
+        <v>6</v>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
@@ -17270,7 +17270,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -17312,7 +17312,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>7.25</v>
+        <v>4</v>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
@@ -17321,7 +17321,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -17363,7 +17363,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>5.76</v>
+        <v>4.51</v>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
@@ -17372,7 +17372,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -17414,7 +17414,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>4.99</v>
+        <v>6</v>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
@@ -17423,7 +17423,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -17465,7 +17465,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>5.79</v>
+        <v>27.08</v>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -17474,7 +17474,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -17516,7 +17516,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>4.78</v>
+        <v>6.48</v>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
@@ -17525,7 +17525,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -17567,7 +17567,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>3.72</v>
+        <v>3.17</v>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -17618,7 +17618,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>7.19</v>
+        <v>4</v>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
@@ -17627,7 +17627,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -17669,7 +17669,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>4.82</v>
+        <v>3</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
@@ -17678,7 +17678,7 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -17720,7 +17720,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>4.14</v>
+        <v>6.03</v>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
@@ -17733,7 +17733,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -17775,7 +17775,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>5</v>
+        <v>2.83</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
@@ -17788,7 +17788,7 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -17830,7 +17830,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>10</v>
+        <v>7.39</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
@@ -17839,7 +17839,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -17881,7 +17881,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>8.140000000000001</v>
+        <v>7.35</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -17932,7 +17932,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>5.81</v>
+        <v>5</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -17941,7 +17941,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -17983,7 +17983,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -18034,7 +18034,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>8</v>
+        <v>8.49</v>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
@@ -18043,7 +18043,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -18085,7 +18085,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>3.99</v>
+        <v>2.5</v>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -18136,7 +18136,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>4</v>
+        <v>3.08</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -18145,7 +18145,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -18187,7 +18187,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>10.7</v>
+        <v>8.93</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
@@ -18196,7 +18196,7 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -18238,7 +18238,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>6</v>
+        <v>5.57</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -18289,7 +18289,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>8.23</v>
+        <v>4.41</v>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -18298,7 +18298,7 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -18340,7 +18340,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>5.77</v>
+        <v>6</v>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
@@ -18349,7 +18349,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -18391,7 +18391,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>7</v>
+        <v>5.19</v>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -18442,7 +18442,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>6</v>
+        <v>4.92</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -18493,7 +18493,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
@@ -18502,7 +18502,7 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -18544,7 +18544,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>8.31</v>
+        <v>3.99</v>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -18553,7 +18553,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -18595,7 +18595,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>6.68</v>
+        <v>5.2</v>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
@@ -18604,7 +18604,7 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -18646,7 +18646,7 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>7.76</v>
+        <v>7</v>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
@@ -18655,7 +18655,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -18697,7 +18697,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>5.6</v>
+        <v>5.08</v>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
@@ -18706,7 +18706,7 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -18748,7 +18748,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>6</v>
+        <v>3.99</v>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
@@ -18757,7 +18757,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -18799,7 +18799,7 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>7</v>
+        <v>7.75</v>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
@@ -18808,7 +18808,7 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -18850,7 +18850,7 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>6</v>
+        <v>3.94</v>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
@@ -18859,7 +18859,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -18901,7 +18901,7 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>7.24</v>
+        <v>4.12</v>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
@@ -18910,7 +18910,7 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -18952,7 +18952,7 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>6.76</v>
+        <v>8</v>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
@@ -18961,7 +18961,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -19003,7 +19003,7 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>7.99</v>
+        <v>4</v>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
@@ -19012,7 +19012,7 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -19054,7 +19054,7 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>6.01</v>
+        <v>4.31</v>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
@@ -19063,7 +19063,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -19105,7 +19105,7 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>6</v>
+        <v>4.72</v>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -19156,7 +19156,7 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>8.880000000000001</v>
+        <v>4.97</v>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
@@ -19165,7 +19165,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -19207,7 +19207,7 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>5.39</v>
+        <v>5.04</v>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -19258,7 +19258,7 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>8.73</v>
+        <v>3.96</v>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
@@ -19267,7 +19267,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -19309,7 +19309,7 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>6.26</v>
+        <v>6.02</v>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
@@ -19318,7 +19318,7 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -19360,7 +19360,7 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
@@ -19369,7 +19369,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -19411,7 +19411,7 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>6.37</v>
+        <v>3.04</v>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -19420,7 +19420,7 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -19462,7 +19462,7 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>5</v>
+        <v>3.96</v>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
@@ -19471,7 +19471,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -19513,7 +19513,7 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
@@ -19522,7 +19522,7 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -19564,7 +19564,7 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -19615,7 +19615,7 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
@@ -19624,7 +19624,7 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -19666,7 +19666,7 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>4.5</v>
+        <v>4.16</v>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
@@ -19679,7 +19679,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -19721,7 +19721,7 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>6.08</v>
+        <v>6.02</v>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -19776,7 +19776,7 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>10.68</v>
+        <v>9.98</v>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -19827,7 +19827,7 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>8</v>
+        <v>8.43</v>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -19878,7 +19878,7 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>7.47</v>
+        <v>6.77</v>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
@@ -19887,7 +19887,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -19929,7 +19929,7 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>7.75</v>
+        <v>9.18</v>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
@@ -19938,7 +19938,7 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -19980,7 +19980,7 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>6.24</v>
+        <v>6</v>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
@@ -19989,7 +19989,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -20031,7 +20031,7 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>3.76</v>
+        <v>3.4</v>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
@@ -20040,7 +20040,7 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -20082,7 +20082,7 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>6.32</v>
+        <v>6</v>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
@@ -20091,7 +20091,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:02</t>
         </is>
       </c>
     </row>
@@ -20133,7 +20133,7 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>10.47</v>
+        <v>7</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
@@ -20142,7 +20142,7 @@
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -20184,7 +20184,7 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>8.99</v>
+        <v>4</v>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
@@ -20193,7 +20193,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -20235,7 +20235,7 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
@@ -20244,7 +20244,7 @@
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -20286,7 +20286,7 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>7</v>
+        <v>4.13</v>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
@@ -20295,7 +20295,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -20337,7 +20337,7 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>6.23</v>
+        <v>5</v>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
@@ -20346,7 +20346,7 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -20388,7 +20388,7 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>7.78</v>
+        <v>6</v>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
@@ -20397,7 +20397,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -20439,7 +20439,7 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>7.03</v>
+        <v>4</v>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
@@ -20448,7 +20448,7 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -20490,7 +20490,7 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>5.97</v>
+        <v>4.13</v>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
@@ -20499,7 +20499,7 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -20550,7 +20550,7 @@
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -20592,7 +20592,7 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
@@ -20601,7 +20601,7 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -20643,7 +20643,7 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
@@ -20652,7 +20652,7 @@
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -20694,7 +20694,7 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>6</v>
+        <v>7.1</v>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
@@ -20703,7 +20703,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -20745,7 +20745,7 @@
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -20796,7 +20796,7 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>8.01</v>
+        <v>5.03</v>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -20847,7 +20847,7 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>6.52</v>
+        <v>3.97</v>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
@@ -20856,7 +20856,7 @@
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -20898,7 +20898,7 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>7.65</v>
+        <v>7</v>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
@@ -20907,7 +20907,7 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -20949,7 +20949,7 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>6.16</v>
+        <v>4</v>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
@@ -20958,7 +20958,7 @@
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -21000,7 +21000,7 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
@@ -21009,7 +21009,7 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -21051,7 +21051,7 @@
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>7.15</v>
+        <v>6</v>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
@@ -21060,7 +21060,7 @@
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -21102,7 +21102,7 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>5.85</v>
+        <v>4</v>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
@@ -21111,7 +21111,7 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -21153,7 +21153,7 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>7.8</v>
+        <v>5.12</v>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
@@ -21162,7 +21162,7 @@
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -21204,7 +21204,7 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>5.4</v>
+        <v>5.88</v>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
@@ -21213,7 +21213,7 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -21255,7 +21255,7 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>8.01</v>
+        <v>5.63</v>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -21306,7 +21306,7 @@
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>5.06</v>
+        <v>3.48</v>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -21357,7 +21357,7 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>4.14</v>
+        <v>3.03</v>
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
@@ -21366,7 +21366,7 @@
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -21408,7 +21408,7 @@
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>5</v>
+        <v>6.11</v>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
@@ -21417,7 +21417,7 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -21459,7 +21459,7 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>6.51</v>
+        <v>3.09</v>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
@@ -21468,7 +21468,7 @@
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -21510,7 +21510,7 @@
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>5.18</v>
+        <v>3.91</v>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
@@ -21519,7 +21519,7 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -21561,7 +21561,7 @@
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>5.31</v>
+        <v>4</v>
       </c>
       <c r="J117" s="4" t="inlineStr">
         <is>
@@ -21570,7 +21570,7 @@
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -21612,7 +21612,7 @@
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>6.32</v>
+        <v>6</v>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
@@ -21625,7 +21625,7 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -21667,7 +21667,7 @@
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>5.03</v>
+        <v>4.03</v>
       </c>
       <c r="J119" s="4" t="inlineStr">
         <is>
@@ -21680,7 +21680,7 @@
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -21722,7 +21722,7 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>12.33</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
@@ -21731,7 +21731,7 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -21773,7 +21773,7 @@
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>6.57</v>
+        <v>6</v>
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
@@ -21782,7 +21782,7 @@
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -21824,7 +21824,7 @@
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
@@ -21833,7 +21833,7 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -21875,7 +21875,7 @@
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>7.2</v>
+        <v>7.04</v>
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
@@ -21884,7 +21884,7 @@
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -21926,7 +21926,7 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>8</v>
+        <v>4.96</v>
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
@@ -21935,7 +21935,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -21977,7 +21977,7 @@
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>5</v>
+        <v>3.02</v>
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
@@ -21986,7 +21986,7 @@
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -22028,7 +22028,7 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
@@ -22037,7 +22037,7 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -22079,7 +22079,7 @@
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>10.77</v>
+        <v>10.81</v>
       </c>
       <c r="J127" s="4" t="inlineStr">
         <is>
@@ -22088,7 +22088,7 @@
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -22130,7 +22130,7 @@
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>6.11</v>
+        <v>5.93</v>
       </c>
       <c r="J128" s="4" t="inlineStr">
         <is>
@@ -22139,7 +22139,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -22181,7 +22181,7 @@
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>9.140000000000001</v>
+        <v>9.18</v>
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
@@ -22190,7 +22190,7 @@
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -22232,7 +22232,7 @@
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>4.85</v>
+        <v>5</v>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
@@ -22241,7 +22241,7 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -22283,7 +22283,7 @@
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -22334,7 +22334,7 @@
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>6</v>
+        <v>6.01</v>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
@@ -22343,7 +22343,7 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -22385,7 +22385,7 @@
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
@@ -22394,7 +22394,7 @@
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -22436,7 +22436,7 @@
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
@@ -22445,7 +22445,7 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -22487,7 +22487,7 @@
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>8.960000000000001</v>
+        <v>5</v>
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
@@ -22496,7 +22496,7 @@
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -22538,7 +22538,7 @@
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
@@ -22547,7 +22547,7 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -22589,7 +22589,7 @@
         </is>
       </c>
       <c r="I137" s="2" t="n">
-        <v>6.96</v>
+        <v>6</v>
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
@@ -22598,7 +22598,7 @@
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -22640,7 +22640,7 @@
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>9.01</v>
+        <v>8</v>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
@@ -22649,7 +22649,7 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -22691,7 +22691,7 @@
         </is>
       </c>
       <c r="I139" s="2" t="n">
-        <v>10.47</v>
+        <v>7</v>
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
@@ -22700,7 +22700,7 @@
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -22742,7 +22742,7 @@
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
@@ -22751,7 +22751,7 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -22793,7 +22793,7 @@
         </is>
       </c>
       <c r="I141" s="2" t="n">
-        <v>7.01</v>
+        <v>7.34</v>
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -22844,7 +22844,7 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>8.619999999999999</v>
+        <v>11.04</v>
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
@@ -22853,7 +22853,7 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -22895,7 +22895,7 @@
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>7.07</v>
+        <v>6.35</v>
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
@@ -22904,7 +22904,7 @@
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -22946,7 +22946,7 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>10.93</v>
+        <v>8.69</v>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
@@ -22955,7 +22955,7 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -22997,7 +22997,7 @@
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
@@ -23006,7 +23006,7 @@
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -23048,7 +23048,7 @@
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>9.42</v>
+        <v>5.2</v>
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
@@ -23057,7 +23057,7 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -23099,7 +23099,7 @@
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>6.58</v>
+        <v>6.99</v>
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
@@ -23108,7 +23108,7 @@
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -23150,7 +23150,7 @@
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>9.34</v>
+        <v>4.81</v>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
@@ -23159,7 +23159,7 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="I149" s="2" t="n">
-        <v>6</v>
+        <v>4.05</v>
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
@@ -23210,7 +23210,7 @@
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -23252,7 +23252,7 @@
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>5.19</v>
+        <v>4</v>
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
@@ -23261,7 +23261,7 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -23303,7 +23303,7 @@
         </is>
       </c>
       <c r="I151" s="2" t="n">
-        <v>6.61</v>
+        <v>4.19</v>
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
@@ -23312,7 +23312,7 @@
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -23354,7 +23354,7 @@
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>5.83</v>
+        <v>3.54</v>
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
@@ -23363,7 +23363,7 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -23405,7 +23405,7 @@
         </is>
       </c>
       <c r="I153" s="2" t="n">
-        <v>7.01</v>
+        <v>3.08</v>
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -23456,7 +23456,7 @@
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>6.27</v>
+        <v>4</v>
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
@@ -23465,7 +23465,7 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -23507,7 +23507,7 @@
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="J155" s="4" t="inlineStr">
         <is>
@@ -23516,7 +23516,7 @@
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -23558,7 +23558,7 @@
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>6.77</v>
+        <v>4.22</v>
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
@@ -23571,7 +23571,7 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -23613,7 +23613,7 @@
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>7.21</v>
+        <v>2.78</v>
       </c>
       <c r="J157" s="4" t="inlineStr">
         <is>
@@ -23626,7 +23626,7 @@
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -23668,7 +23668,7 @@
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>16.87</v>
+        <v>10.72</v>
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
@@ -23677,7 +23677,7 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -23719,7 +23719,7 @@
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>12.37</v>
+        <v>4.57</v>
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
@@ -23728,7 +23728,7 @@
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:26</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -23770,7 +23770,7 @@
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>11.77</v>
+        <v>5.21</v>
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
@@ -23779,7 +23779,7 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -23821,7 +23821,7 @@
         </is>
       </c>
       <c r="I161" s="2" t="n">
-        <v>11.23</v>
+        <v>6</v>
       </c>
       <c r="J161" s="2" t="inlineStr">
         <is>
@@ -23830,7 +23830,7 @@
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -23872,7 +23872,7 @@
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>10.61</v>
+        <v>5.07</v>
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
@@ -23881,7 +23881,7 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -23923,7 +23923,7 @@
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
@@ -23932,7 +23932,7 @@
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>7.89</v>
+        <v>3</v>
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
@@ -23983,7 +23983,7 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -24025,7 +24025,7 @@
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>16.12</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="J165" s="4" t="inlineStr">
         <is>
@@ -24034,7 +24034,7 @@
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -24076,7 +24076,7 @@
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>11.25</v>
+        <v>5.17</v>
       </c>
       <c r="J166" s="4" t="inlineStr">
         <is>
@@ -24085,7 +24085,7 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -24127,7 +24127,7 @@
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>10.21</v>
+        <v>6.89</v>
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
@@ -24136,7 +24136,7 @@
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -24178,7 +24178,7 @@
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>10.77</v>
+        <v>4.22</v>
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
@@ -24187,7 +24187,7 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -24229,7 +24229,7 @@
         </is>
       </c>
       <c r="I169" s="2" t="n">
-        <v>8.1</v>
+        <v>3.78</v>
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
@@ -24238,7 +24238,7 @@
       </c>
       <c r="K169" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -24280,7 +24280,7 @@
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>9.02</v>
+        <v>4.19</v>
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
@@ -24289,7 +24289,7 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -24331,7 +24331,7 @@
         </is>
       </c>
       <c r="I171" s="2" t="n">
-        <v>11.17</v>
+        <v>5.81</v>
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
@@ -24340,7 +24340,7 @@
       </c>
       <c r="K171" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -24382,7 +24382,7 @@
         </is>
       </c>
       <c r="I172" s="2" t="n">
-        <v>9.130000000000001</v>
+        <v>4</v>
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
@@ -24391,7 +24391,7 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -24433,7 +24433,7 @@
         </is>
       </c>
       <c r="I173" s="2" t="n">
-        <v>9.82</v>
+        <v>4.02</v>
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
@@ -24442,7 +24442,7 @@
       </c>
       <c r="K173" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -24484,7 +24484,7 @@
         </is>
       </c>
       <c r="I174" s="2" t="n">
-        <v>9.02</v>
+        <v>6.16</v>
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
@@ -24493,7 +24493,7 @@
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -24535,7 +24535,7 @@
         </is>
       </c>
       <c r="I175" s="2" t="n">
-        <v>10.2</v>
+        <v>3.82</v>
       </c>
       <c r="J175" s="2" t="inlineStr">
         <is>
@@ -24544,7 +24544,7 @@
       </c>
       <c r="K175" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -24586,7 +24586,7 @@
         </is>
       </c>
       <c r="I176" s="2" t="n">
-        <v>8.09</v>
+        <v>4</v>
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
@@ -24595,7 +24595,7 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -24637,7 +24637,7 @@
         </is>
       </c>
       <c r="I177" s="2" t="n">
-        <v>9.720000000000001</v>
+        <v>4</v>
       </c>
       <c r="J177" s="2" t="inlineStr">
         <is>
@@ -24646,7 +24646,7 @@
       </c>
       <c r="K177" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -24688,7 +24688,7 @@
         </is>
       </c>
       <c r="I178" s="2" t="n">
-        <v>6.47</v>
+        <v>6</v>
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
@@ -24697,7 +24697,7 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -24739,7 +24739,7 @@
         </is>
       </c>
       <c r="I179" s="2" t="n">
-        <v>10.28</v>
+        <v>4.8</v>
       </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
@@ -24748,7 +24748,7 @@
       </c>
       <c r="K179" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -24790,7 +24790,7 @@
         </is>
       </c>
       <c r="I180" s="2" t="n">
-        <v>9.279999999999999</v>
+        <v>4.82</v>
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
@@ -24799,7 +24799,7 @@
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -24841,7 +24841,7 @@
         </is>
       </c>
       <c r="I181" s="2" t="n">
-        <v>8.06</v>
+        <v>6.05</v>
       </c>
       <c r="J181" s="2" t="inlineStr">
         <is>
@@ -24850,7 +24850,7 @@
       </c>
       <c r="K181" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -24892,7 +24892,7 @@
         </is>
       </c>
       <c r="I182" s="2" t="n">
-        <v>9.27</v>
+        <v>4</v>
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
@@ -24901,7 +24901,7 @@
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -24943,7 +24943,7 @@
         </is>
       </c>
       <c r="I183" s="2" t="n">
-        <v>8.1</v>
+        <v>4</v>
       </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
@@ -24952,7 +24952,7 @@
       </c>
       <c r="K183" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -24994,7 +24994,7 @@
         </is>
       </c>
       <c r="I184" s="2" t="n">
-        <v>9.109999999999999</v>
+        <v>6</v>
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
@@ -25003,7 +25003,7 @@
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -25045,7 +25045,7 @@
         </is>
       </c>
       <c r="I185" s="2" t="n">
-        <v>7.61</v>
+        <v>5.08</v>
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
@@ -25054,7 +25054,7 @@
       </c>
       <c r="K185" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -25096,7 +25096,7 @@
         </is>
       </c>
       <c r="I186" s="2" t="n">
-        <v>8.550000000000001</v>
+        <v>4</v>
       </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
@@ -25105,7 +25105,7 @@
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -25147,7 +25147,7 @@
         </is>
       </c>
       <c r="I187" s="2" t="n">
-        <v>10.11</v>
+        <v>5</v>
       </c>
       <c r="J187" s="2" t="inlineStr">
         <is>
@@ -25156,7 +25156,7 @@
       </c>
       <c r="K187" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -25198,7 +25198,7 @@
         </is>
       </c>
       <c r="I188" s="2" t="n">
-        <v>7.09</v>
+        <v>5</v>
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
@@ -25207,7 +25207,7 @@
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -25249,7 +25249,7 @@
         </is>
       </c>
       <c r="I189" s="2" t="n">
-        <v>5.95</v>
+        <v>3.26</v>
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
       </c>
       <c r="K189" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -25300,7 +25300,7 @@
         </is>
       </c>
       <c r="I190" s="2" t="n">
-        <v>9.859999999999999</v>
+        <v>3.74</v>
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
@@ -25309,7 +25309,7 @@
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -25351,7 +25351,7 @@
         </is>
       </c>
       <c r="I191" s="2" t="n">
-        <v>6.66</v>
+        <v>4</v>
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
@@ -25360,7 +25360,7 @@
       </c>
       <c r="K191" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -25402,7 +25402,7 @@
         </is>
       </c>
       <c r="I192" s="2" t="n">
-        <v>8.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -25453,7 +25453,7 @@
         </is>
       </c>
       <c r="I193" s="2" t="n">
-        <v>7.22</v>
+        <v>4.18</v>
       </c>
       <c r="J193" s="4" t="inlineStr">
         <is>
@@ -25462,7 +25462,7 @@
       </c>
       <c r="K193" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -25504,7 +25504,7 @@
         </is>
       </c>
       <c r="I194" s="2" t="n">
-        <v>6.04</v>
+        <v>3.05</v>
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
@@ -25517,7 +25517,7 @@
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -25559,7 +25559,7 @@
         </is>
       </c>
       <c r="I195" s="2" t="n">
-        <v>8.83</v>
+        <v>3</v>
       </c>
       <c r="J195" s="4" t="inlineStr">
         <is>
@@ -25572,7 +25572,7 @@
       </c>
       <c r="K195" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -25614,7 +25614,7 @@
         </is>
       </c>
       <c r="I196" s="2" t="n">
-        <v>17.38</v>
+        <v>10.44</v>
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
@@ -25623,7 +25623,7 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -25665,7 +25665,7 @@
         </is>
       </c>
       <c r="I197" s="2" t="n">
-        <v>11.71</v>
+        <v>4.56</v>
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
@@ -25674,7 +25674,7 @@
       </c>
       <c r="K197" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -25716,7 +25716,7 @@
         </is>
       </c>
       <c r="I198" s="2" t="n">
-        <v>11.26</v>
+        <v>7</v>
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -25767,7 +25767,7 @@
         </is>
       </c>
       <c r="I199" s="2" t="n">
-        <v>9.65</v>
+        <v>4.93</v>
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
       </c>
       <c r="K199" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -25818,7 +25818,7 @@
         </is>
       </c>
       <c r="I200" s="2" t="n">
-        <v>8.359999999999999</v>
+        <v>4.08</v>
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
@@ -25827,7 +25827,7 @@
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -25869,7 +25869,7 @@
         </is>
       </c>
       <c r="I201" s="2" t="n">
-        <v>7.71</v>
+        <v>3.92</v>
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
@@ -25878,7 +25878,7 @@
       </c>
       <c r="K201" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -25920,7 +25920,7 @@
         </is>
       </c>
       <c r="I202" s="2" t="n">
-        <v>6.02</v>
+        <v>4</v>
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
@@ -25929,7 +25929,7 @@
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -25971,7 +25971,7 @@
         </is>
       </c>
       <c r="I203" s="2" t="n">
-        <v>12.61</v>
+        <v>7.24</v>
       </c>
       <c r="J203" s="4" t="inlineStr">
         <is>
@@ -25980,7 +25980,7 @@
       </c>
       <c r="K203" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -26022,7 +26022,7 @@
         </is>
       </c>
       <c r="I204" s="2" t="n">
-        <v>6.23</v>
+        <v>4.76</v>
       </c>
       <c r="J204" s="4" t="inlineStr">
         <is>
@@ -26031,7 +26031,7 @@
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -26073,7 +26073,7 @@
         </is>
       </c>
       <c r="I205" s="2" t="n">
-        <v>10.38</v>
+        <v>7</v>
       </c>
       <c r="J205" s="2" t="inlineStr">
         <is>
@@ -26082,7 +26082,7 @@
       </c>
       <c r="K205" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -26124,7 +26124,7 @@
         </is>
       </c>
       <c r="I206" s="2" t="n">
-        <v>9.359999999999999</v>
+        <v>4</v>
       </c>
       <c r="J206" s="2" t="inlineStr">
         <is>
@@ -26133,7 +26133,7 @@
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -26175,7 +26175,7 @@
         </is>
       </c>
       <c r="I207" s="2" t="n">
-        <v>7.78</v>
+        <v>4.57</v>
       </c>
       <c r="J207" s="2" t="inlineStr">
         <is>
@@ -26184,7 +26184,7 @@
       </c>
       <c r="K207" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -26226,7 +26226,7 @@
         </is>
       </c>
       <c r="I208" s="2" t="n">
-        <v>7.8</v>
+        <v>5</v>
       </c>
       <c r="J208" s="2" t="inlineStr">
         <is>
@@ -26235,7 +26235,7 @@
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -26277,7 +26277,7 @@
         </is>
       </c>
       <c r="I209" s="2" t="n">
-        <v>8.02</v>
+        <v>4.22</v>
       </c>
       <c r="J209" s="2" t="inlineStr">
         <is>
@@ -26286,7 +26286,7 @@
       </c>
       <c r="K209" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -26328,7 +26328,7 @@
         </is>
       </c>
       <c r="I210" s="2" t="n">
-        <v>6.6</v>
+        <v>4</v>
       </c>
       <c r="J210" s="2" t="inlineStr">
         <is>
@@ -26337,7 +26337,7 @@
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -26379,7 +26379,7 @@
         </is>
       </c>
       <c r="I211" s="2" t="n">
-        <v>8.029999999999999</v>
+        <v>5</v>
       </c>
       <c r="J211" s="2" t="inlineStr">
         <is>
@@ -26388,7 +26388,7 @@
       </c>
       <c r="K211" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -26430,7 +26430,7 @@
         </is>
       </c>
       <c r="I212" s="2" t="n">
-        <v>7.58</v>
+        <v>5</v>
       </c>
       <c r="J212" s="2" t="inlineStr">
         <is>
@@ -26439,7 +26439,7 @@
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -26481,7 +26481,7 @@
         </is>
       </c>
       <c r="I213" s="2" t="n">
-        <v>9.470000000000001</v>
+        <v>4</v>
       </c>
       <c r="J213" s="2" t="inlineStr">
         <is>
@@ -26490,7 +26490,7 @@
       </c>
       <c r="K213" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -26532,7 +26532,7 @@
         </is>
       </c>
       <c r="I214" s="2" t="n">
-        <v>6.09</v>
+        <v>5</v>
       </c>
       <c r="J214" s="2" t="inlineStr">
         <is>
@@ -26541,7 +26541,7 @@
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -26583,7 +26583,7 @@
         </is>
       </c>
       <c r="I215" s="2" t="n">
-        <v>8.69</v>
+        <v>6.04</v>
       </c>
       <c r="J215" s="2" t="inlineStr">
         <is>
@@ -26592,7 +26592,7 @@
       </c>
       <c r="K215" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
         </is>
       </c>
       <c r="I216" s="2" t="n">
-        <v>7.3</v>
+        <v>3.96</v>
       </c>
       <c r="J216" s="2" t="inlineStr">
         <is>
@@ -26643,7 +26643,7 @@
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -26685,7 +26685,7 @@
         </is>
       </c>
       <c r="I217" s="2" t="n">
-        <v>7.7</v>
+        <v>4</v>
       </c>
       <c r="J217" s="2" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
       </c>
       <c r="K217" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -26736,7 +26736,7 @@
         </is>
       </c>
       <c r="I218" s="2" t="n">
-        <v>7.09</v>
+        <v>7</v>
       </c>
       <c r="J218" s="2" t="inlineStr">
         <is>
@@ -26745,7 +26745,7 @@
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -26787,7 +26787,7 @@
         </is>
       </c>
       <c r="I219" s="2" t="n">
-        <v>7.92</v>
+        <v>4</v>
       </c>
       <c r="J219" s="2" t="inlineStr">
         <is>
@@ -26796,7 +26796,7 @@
       </c>
       <c r="K219" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -26838,7 +26838,7 @@
         </is>
       </c>
       <c r="I220" s="2" t="n">
-        <v>7.27</v>
+        <v>5</v>
       </c>
       <c r="J220" s="2" t="inlineStr">
         <is>
@@ -26847,7 +26847,7 @@
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -26889,7 +26889,7 @@
         </is>
       </c>
       <c r="I221" s="2" t="n">
-        <v>7.73</v>
+        <v>4</v>
       </c>
       <c r="J221" s="2" t="inlineStr">
         <is>
@@ -26898,7 +26898,7 @@
       </c>
       <c r="K221" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -26940,7 +26940,7 @@
         </is>
       </c>
       <c r="I222" s="2" t="n">
-        <v>6.12</v>
+        <v>6</v>
       </c>
       <c r="J222" s="2" t="inlineStr">
         <is>
@@ -26949,7 +26949,7 @@
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -26991,7 +26991,7 @@
         </is>
       </c>
       <c r="I223" s="2" t="n">
-        <v>7.24</v>
+        <v>4</v>
       </c>
       <c r="J223" s="2" t="inlineStr">
         <is>
@@ -27000,7 +27000,7 @@
       </c>
       <c r="K223" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -27042,7 +27042,7 @@
         </is>
       </c>
       <c r="I224" s="2" t="n">
-        <v>9.07</v>
+        <v>5</v>
       </c>
       <c r="J224" s="2" t="inlineStr">
         <is>
@@ -27051,7 +27051,7 @@
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -27093,7 +27093,7 @@
         </is>
       </c>
       <c r="I225" s="2" t="n">
-        <v>6.55</v>
+        <v>6</v>
       </c>
       <c r="J225" s="2" t="inlineStr">
         <is>
@@ -27102,7 +27102,7 @@
       </c>
       <c r="K225" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -27144,7 +27144,7 @@
         </is>
       </c>
       <c r="I226" s="2" t="n">
-        <v>6.92</v>
+        <v>3.19</v>
       </c>
       <c r="J226" s="2" t="inlineStr">
         <is>
@@ -27153,7 +27153,7 @@
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -27195,7 +27195,7 @@
         </is>
       </c>
       <c r="I227" s="2" t="n">
-        <v>5.19</v>
+        <v>4</v>
       </c>
       <c r="J227" s="2" t="inlineStr">
         <is>
@@ -27204,7 +27204,7 @@
       </c>
       <c r="K227" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -27246,7 +27246,7 @@
         </is>
       </c>
       <c r="I228" s="2" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="J228" s="2" t="inlineStr">
         <is>
@@ -27255,7 +27255,7 @@
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -27297,7 +27297,7 @@
         </is>
       </c>
       <c r="I229" s="2" t="n">
-        <v>8.140000000000001</v>
+        <v>6</v>
       </c>
       <c r="J229" s="2" t="inlineStr">
         <is>
@@ -27306,7 +27306,7 @@
       </c>
       <c r="K229" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -27348,7 +27348,7 @@
         </is>
       </c>
       <c r="I230" s="2" t="n">
-        <v>4.97</v>
+        <v>4</v>
       </c>
       <c r="J230" s="2" t="inlineStr">
         <is>
@@ -27357,7 +27357,7 @@
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -27399,7 +27399,7 @@
         </is>
       </c>
       <c r="I231" s="2" t="n">
-        <v>9.140000000000001</v>
+        <v>4</v>
       </c>
       <c r="J231" s="4" t="inlineStr">
         <is>
@@ -27408,7 +27408,7 @@
       </c>
       <c r="K231" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -27450,7 +27450,7 @@
         </is>
       </c>
       <c r="I232" s="2" t="n">
-        <v>5.97</v>
+        <v>4.03</v>
       </c>
       <c r="J232" s="2" t="inlineStr">
         <is>
@@ -27463,7 +27463,7 @@
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -27505,7 +27505,7 @@
         </is>
       </c>
       <c r="I233" s="2" t="n">
-        <v>5.64</v>
+        <v>4.97</v>
       </c>
       <c r="J233" s="4" t="inlineStr">
         <is>
@@ -27518,7 +27518,7 @@
       </c>
       <c r="K233" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -27560,7 +27560,7 @@
         </is>
       </c>
       <c r="I234" s="2" t="n">
-        <v>14.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J234" s="2" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -27611,7 +27611,7 @@
         </is>
       </c>
       <c r="I235" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J235" s="2" t="inlineStr">
         <is>
@@ -27620,7 +27620,7 @@
       </c>
       <c r="K235" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -27662,7 +27662,7 @@
         </is>
       </c>
       <c r="I236" s="2" t="n">
-        <v>8.140000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="J236" s="2" t="inlineStr">
         <is>
@@ -27671,7 +27671,7 @@
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -27713,7 +27713,7 @@
         </is>
       </c>
       <c r="I237" s="2" t="n">
-        <v>9.65</v>
+        <v>5</v>
       </c>
       <c r="J237" s="2" t="inlineStr">
         <is>
@@ -27722,7 +27722,7 @@
       </c>
       <c r="K237" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -27764,7 +27764,7 @@
         </is>
       </c>
       <c r="I238" s="2" t="n">
-        <v>7.1</v>
+        <v>6</v>
       </c>
       <c r="J238" s="2" t="inlineStr">
         <is>
@@ -27773,7 +27773,7 @@
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -27815,7 +27815,7 @@
         </is>
       </c>
       <c r="I239" s="2" t="n">
-        <v>6.71</v>
+        <v>4.03</v>
       </c>
       <c r="J239" s="2" t="inlineStr">
         <is>
@@ -27824,7 +27824,7 @@
       </c>
       <c r="K239" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -27866,7 +27866,7 @@
         </is>
       </c>
       <c r="I240" s="2" t="n">
-        <v>5.49</v>
+        <v>3.11</v>
       </c>
       <c r="J240" s="2" t="inlineStr">
         <is>
@@ -27875,7 +27875,7 @@
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -27917,7 +27917,7 @@
         </is>
       </c>
       <c r="I241" s="2" t="n">
-        <v>12.34</v>
+        <v>7</v>
       </c>
       <c r="J241" s="4" t="inlineStr">
         <is>
@@ -27926,7 +27926,7 @@
       </c>
       <c r="K241" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -27968,7 +27968,7 @@
         </is>
       </c>
       <c r="I242" s="2" t="n">
-        <v>6.82</v>
+        <v>6</v>
       </c>
       <c r="J242" s="4" t="inlineStr">
         <is>
@@ -27977,7 +27977,7 @@
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -28019,7 +28019,7 @@
         </is>
       </c>
       <c r="I243" s="2" t="n">
-        <v>9.84</v>
+        <v>5</v>
       </c>
       <c r="J243" s="2" t="inlineStr">
         <is>
@@ -28028,7 +28028,7 @@
       </c>
       <c r="K243" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -28070,7 +28070,7 @@
         </is>
       </c>
       <c r="I244" s="2" t="n">
-        <v>6.52</v>
+        <v>4</v>
       </c>
       <c r="J244" s="2" t="inlineStr">
         <is>
@@ -28079,7 +28079,7 @@
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -28121,7 +28121,7 @@
         </is>
       </c>
       <c r="I245" s="2" t="n">
-        <v>8.26</v>
+        <v>7</v>
       </c>
       <c r="J245" s="2" t="inlineStr">
         <is>
@@ -28130,7 +28130,7 @@
       </c>
       <c r="K245" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -28172,7 +28172,7 @@
         </is>
       </c>
       <c r="I246" s="2" t="n">
-        <v>7.04</v>
+        <v>4.05</v>
       </c>
       <c r="J246" s="2" t="inlineStr">
         <is>
@@ -28181,7 +28181,7 @@
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -28223,7 +28223,7 @@
         </is>
       </c>
       <c r="I247" s="2" t="n">
-        <v>7.96</v>
+        <v>5</v>
       </c>
       <c r="J247" s="2" t="inlineStr">
         <is>
@@ -28232,7 +28232,7 @@
       </c>
       <c r="K247" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -28274,7 +28274,7 @@
         </is>
       </c>
       <c r="I248" s="2" t="n">
-        <v>7.19</v>
+        <v>6.18</v>
       </c>
       <c r="J248" s="2" t="inlineStr">
         <is>
@@ -28283,7 +28283,7 @@
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -28325,7 +28325,7 @@
         </is>
       </c>
       <c r="I249" s="2" t="n">
-        <v>6.91</v>
+        <v>4</v>
       </c>
       <c r="J249" s="2" t="inlineStr">
         <is>
@@ -28334,7 +28334,7 @@
       </c>
       <c r="K249" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -28376,7 +28376,7 @@
         </is>
       </c>
       <c r="I250" s="2" t="n">
-        <v>8.44</v>
+        <v>4</v>
       </c>
       <c r="J250" s="2" t="inlineStr">
         <is>
@@ -28385,7 +28385,7 @@
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -28427,7 +28427,7 @@
         </is>
       </c>
       <c r="I251" s="2" t="n">
-        <v>6.67</v>
+        <v>4</v>
       </c>
       <c r="J251" s="2" t="inlineStr">
         <is>
@@ -28436,7 +28436,7 @@
       </c>
       <c r="K251" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -28478,7 +28478,7 @@
         </is>
       </c>
       <c r="I252" s="2" t="n">
-        <v>8.24</v>
+        <v>6.02</v>
       </c>
       <c r="J252" s="2" t="inlineStr">
         <is>
@@ -28487,7 +28487,7 @@
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -28529,7 +28529,7 @@
         </is>
       </c>
       <c r="I253" s="2" t="n">
-        <v>5.68</v>
+        <v>4.98</v>
       </c>
       <c r="J253" s="2" t="inlineStr">
         <is>
@@ -28538,7 +28538,7 @@
       </c>
       <c r="K253" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -28580,7 +28580,7 @@
         </is>
       </c>
       <c r="I254" s="2" t="n">
-        <v>8.34</v>
+        <v>4.18</v>
       </c>
       <c r="J254" s="2" t="inlineStr">
         <is>
@@ -28589,7 +28589,7 @@
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -28631,7 +28631,7 @@
         </is>
       </c>
       <c r="I255" s="2" t="n">
-        <v>5.82</v>
+        <v>6</v>
       </c>
       <c r="J255" s="2" t="inlineStr">
         <is>
@@ -28640,7 +28640,7 @@
       </c>
       <c r="K255" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -28682,7 +28682,7 @@
         </is>
       </c>
       <c r="I256" s="2" t="n">
-        <v>10</v>
+        <v>5.44</v>
       </c>
       <c r="J256" s="2" t="inlineStr">
         <is>
@@ -28691,7 +28691,7 @@
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -28733,7 +28733,7 @@
         </is>
       </c>
       <c r="I257" s="2" t="n">
-        <v>7.37</v>
+        <v>3.56</v>
       </c>
       <c r="J257" s="2" t="inlineStr">
         <is>
@@ -28742,7 +28742,7 @@
       </c>
       <c r="K257" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -28784,7 +28784,7 @@
         </is>
       </c>
       <c r="I258" s="2" t="n">
-        <v>8.630000000000001</v>
+        <v>6</v>
       </c>
       <c r="J258" s="2" t="inlineStr">
         <is>
@@ -28793,7 +28793,7 @@
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -28835,7 +28835,7 @@
         </is>
       </c>
       <c r="I259" s="2" t="n">
-        <v>6</v>
+        <v>5.03</v>
       </c>
       <c r="J259" s="2" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
       </c>
       <c r="K259" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -28886,7 +28886,7 @@
         </is>
       </c>
       <c r="I260" s="2" t="n">
-        <v>7</v>
+        <v>4.1</v>
       </c>
       <c r="J260" s="2" t="inlineStr">
         <is>
@@ -28895,7 +28895,7 @@
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -28937,7 +28937,7 @@
         </is>
       </c>
       <c r="I261" s="2" t="n">
-        <v>9</v>
+        <v>4.25</v>
       </c>
       <c r="J261" s="2" t="inlineStr">
         <is>
@@ -28946,7 +28946,7 @@
       </c>
       <c r="K261" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -28988,7 +28988,7 @@
         </is>
       </c>
       <c r="I262" s="2" t="n">
-        <v>6.86</v>
+        <v>6.05</v>
       </c>
       <c r="J262" s="2" t="inlineStr">
         <is>
@@ -28997,7 +28997,7 @@
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -29039,7 +29039,7 @@
         </is>
       </c>
       <c r="I263" s="2" t="n">
-        <v>8.1</v>
+        <v>5</v>
       </c>
       <c r="J263" s="2" t="inlineStr">
         <is>
@@ -29048,7 +29048,7 @@
       </c>
       <c r="K263" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -29090,7 +29090,7 @@
         </is>
       </c>
       <c r="I264" s="2" t="n">
-        <v>5.25</v>
+        <v>3</v>
       </c>
       <c r="J264" s="2" t="inlineStr">
         <is>
@@ -29099,7 +29099,7 @@
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -29141,7 +29141,7 @@
         </is>
       </c>
       <c r="I265" s="2" t="n">
-        <v>8.16</v>
+        <v>5</v>
       </c>
       <c r="J265" s="2" t="inlineStr">
         <is>
@@ -29150,7 +29150,7 @@
       </c>
       <c r="K265" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -29192,7 +29192,7 @@
         </is>
       </c>
       <c r="I266" s="2" t="n">
-        <v>5</v>
+        <v>6.23</v>
       </c>
       <c r="J266" s="2" t="inlineStr">
         <is>
@@ -29201,7 +29201,7 @@
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -29243,7 +29243,7 @@
         </is>
       </c>
       <c r="I267" s="2" t="n">
-        <v>5.47</v>
+        <v>3.82</v>
       </c>
       <c r="J267" s="2" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
       </c>
       <c r="K267" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
         </is>
       </c>
       <c r="I268" s="2" t="n">
-        <v>7.3</v>
+        <v>4.08</v>
       </c>
       <c r="J268" s="2" t="inlineStr">
         <is>
@@ -29303,7 +29303,7 @@
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -29345,7 +29345,7 @@
         </is>
       </c>
       <c r="I269" s="2" t="n">
-        <v>5.94</v>
+        <v>4.92</v>
       </c>
       <c r="J269" s="4" t="inlineStr">
         <is>
@@ -29354,7 +29354,7 @@
       </c>
       <c r="K269" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -29396,7 +29396,7 @@
         </is>
       </c>
       <c r="I270" s="2" t="n">
-        <v>5.37</v>
+        <v>4</v>
       </c>
       <c r="J270" s="2" t="inlineStr">
         <is>
@@ -29409,7 +29409,7 @@
       </c>
       <c r="K270" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -29451,7 +29451,7 @@
         </is>
       </c>
       <c r="I271" s="2" t="n">
-        <v>7.95</v>
+        <v>4.08</v>
       </c>
       <c r="J271" s="4" t="inlineStr">
         <is>
@@ -29464,7 +29464,7 @@
       </c>
       <c r="K271" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -29506,7 +29506,7 @@
         </is>
       </c>
       <c r="I272" s="2" t="n">
-        <v>14.39</v>
+        <v>10.34</v>
       </c>
       <c r="J272" s="2" t="inlineStr">
         <is>
@@ -29515,7 +29515,7 @@
       </c>
       <c r="K272" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -29557,7 +29557,7 @@
         </is>
       </c>
       <c r="I273" s="2" t="n">
-        <v>8.23</v>
+        <v>5.75</v>
       </c>
       <c r="J273" s="2" t="inlineStr">
         <is>
@@ -29566,7 +29566,7 @@
       </c>
       <c r="K273" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -29608,7 +29608,7 @@
         </is>
       </c>
       <c r="I274" s="2" t="n">
-        <v>10.59</v>
+        <v>3.83</v>
       </c>
       <c r="J274" s="2" t="inlineStr">
         <is>
@@ -29617,7 +29617,7 @@
       </c>
       <c r="K274" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -29659,7 +29659,7 @@
         </is>
       </c>
       <c r="I275" s="2" t="n">
-        <v>8.199999999999999</v>
+        <v>7.24</v>
       </c>
       <c r="J275" s="2" t="inlineStr">
         <is>
@@ -29668,7 +29668,7 @@
       </c>
       <c r="K275" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -29710,7 +29710,7 @@
         </is>
       </c>
       <c r="I276" s="2" t="n">
-        <v>10.04</v>
+        <v>4.91</v>
       </c>
       <c r="J276" s="2" t="inlineStr">
         <is>
@@ -29719,7 +29719,7 @@
       </c>
       <c r="K276" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -29761,7 +29761,7 @@
         </is>
       </c>
       <c r="I277" s="2" t="n">
-        <v>5.4</v>
+        <v>3</v>
       </c>
       <c r="J277" s="2" t="inlineStr">
         <is>
@@ -29770,7 +29770,7 @@
       </c>
       <c r="K277" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -29812,7 +29812,7 @@
         </is>
       </c>
       <c r="I278" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J278" s="2" t="inlineStr">
         <is>
@@ -29821,7 +29821,7 @@
       </c>
       <c r="K278" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:27</t>
+          <t>2026-08-10 22:52:03</t>
         </is>
       </c>
     </row>
@@ -29863,7 +29863,7 @@
         </is>
       </c>
       <c r="I279" s="2" t="n">
-        <v>13.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J279" s="4" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
       </c>
       <c r="K279" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:28</t>
+          <t>2026-08-10 22:52:04</t>
         </is>
       </c>
     </row>
@@ -29914,7 +29914,7 @@
         </is>
       </c>
       <c r="I280" s="2" t="n">
-        <v>8.07</v>
+        <v>3.8</v>
       </c>
       <c r="J280" s="4" t="inlineStr">
         <is>
@@ -29923,7 +29923,7 @@
       </c>
       <c r="K280" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:28</t>
+          <t>2026-08-10 22:52:04</t>
         </is>
       </c>
     </row>
@@ -29965,7 +29965,7 @@
         </is>
       </c>
       <c r="I281" s="2" t="n">
-        <v>10.41</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="J281" s="2" t="inlineStr">
         <is>
@@ -29974,7 +29974,7 @@
       </c>
       <c r="K281" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:28</t>
+          <t>2026-08-10 22:52:04</t>
         </is>
       </c>
     </row>
@@ -30016,7 +30016,7 @@
         </is>
       </c>
       <c r="I282" s="2" t="n">
-        <v>6.76</v>
+        <v>3.98</v>
       </c>
       <c r="J282" s="2" t="inlineStr">
         <is>
@@ -30025,7 +30025,7 @@
       </c>
       <c r="K282" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:28</t>
+          <t>2026-08-10 22:52:04</t>
         </is>
       </c>
     </row>
@@ -30067,7 +30067,7 @@
         </is>
       </c>
       <c r="I283" s="2" t="n">
-        <v>10.72</v>
+        <v>4.19</v>
       </c>
       <c r="J283" s="2" t="inlineStr">
         <is>
@@ -30076,7 +30076,7 @@
       </c>
       <c r="K283" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:28</t>
+          <t>2026-08-10 22:52:04</t>
         </is>
       </c>
     </row>
@@ -30118,7 +30118,7 @@
         </is>
       </c>
       <c r="I284" s="2" t="n">
-        <v>6.28</v>
+        <v>3.8</v>
       </c>
       <c r="J284" s="2" t="inlineStr">
         <is>
@@ -30127,7 +30127,7 @@
       </c>
       <c r="K284" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:28</t>
+          <t>2026-08-10 22:52:04</t>
         </is>
       </c>
     </row>
@@ -30169,7 +30169,7 @@
         </is>
       </c>
       <c r="I285" s="2" t="n">
-        <v>9.960000000000001</v>
+        <v>7</v>
       </c>
       <c r="J285" s="2" t="inlineStr">
         <is>
@@ -30178,7 +30178,7 @@
       </c>
       <c r="K285" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:28</t>
+          <t>2026-08-10 22:52:04</t>
         </is>
       </c>
     </row>
@@ -30220,7 +30220,7 @@
         </is>
       </c>
       <c r="I286" s="2" t="n">
-        <v>7.51</v>
+        <v>4</v>
       </c>
       <c r="J286" s="2" t="inlineStr">
         <is>
@@ -30229,7 +30229,7 @@
       </c>
       <c r="K286" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:28</t>
+          <t>2026-08-10 22:52:04</t>
         </is>
       </c>
     </row>
@@ -30271,7 +30271,7 @@
         </is>
       </c>
       <c r="I287" s="2" t="n">
-        <v>9.56</v>
+        <v>4</v>
       </c>
       <c r="J287" s="2" t="inlineStr">
         <is>
@@ -30280,7 +30280,7 @@
       </c>
       <c r="K287" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:28</t>
+          <t>2026-08-10 22:52:04</t>
         </is>
       </c>
     </row>
@@ -30322,7 +30322,7 @@
         </is>
       </c>
       <c r="I288" s="2" t="n">
-        <v>8.449999999999999</v>
+        <v>6</v>
       </c>
       <c r="J288" s="2" t="inlineStr">
         <is>
@@ -30331,7 +30331,7 @@
       </c>
       <c r="K288" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:28</t>
+          <t>2026-08-10 22:52:04</t>
         </is>
       </c>
     </row>
@@ -30373,7 +30373,7 @@
         </is>
       </c>
       <c r="I289" s="2" t="n">
-        <v>10.22</v>
+        <v>5.06</v>
       </c>
       <c r="J289" s="2" t="inlineStr">
         <is>
@@ -30382,7 +30382,7 @@
       </c>
       <c r="K289" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:28</t>
+          <t>2026-08-10 22:52:04</t>
         </is>
       </c>
     </row>
@@ -30424,7 +30424,7 @@
         </is>
       </c>
       <c r="I290" s="2" t="n">
-        <v>6.81</v>
+        <v>3.86</v>
       </c>
       <c r="J290" s="2" t="inlineStr">
         <is>
@@ -30433,7 +30433,7 @@
       </c>
       <c r="K290" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:28</t>
+          <t>2026-08-10 22:52:04</t>
         </is>
       </c>
     </row>
@@ -30475,7 +30475,7 @@
         </is>
       </c>
       <c r="I291" s="2" t="n">
-        <v>10.17</v>
+        <v>5.05</v>
       </c>
       <c r="J291" s="2" t="inlineStr">
         <is>
@@ -30484,7 +30484,7 @@
       </c>
       <c r="K291" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:28</t>
+          <t>2026-08-10 22:52:04</t>
         </is>
       </c>
     </row>
@@ -30526,7 +30526,7 @@
         </is>
       </c>
       <c r="I292" s="2" t="n">
-        <v>7.3</v>
+        <v>4.95</v>
       </c>
       <c r="J292" s="2" t="inlineStr">
         <is>
@@ -30535,7 +30535,7 @@
       </c>
       <c r="K292" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:28</t>
+          <t>2026-08-10 22:52:04</t>
         </is>
       </c>
     </row>
@@ -30577,7 +30577,7 @@
         </is>
       </c>
       <c r="I293" s="2" t="n">
-        <v>9.289999999999999</v>
+        <v>4</v>
       </c>
       <c r="J293" s="2" t="inlineStr">
         <is>
@@ -30586,7 +30586,7 @@
       </c>
       <c r="K293" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:28</t>
+          <t>2026-08-10 22:52:04</t>
         </is>
       </c>
     </row>
@@ -30628,7 +30628,7 @@
         </is>
       </c>
       <c r="I294" s="2" t="n">
-        <v>10.7</v>
+        <v>5</v>
       </c>
       <c r="J294" s="2" t="inlineStr">
         <is>
@@ -30637,7 +30637,7 @@
       </c>
       <c r="K294" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:28</t>
+          <t>2026-08-10 22:52:04</t>
         </is>
       </c>
     </row>
@@ -30679,7 +30679,7 @@
         </is>
       </c>
       <c r="I295" s="2" t="n">
-        <v>8.359999999999999</v>
+        <v>6</v>
       </c>
       <c r="J295" s="2" t="inlineStr">
         <is>
@@ -30688,7 +30688,7 @@
       </c>
       <c r="K295" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:28</t>
+          <t>2026-08-10 22:52:04</t>
         </is>
       </c>
     </row>
@@ -30730,7 +30730,7 @@
         </is>
       </c>
       <c r="I296" s="2" t="n">
-        <v>10.38</v>
+        <v>5</v>
       </c>
       <c r="J296" s="2" t="inlineStr">
         <is>
@@ -30739,7 +30739,7 @@
       </c>
       <c r="K296" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:28</t>
+          <t>2026-08-10 22:52:04</t>
         </is>
       </c>
     </row>
@@ -30781,7 +30781,7 @@
         </is>
       </c>
       <c r="I297" s="2" t="n">
-        <v>6.88</v>
+        <v>4</v>
       </c>
       <c r="J297" s="2" t="inlineStr">
         <is>
@@ -30790,7 +30790,7 @@
       </c>
       <c r="K297" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:28</t>
+          <t>2026-08-10 22:52:04</t>
         </is>
       </c>
     </row>
@@ -30832,7 +30832,7 @@
         </is>
       </c>
       <c r="I298" s="2" t="n">
-        <v>10.09</v>
+        <v>7.1</v>
       </c>
       <c r="J298" s="2" t="inlineStr">
         <is>
@@ -30841,7 +30841,7 @@
       </c>
       <c r="K298" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:28</t>
+          <t>2026-08-10 22:52:04</t>
         </is>
       </c>
     </row>
@@ -30883,7 +30883,7 @@
         </is>
       </c>
       <c r="I299" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J299" s="2" t="inlineStr">
         <is>
@@ -30892,7 +30892,7 @@
       </c>
       <c r="K299" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:28</t>
+          <t>2026-08-10 22:52:04</t>
         </is>
       </c>
     </row>
@@ -30934,7 +30934,7 @@
         </is>
       </c>
       <c r="I300" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J300" s="2" t="inlineStr">
         <is>
@@ -30943,7 +30943,7 @@
       </c>
       <c r="K300" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:28</t>
+          <t>2026-08-10 22:52:04</t>
         </is>
       </c>
     </row>
@@ -30985,7 +30985,7 @@
         </is>
       </c>
       <c r="I301" s="2" t="n">
-        <v>6.82</v>
+        <v>4</v>
       </c>
       <c r="J301" s="2" t="inlineStr">
         <is>
@@ -30994,7 +30994,7 @@
       </c>
       <c r="K301" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:28</t>
+          <t>2026-08-10 22:52:04</t>
         </is>
       </c>
     </row>
@@ -31112,7 +31112,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>101.13 req/s</t>
+          <t>162.96 req/s</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -31134,7 +31134,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>96.98 ms</t>
+          <t>59.15 ms</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -31156,7 +31156,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>23 ms / 202 ms</t>
+          <t>11 ms / 962 ms</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -31178,7 +31178,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>91 ms</t>
+          <t>52 ms</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -31200,7 +31200,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>143 ms</t>
+          <t>79 ms</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -31222,7 +31222,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>191 ms</t>
+          <t>364 ms</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -31362,7 +31362,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:33</t>
+          <t>2026-08-10 22:52:07</t>
         </is>
       </c>
     </row>
@@ -31414,7 +31414,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:33</t>
+          <t>2026-08-10 22:52:07</t>
         </is>
       </c>
     </row>
@@ -31466,7 +31466,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:33</t>
+          <t>2026-08-10 22:52:07</t>
         </is>
       </c>
     </row>
@@ -31518,7 +31518,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:33</t>
+          <t>2026-08-10 22:52:07</t>
         </is>
       </c>
     </row>
@@ -31570,7 +31570,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:33</t>
+          <t>2026-08-10 22:52:07</t>
         </is>
       </c>
     </row>
@@ -31622,7 +31622,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:33</t>
+          <t>2026-08-10 22:52:07</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:33</t>
+          <t>2026-08-10 22:52:07</t>
         </is>
       </c>
     </row>
@@ -31726,7 +31726,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:33</t>
+          <t>2026-08-10 22:52:07</t>
         </is>
       </c>
     </row>
@@ -31778,7 +31778,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:33</t>
+          <t>2026-08-10 22:52:07</t>
         </is>
       </c>
     </row>
@@ -31830,7 +31830,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:33</t>
+          <t>2026-08-10 22:52:07</t>
         </is>
       </c>
     </row>
@@ -31882,7 +31882,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:33</t>
+          <t>2026-08-10 22:52:07</t>
         </is>
       </c>
     </row>
@@ -31934,7 +31934,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:33</t>
+          <t>2026-08-10 22:52:07</t>
         </is>
       </c>
     </row>
@@ -31986,7 +31986,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:33</t>
+          <t>2026-08-10 22:52:07</t>
         </is>
       </c>
     </row>
@@ -32038,7 +32038,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:33</t>
+          <t>2026-08-10 22:52:07</t>
         </is>
       </c>
     </row>
@@ -32090,7 +32090,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:06:33</t>
+          <t>2026-08-10 22:52:07</t>
         </is>
       </c>
     </row>
@@ -32206,7 +32206,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>RPS: 19.91 req/s</t>
+          <t>RPS: 15.44 req/s</t>
         </is>
       </c>
     </row>
@@ -32222,7 +32222,7 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>369</v>
+        <v>355</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -32236,7 +32236,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Success Rate: 98.40%</t>
+          <t>Success Rate: 94.67%</t>
         </is>
       </c>
     </row>
@@ -32252,7 +32252,7 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -32266,7 +32266,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Error Rate: 1.60%</t>
+          <t>Error Rate: 5.33%</t>
         </is>
       </c>
     </row>
@@ -32283,7 +32283,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>249.94 ms</t>
+          <t>321.97 ms</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -32315,7 +32315,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>39.42 ms</t>
+          <t>21.48 ms</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -32347,7 +32347,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>531.13 ms</t>
+          <t>5008.08 ms</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -32379,7 +32379,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5032.38 ms</t>
+          <t>5032.01 ms</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -32411,7 +32411,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>5798.12 ms</t>
+          <t>5043.07 ms</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -32443,7 +32443,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>62.78%</t>
+          <t>46.49%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -32475,7 +32475,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>59.02 MB</t>
+          <t>59.1 MB</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -32490,7 +32490,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Max RAM: 59.04 MB (+0.43 MB growth)</t>
+          <t>Max RAM: 59.11 MB (+0.49 MB growth)</t>
         </is>
       </c>
     </row>
@@ -32522,7 +32522,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Ping: 12.0 ms (sqlite)</t>
+          <t>Ping: 5.0 ms (sqlite)</t>
         </is>
       </c>
     </row>
@@ -32571,12 +32571,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Avg 56.11 ms (Min 12.9 / Max 103.48 ms)</t>
+          <t>Avg 25.23 ms (Min 7.38 / Max 63.35 ms)</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 0.8 req/s</t>
+          <t>15 reqs, 0.62 req/s</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -32603,12 +32603,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Avg 60.57 ms (Min 41.26 / Max 83.17 ms)</t>
+          <t>Avg 17.72 ms (Min 11.08 / Max 22.14 ms)</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 0.8 req/s</t>
+          <t>15 reqs, 0.62 req/s</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -32635,12 +32635,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Avg 54.56 ms (Min 46.91 / Max 71.45 ms)</t>
+          <t>Avg 21.18 ms (Min 16.78 / Max 27.86 ms)</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 0.8 req/s</t>
+          <t>15 reqs, 0.62 req/s</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -32667,12 +32667,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Avg 89.38 ms (Min 67.34 / Max 172.23 ms)</t>
+          <t>Avg 47.05 ms (Min 25.14 / Max 90.69 ms)</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 0.8 req/s</t>
+          <t>15 reqs, 0.62 req/s</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -32699,12 +32699,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Avg 81.52 ms (Min 33.69 / Max 273.92 ms)</t>
+          <t>Avg 28.36 ms (Min 16.53 / Max 48.19 ms)</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>45 reqs, 2.39 req/s</t>
+          <t>45 reqs, 1.85 req/s</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -32731,12 +32731,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Avg 31.73 ms (Min 21.02 / Max 39.18 ms)</t>
+          <t>Avg 14.45 ms (Min 10.31 / Max 17.33 ms)</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 0.8 req/s</t>
+          <t>15 reqs, 0.62 req/s</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -32763,12 +32763,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Avg 38.72 ms (Min 28.08 / Max 49.06 ms)</t>
+          <t>Avg 22.04 ms (Min 16.29 / Max 31.29 ms)</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 0.8 req/s</t>
+          <t>15 reqs, 0.62 req/s</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -32795,12 +32795,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Avg 44.01 ms (Min 33.7 / Max 56.82 ms)</t>
+          <t>Avg 29.42 ms (Min 17.14 / Max 44.75 ms)</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 0.8 req/s</t>
+          <t>15 reqs, 0.62 req/s</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -32827,12 +32827,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Avg 32.13 ms (Min 24.48 / Max 36.71 ms)</t>
+          <t>Avg 19.56 ms (Min 16.16 / Max 23.3 ms)</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 0.8 req/s</t>
+          <t>15 reqs, 0.62 req/s</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -32859,12 +32859,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Avg 33.63 ms (Min 26.92 / Max 43.41 ms)</t>
+          <t>Avg 20.55 ms (Min 13.0 / Max 28.25 ms)</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 0.8 req/s</t>
+          <t>15 reqs, 0.62 req/s</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -32891,12 +32891,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Avg 31.78 ms (Min 26.3 / Max 37.35 ms)</t>
+          <t>Avg 21.82 ms (Min 13.49 / Max 29.97 ms)</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 0.8 req/s</t>
+          <t>15 reqs, 0.62 req/s</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -32923,12 +32923,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Avg 32.38 ms (Min 29.6 / Max 36.48 ms)</t>
+          <t>Avg 19.42 ms (Min 14.0 / Max 25.67 ms)</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 0.8 req/s</t>
+          <t>15 reqs, 0.62 req/s</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -32955,12 +32955,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Avg 32.28 ms (Min 26.91 / Max 38.26 ms)</t>
+          <t>Avg 18.62 ms (Min 12.99 / Max 24.94 ms)</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 0.8 req/s</t>
+          <t>15 reqs, 0.62 req/s</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -32987,12 +32987,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Avg 37.21 ms (Min 31.83 / Max 46.61 ms)</t>
+          <t>Avg 19.85 ms (Min 13.23 / Max 28.22 ms)</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 0.8 req/s</t>
+          <t>15 reqs, 0.62 req/s</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -33019,12 +33019,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Avg 45.38 ms (Min 36.55 / Max 51.72 ms)</t>
+          <t>Avg 21.06 ms (Min 13.78 / Max 27.49 ms)</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 0.8 req/s</t>
+          <t>15 reqs, 0.62 req/s</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -33051,12 +33051,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Avg 43.04 ms (Min 39.18 / Max 47.04 ms)</t>
+          <t>Avg 19.85 ms (Min 16.34 / Max 22.54 ms)</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 0.8 req/s</t>
+          <t>15 reqs, 0.62 req/s</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -33083,12 +33083,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Avg 39.43 ms (Min 34.23 / Max 46.25 ms)</t>
+          <t>Avg 20.54 ms (Min 15.34 / Max 24.75 ms)</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 0.8 req/s</t>
+          <t>15 reqs, 0.62 req/s</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -33115,12 +33115,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Avg 34.85 ms (Min 26.75 / Max 41.12 ms)</t>
+          <t>Avg 22.37 ms (Min 15.94 / Max 36.73 ms)</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 0.8 req/s</t>
+          <t>15 reqs, 0.62 req/s</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -33147,12 +33147,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Avg 34.03 ms (Min 26.5 / Max 42.55 ms)</t>
+          <t>Avg 22.71 ms (Min 15.3 / Max 27.49 ms)</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 0.8 req/s</t>
+          <t>15 reqs, 0.62 req/s</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -33179,12 +33179,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Avg 25.84 ms (Min 20.34 / Max 30.34 ms)</t>
+          <t>Avg 19.45 ms (Min 14.02 / Max 25.07 ms)</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 0.8 req/s</t>
+          <t>15 reqs, 0.62 req/s</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -33211,12 +33211,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Avg 372.79 ms (Min 25.0 / Max 1747.34 ms)</t>
+          <t>Avg 23.46 ms (Min 19.4 / Max 28.85 ms)</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 0.8 req/s</t>
+          <t>15 reqs, 0.62 req/s</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -33243,12 +33243,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Avg 4721.67 ms (Min 2993.66 / Max 5798.12 ms)</t>
+          <t>Avg 5025.33 ms (Min 5006.91 / Max 5043.07 ms)</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 0.8 req/s</t>
+          <t>15 reqs, 0.62 req/s</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
@@ -33258,7 +33258,7 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>Errors: 6 (40.0%)</t>
+          <t>Errors: 15 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -33275,22 +33275,22 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Avg 112.4 ms (Min 29.24 / Max 1131.3 ms)</t>
+          <t>Avg 2492.58 ms (Min 8.78 / Max 5013.7 ms)</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>15 reqs, 0.8 req/s</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+          <t>15 reqs, 0.62 req/s</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>Errors: 0 (0.0%)</t>
+          <t>Errors: 5 (33.33%)</t>
         </is>
       </c>
     </row>
